--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="5"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="416" uniqueCount="149">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="154">
   <si>
     <t>!Enum</t>
   </si>
@@ -395,9 +395,6 @@
   <si>
     <t>고블린 고브의 황금 던전이다.
 골드를 주보상으로 얻을 수 있다.</t>
-  </si>
-  <si>
-    <t>Image_GoldDungeon</t>
   </si>
   <si>
     <t>Rift</t>
@@ -473,6 +470,30 @@
   </si>
   <si>
     <t>2001;2002;2003</t>
+  </si>
+  <si>
+    <t>Image_GoldDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Thumbnail</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_GoldDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_RiftDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_LabyrinthDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_RuinsDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
 </file>
@@ -985,7 +1006,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -3156,7 +3177,7 @@
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
@@ -3164,17 +3185,18 @@
     <col min="3" max="3" width="17.875" style="2" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="58.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="24.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="18.125" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="15.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="15.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="11.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="20.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="16.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="9" style="2" customWidth="1"/>
-    <col min="13" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="24.875" style="2" customWidth="1"/>
+    <col min="7" max="7" width="18.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="15.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="15.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="11.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="20.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="16.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
         <v>112</v>
       </c>
@@ -3186,8 +3208,9 @@
       <c r="E1" s="9"/>
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
-    </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="H1" s="9"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
         <v>7</v>
@@ -3201,26 +3224,29 @@
       <c r="E2" s="8" t="s">
         <v>10</v>
       </c>
-      <c r="F2" t="s">
+      <c r="F2" s="8" t="s">
+        <v>149</v>
+      </c>
+      <c r="G2" t="s">
         <v>113</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>114</v>
       </c>
-      <c r="H2" s="2" t="s">
+      <c r="I2" s="2" t="s">
         <v>115</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>116</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>117</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>118</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>119</v>
@@ -3235,25 +3261,28 @@
         <v>14</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>13</v>
+        <v>14</v>
       </c>
       <c r="G3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="H3" s="2" t="s">
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="2" t="s">
         <v>120</v>
       </c>
-      <c r="I3" s="2" t="s">
+      <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="J3" s="2" t="s">
+      <c r="K3" s="2" t="s">
         <v>121</v>
       </c>
-      <c r="K3" s="2" t="s">
+      <c r="L3" s="2" t="s">
         <v>13</v>
       </c>
     </row>
-    <row r="4" spans="1:11" ht="33" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
         <v>122</v>
       </c>
@@ -3264,120 +3293,132 @@
         <v>124</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>125</v>
-      </c>
-      <c r="F4" s="2">
+        <v>150</v>
+      </c>
+      <c r="F4" s="2" t="s">
+        <v>148</v>
+      </c>
+      <c r="G4" s="2">
         <v>5</v>
       </c>
-      <c r="G4" s="2">
+      <c r="H4" s="2">
         <v>30</v>
       </c>
-      <c r="H4" t="s">
-        <v>130</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="I4" t="s">
+        <v>129</v>
+      </c>
+      <c r="J4" s="2">
         <v>500</v>
-      </c>
-      <c r="J4" s="2">
-        <v>2</v>
       </c>
       <c r="K4" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="5" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L4" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
+        <v>125</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>126</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>127</v>
       </c>
-      <c r="D5" s="17" t="s">
+      <c r="E5" s="2" t="s">
+        <v>151</v>
+      </c>
+      <c r="F5" s="2" t="s">
         <v>128</v>
       </c>
-      <c r="E5" s="2" t="s">
+      <c r="G5" s="2">
+        <v>5</v>
+      </c>
+      <c r="H5" s="2">
+        <v>30</v>
+      </c>
+      <c r="I5" t="s">
         <v>129</v>
       </c>
-      <c r="F5" s="2">
-        <v>5</v>
-      </c>
-      <c r="G5" s="2">
-        <v>30</v>
-      </c>
-      <c r="H5" t="s">
-        <v>130</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="J5" s="2">
         <v>500</v>
-      </c>
-      <c r="J5" s="2">
-        <v>2</v>
       </c>
       <c r="K5" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="6" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L5" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
+        <v>130</v>
+      </c>
+      <c r="C6" s="2" t="s">
         <v>131</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="D6" s="17" t="s">
         <v>132</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="E6" s="2" t="s">
+        <v>152</v>
+      </c>
+      <c r="F6" s="2" t="s">
         <v>133</v>
       </c>
-      <c r="E6" s="2" t="s">
-        <v>134</v>
-      </c>
-      <c r="F6" s="2">
+      <c r="G6" s="2">
         <v>5</v>
       </c>
-      <c r="G6" s="2">
+      <c r="H6" s="2">
         <v>30</v>
       </c>
-      <c r="H6" t="s">
-        <v>130</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="I6" t="s">
+        <v>129</v>
+      </c>
+      <c r="J6" s="2">
         <v>500</v>
-      </c>
-      <c r="J6" s="2">
-        <v>2</v>
       </c>
       <c r="K6" s="2">
         <v>2</v>
       </c>
-    </row>
-    <row r="7" spans="1:11" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="L6" s="2">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>134</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>135</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="D7" s="17" t="s">
         <v>136</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="E7" s="2" t="s">
+        <v>153</v>
+      </c>
+      <c r="F7" s="2" t="s">
         <v>137</v>
       </c>
-      <c r="E7" s="2" t="s">
-        <v>138</v>
-      </c>
-      <c r="F7" s="2">
+      <c r="G7" s="2">
         <v>5</v>
       </c>
-      <c r="G7" s="2">
+      <c r="H7" s="2">
         <v>30</v>
       </c>
-      <c r="H7" t="s">
-        <v>130</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="I7" t="s">
+        <v>129</v>
+      </c>
+      <c r="J7" s="2">
         <v>500</v>
       </c>
-      <c r="J7" s="2">
+      <c r="K7" s="2">
         <v>2</v>
       </c>
-      <c r="K7" s="2">
+      <c r="L7" s="2">
         <v>2</v>
       </c>
     </row>
@@ -3410,7 +3451,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3426,28 +3467,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>139</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>142</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>143</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>144</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>145</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>146</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>147</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3494,7 +3535,7 @@
         <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3517,7 +3558,7 @@
         <v>2001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -3540,7 +3581,7 @@
         <v>2001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
@@ -3563,7 +3604,7 @@
         <v>2001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G7" s="2">
         <v>150</v>
@@ -3586,7 +3627,7 @@
         <v>2001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G8" s="2">
         <v>200</v>
@@ -3609,7 +3650,7 @@
         <v>2001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G9" s="2">
         <v>250</v>
@@ -3632,7 +3673,7 @@
         <v>2001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G10" s="2">
         <v>300</v>
@@ -3655,7 +3696,7 @@
         <v>2001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G11" s="2">
         <v>350</v>
@@ -3678,7 +3719,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G12" s="2">
         <v>400</v>
@@ -3701,7 +3742,7 @@
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G13" s="2">
         <v>450</v>
@@ -3724,7 +3765,7 @@
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G14" s="2">
         <v>500</v>
@@ -3747,7 +3788,7 @@
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G15" s="2">
         <v>550</v>
@@ -3770,7 +3811,7 @@
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G16" s="2">
         <v>600</v>
@@ -3793,7 +3834,7 @@
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G17" s="2">
         <v>650</v>
@@ -3816,7 +3857,7 @@
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G18" s="2">
         <v>700</v>
@@ -3830,7 +3871,7 @@
         <v>20001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -3839,7 +3880,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -3853,7 +3894,7 @@
         <v>20002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -3862,7 +3903,7 @@
         <v>3001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G20" s="2">
         <v>50</v>
@@ -3876,7 +3917,7 @@
         <v>20003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -3885,7 +3926,7 @@
         <v>3001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G21" s="2">
         <v>75</v>
@@ -3899,7 +3940,7 @@
         <v>20004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -3908,7 +3949,7 @@
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G22" s="2">
         <v>100</v>
@@ -3922,7 +3963,7 @@
         <v>20005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -3931,7 +3972,7 @@
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G23" s="2">
         <v>125</v>
@@ -3945,7 +3986,7 @@
         <v>20006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -3954,7 +3995,7 @@
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G24" s="2">
         <v>150</v>
@@ -3968,7 +4009,7 @@
         <v>20007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D25" s="2">
         <v>7</v>
@@ -3977,7 +4018,7 @@
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G25" s="2">
         <v>175</v>
@@ -3991,7 +4032,7 @@
         <v>20008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D26" s="2">
         <v>8</v>
@@ -4000,7 +4041,7 @@
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G26" s="2">
         <v>200</v>
@@ -4014,7 +4055,7 @@
         <v>20009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D27" s="2">
         <v>9</v>
@@ -4023,7 +4064,7 @@
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G27" s="2">
         <v>225</v>
@@ -4037,7 +4078,7 @@
         <v>20010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
@@ -4046,7 +4087,7 @@
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G28" s="2">
         <v>250</v>
@@ -4060,7 +4101,7 @@
         <v>20011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D29" s="2">
         <v>11</v>
@@ -4069,7 +4110,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G29" s="2">
         <v>275</v>
@@ -4083,7 +4124,7 @@
         <v>20012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -4092,7 +4133,7 @@
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G30" s="2">
         <v>300</v>
@@ -4106,7 +4147,7 @@
         <v>20013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D31" s="2">
         <v>13</v>
@@ -4115,7 +4156,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G31" s="2">
         <v>325</v>
@@ -4129,7 +4170,7 @@
         <v>20014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D32" s="2">
         <v>14</v>
@@ -4138,7 +4179,7 @@
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G32" s="2">
         <v>350</v>
@@ -4152,7 +4193,7 @@
         <v>20015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D33" s="2">
         <v>15</v>
@@ -4161,7 +4202,7 @@
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G33" s="2">
         <v>375</v>
@@ -4175,7 +4216,7 @@
         <v>20016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
@@ -4184,7 +4225,7 @@
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G34" s="2">
         <v>400</v>
@@ -4198,7 +4239,7 @@
         <v>20017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D35" s="2">
         <v>17</v>
@@ -4207,7 +4248,7 @@
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G35" s="2">
         <v>425</v>
@@ -4221,7 +4262,7 @@
         <v>20018</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D36" s="2">
         <v>18</v>
@@ -4230,7 +4271,7 @@
         <v>3001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G36" s="2">
         <v>450</v>
@@ -4244,7 +4285,7 @@
         <v>20019</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D37" s="2">
         <v>19</v>
@@ -4253,7 +4294,7 @@
         <v>3001</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G37" s="2">
         <v>475</v>
@@ -4267,7 +4308,7 @@
         <v>20020</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="D38" s="2">
         <v>20</v>
@@ -4276,7 +4317,7 @@
         <v>3001</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="G38" s="2">
         <v>500</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="422" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="195">
   <si>
     <t>!Enum</t>
   </si>
@@ -168,9 +168,6 @@
     <t>Icon_Field_2-1</t>
   </si>
   <si>
-    <t>MapPrefab_Field_2-1</t>
-  </si>
-  <si>
     <t>Sound_Act2</t>
   </si>
   <si>
@@ -180,18 +177,12 @@
     <t>Icon_Field_2-2</t>
   </si>
   <si>
-    <t>MapPrefab_Field_2-2</t>
-  </si>
-  <si>
     <t>뒤집힌 대상로</t>
   </si>
   <si>
     <t>Icon_Field_2-3</t>
   </si>
   <si>
-    <t>MapPrefab_Field_2-3</t>
-  </si>
-  <si>
     <t>붉은 사구</t>
   </si>
   <si>
@@ -316,9 +307,6 @@
   </si>
   <si>
     <t>Act I - 붉은 안개 산맥</t>
-  </si>
-  <si>
-    <t>Image_Act_1</t>
   </si>
   <si>
     <t>Act II - 핏빛 사막</t>
@@ -493,6 +481,145 @@
   </si>
   <si>
     <t>Icon_RuinsDungeon</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_1-4</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-5</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-6</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-7</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-8</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-9</t>
+  </si>
+  <si>
+    <t>Icon_Field_1-10</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-4</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-5</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-6</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-7</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-8</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-9</t>
+  </si>
+  <si>
+    <t>Icon_Field_2-10</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_4-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_5-1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Icon_Field_5-2</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-3</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-4</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-5</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-6</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-7</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-8</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-9</t>
+  </si>
+  <si>
+    <t>Icon_Field_5-10</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-2</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-3</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-4</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-5</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-6</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-7</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-8</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-9</t>
+  </si>
+  <si>
+    <t>Icon_Field_4-10</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-2</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-3</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-4</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-5</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-6</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-7</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-8</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-9</t>
+  </si>
+  <si>
+    <t>Icon_Field_3-10</t>
+  </si>
+  <si>
+    <t>Image_Act_1</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1277,7 +1404,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>33</v>
@@ -1298,7 +1425,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>39</v>
+        <v>32</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -1312,11 +1439,15 @@
       <c r="C12" s="2" t="s">
         <v>40</v>
       </c>
-      <c r="E12" s="18"/>
+      <c r="E12" s="18" t="s">
+        <v>150</v>
+      </c>
       <c r="F12" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="G12" s="18"/>
+      <c r="G12" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H12" s="2" t="s">
         <v>33</v>
       </c>
@@ -1329,11 +1460,15 @@
       <c r="C13" s="2" t="s">
         <v>41</v>
       </c>
-      <c r="E13" s="18"/>
+      <c r="E13" s="18" t="s">
+        <v>151</v>
+      </c>
       <c r="F13" t="s">
         <v>3</v>
       </c>
-      <c r="G13" s="18"/>
+      <c r="G13" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H13" t="s">
         <v>33</v>
       </c>
@@ -1345,11 +1480,15 @@
       <c r="C14" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="E14"/>
+      <c r="E14" s="18" t="s">
+        <v>152</v>
+      </c>
       <c r="F14" t="s">
         <v>3</v>
       </c>
-      <c r="G14"/>
+      <c r="G14" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H14" t="s">
         <v>33</v>
       </c>
@@ -1361,11 +1500,15 @@
       <c r="C15" t="s">
         <v>43</v>
       </c>
-      <c r="E15"/>
+      <c r="E15" s="18" t="s">
+        <v>153</v>
+      </c>
       <c r="F15" t="s">
         <v>3</v>
       </c>
-      <c r="G15"/>
+      <c r="G15" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H15" t="s">
         <v>33</v>
       </c>
@@ -1377,11 +1520,15 @@
       <c r="C16" t="s">
         <v>44</v>
       </c>
-      <c r="E16"/>
+      <c r="E16" s="18" t="s">
+        <v>154</v>
+      </c>
       <c r="F16" t="s">
         <v>3</v>
       </c>
-      <c r="G16"/>
+      <c r="G16" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H16" t="s">
         <v>33</v>
       </c>
@@ -1393,11 +1540,15 @@
       <c r="C17" t="s">
         <v>45</v>
       </c>
-      <c r="E17"/>
+      <c r="E17" s="18" t="s">
+        <v>155</v>
+      </c>
       <c r="F17" t="s">
         <v>3</v>
       </c>
-      <c r="G17"/>
+      <c r="G17" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="H17" t="s">
         <v>33</v>
       </c>
@@ -1409,11 +1560,15 @@
       <c r="C18" t="s">
         <v>46</v>
       </c>
-      <c r="E18"/>
+      <c r="E18" s="18" t="s">
+        <v>156</v>
+      </c>
       <c r="F18" t="s">
         <v>3</v>
       </c>
-      <c r="G18"/>
+      <c r="G18" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H18" t="s">
         <v>33</v>
       </c>
@@ -1431,11 +1586,11 @@
       <c r="F19" t="s">
         <v>3</v>
       </c>
-      <c r="G19" t="s">
+      <c r="G19" s="18" t="s">
+        <v>32</v>
+      </c>
+      <c r="H19" t="s">
         <v>49</v>
-      </c>
-      <c r="H19" t="s">
-        <v>50</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -1443,19 +1598,19 @@
         <v>20202</v>
       </c>
       <c r="C20" t="s">
+        <v>50</v>
+      </c>
+      <c r="E20" t="s">
         <v>51</v>
       </c>
-      <c r="E20" t="s">
-        <v>52</v>
-      </c>
       <c r="F20" t="s">
         <v>3</v>
       </c>
-      <c r="G20" t="s">
-        <v>53</v>
+      <c r="G20" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="H20" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
@@ -1463,19 +1618,19 @@
         <v>20203</v>
       </c>
       <c r="C21" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="E21" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="F21" t="s">
         <v>3</v>
       </c>
-      <c r="G21" t="s">
-        <v>56</v>
+      <c r="G21" s="18" t="s">
+        <v>32</v>
       </c>
       <c r="H21" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
@@ -1483,15 +1638,19 @@
         <v>20204</v>
       </c>
       <c r="C22" t="s">
-        <v>57</v>
-      </c>
-      <c r="E22"/>
+        <v>54</v>
+      </c>
+      <c r="E22" t="s">
+        <v>157</v>
+      </c>
       <c r="F22" t="s">
         <v>3</v>
       </c>
-      <c r="G22"/>
+      <c r="G22" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H22" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
@@ -1499,15 +1658,19 @@
         <v>20205</v>
       </c>
       <c r="C23" t="s">
-        <v>58</v>
-      </c>
-      <c r="E23"/>
+        <v>55</v>
+      </c>
+      <c r="E23" t="s">
+        <v>158</v>
+      </c>
       <c r="F23" t="s">
         <v>3</v>
       </c>
-      <c r="G23"/>
+      <c r="G23" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H23" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -1515,15 +1678,19 @@
         <v>20206</v>
       </c>
       <c r="C24" t="s">
-        <v>59</v>
-      </c>
-      <c r="E24"/>
+        <v>56</v>
+      </c>
+      <c r="E24" t="s">
+        <v>159</v>
+      </c>
       <c r="F24" t="s">
         <v>3</v>
       </c>
-      <c r="G24"/>
+      <c r="G24" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H24" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
@@ -1531,15 +1698,19 @@
         <v>20207</v>
       </c>
       <c r="C25" t="s">
-        <v>60</v>
-      </c>
-      <c r="E25"/>
+        <v>57</v>
+      </c>
+      <c r="E25" t="s">
+        <v>160</v>
+      </c>
       <c r="F25" t="s">
         <v>3</v>
       </c>
-      <c r="G25"/>
+      <c r="G25" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H25" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
@@ -1547,15 +1718,19 @@
         <v>20208</v>
       </c>
       <c r="C26" t="s">
-        <v>61</v>
-      </c>
-      <c r="E26"/>
+        <v>58</v>
+      </c>
+      <c r="E26" t="s">
+        <v>161</v>
+      </c>
       <c r="F26" t="s">
         <v>3</v>
       </c>
-      <c r="G26"/>
+      <c r="G26" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H26" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
@@ -1563,15 +1738,19 @@
         <v>20209</v>
       </c>
       <c r="C27" t="s">
-        <v>62</v>
-      </c>
-      <c r="E27"/>
+        <v>59</v>
+      </c>
+      <c r="E27" t="s">
+        <v>162</v>
+      </c>
       <c r="F27" t="s">
         <v>3</v>
       </c>
-      <c r="G27"/>
+      <c r="G27" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="H27" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
@@ -1579,15 +1758,19 @@
         <v>20210</v>
       </c>
       <c r="C28" t="s">
-        <v>63</v>
-      </c>
-      <c r="E28"/>
+        <v>60</v>
+      </c>
+      <c r="E28" t="s">
+        <v>163</v>
+      </c>
       <c r="F28" t="s">
         <v>3</v>
       </c>
-      <c r="G28"/>
+      <c r="G28" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H28" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -1595,15 +1778,19 @@
         <v>20301</v>
       </c>
       <c r="C29" t="s">
-        <v>64</v>
-      </c>
-      <c r="E29"/>
+        <v>61</v>
+      </c>
+      <c r="E29" t="s">
+        <v>164</v>
+      </c>
       <c r="F29" t="s">
         <v>3</v>
       </c>
-      <c r="G29"/>
+      <c r="G29" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H29" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -1611,15 +1798,19 @@
         <v>20302</v>
       </c>
       <c r="C30" t="s">
-        <v>66</v>
-      </c>
-      <c r="E30"/>
+        <v>63</v>
+      </c>
+      <c r="E30" t="s">
+        <v>185</v>
+      </c>
       <c r="F30" t="s">
         <v>3</v>
       </c>
-      <c r="G30"/>
+      <c r="G30" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H30" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -1627,15 +1818,19 @@
         <v>20303</v>
       </c>
       <c r="C31" t="s">
-        <v>67</v>
-      </c>
-      <c r="E31"/>
+        <v>64</v>
+      </c>
+      <c r="E31" t="s">
+        <v>186</v>
+      </c>
       <c r="F31" t="s">
         <v>3</v>
       </c>
-      <c r="G31"/>
+      <c r="G31" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H31" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
@@ -1643,15 +1838,19 @@
         <v>20304</v>
       </c>
       <c r="C32" t="s">
-        <v>68</v>
-      </c>
-      <c r="E32"/>
+        <v>65</v>
+      </c>
+      <c r="E32" t="s">
+        <v>187</v>
+      </c>
       <c r="F32" t="s">
         <v>3</v>
       </c>
-      <c r="G32"/>
+      <c r="G32" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H32" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -1659,15 +1858,19 @@
         <v>20305</v>
       </c>
       <c r="C33" t="s">
-        <v>69</v>
-      </c>
-      <c r="E33"/>
+        <v>66</v>
+      </c>
+      <c r="E33" t="s">
+        <v>188</v>
+      </c>
       <c r="F33" t="s">
         <v>3</v>
       </c>
-      <c r="G33"/>
+      <c r="G33" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H33" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -1675,15 +1878,19 @@
         <v>20306</v>
       </c>
       <c r="C34" t="s">
-        <v>70</v>
-      </c>
-      <c r="E34"/>
+        <v>67</v>
+      </c>
+      <c r="E34" t="s">
+        <v>189</v>
+      </c>
       <c r="F34" t="s">
         <v>3</v>
       </c>
-      <c r="G34"/>
+      <c r="G34" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H34" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -1691,15 +1898,19 @@
         <v>20307</v>
       </c>
       <c r="C35" t="s">
-        <v>71</v>
-      </c>
-      <c r="E35"/>
+        <v>68</v>
+      </c>
+      <c r="E35" t="s">
+        <v>190</v>
+      </c>
       <c r="F35" t="s">
         <v>3</v>
       </c>
-      <c r="G35"/>
+      <c r="G35" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H35" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -1707,15 +1918,19 @@
         <v>20308</v>
       </c>
       <c r="C36" t="s">
-        <v>72</v>
-      </c>
-      <c r="E36"/>
+        <v>69</v>
+      </c>
+      <c r="E36" t="s">
+        <v>191</v>
+      </c>
       <c r="F36" t="s">
         <v>3</v>
       </c>
-      <c r="G36"/>
+      <c r="G36" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H36" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
@@ -1723,15 +1938,19 @@
         <v>20309</v>
       </c>
       <c r="C37" t="s">
-        <v>73</v>
-      </c>
-      <c r="E37"/>
+        <v>70</v>
+      </c>
+      <c r="E37" t="s">
+        <v>192</v>
+      </c>
       <c r="F37" t="s">
         <v>3</v>
       </c>
-      <c r="G37"/>
+      <c r="G37" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="H37" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
@@ -1739,15 +1958,19 @@
         <v>20310</v>
       </c>
       <c r="C38" t="s">
-        <v>74</v>
-      </c>
-      <c r="E38"/>
+        <v>71</v>
+      </c>
+      <c r="E38" t="s">
+        <v>193</v>
+      </c>
       <c r="F38" t="s">
         <v>3</v>
       </c>
-      <c r="G38"/>
+      <c r="G38" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H38" t="s">
-        <v>65</v>
+        <v>62</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -1755,15 +1978,19 @@
         <v>20401</v>
       </c>
       <c r="C39" t="s">
-        <v>75</v>
-      </c>
-      <c r="E39"/>
+        <v>72</v>
+      </c>
+      <c r="E39" t="s">
+        <v>165</v>
+      </c>
       <c r="F39" t="s">
         <v>3</v>
       </c>
-      <c r="G39"/>
+      <c r="G39" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H39" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -1771,15 +1998,19 @@
         <v>20402</v>
       </c>
       <c r="C40" t="s">
-        <v>77</v>
-      </c>
-      <c r="E40"/>
+        <v>74</v>
+      </c>
+      <c r="E40" t="s">
+        <v>176</v>
+      </c>
       <c r="F40" t="s">
         <v>3</v>
       </c>
-      <c r="G40"/>
+      <c r="G40" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H40" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
@@ -1787,15 +2018,19 @@
         <v>20403</v>
       </c>
       <c r="C41" t="s">
-        <v>78</v>
-      </c>
-      <c r="E41"/>
+        <v>75</v>
+      </c>
+      <c r="E41" t="s">
+        <v>177</v>
+      </c>
       <c r="F41" t="s">
         <v>3</v>
       </c>
-      <c r="G41"/>
+      <c r="G41" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H41" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
@@ -1803,15 +2038,19 @@
         <v>20404</v>
       </c>
       <c r="C42" t="s">
-        <v>79</v>
-      </c>
-      <c r="E42"/>
+        <v>76</v>
+      </c>
+      <c r="E42" t="s">
+        <v>178</v>
+      </c>
       <c r="F42" t="s">
         <v>3</v>
       </c>
-      <c r="G42"/>
+      <c r="G42" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H42" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
@@ -1819,15 +2058,19 @@
         <v>20405</v>
       </c>
       <c r="C43" t="s">
-        <v>80</v>
-      </c>
-      <c r="E43"/>
+        <v>77</v>
+      </c>
+      <c r="E43" t="s">
+        <v>179</v>
+      </c>
       <c r="F43" t="s">
         <v>3</v>
       </c>
-      <c r="G43"/>
+      <c r="G43" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H43" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -1835,15 +2078,19 @@
         <v>20406</v>
       </c>
       <c r="C44" t="s">
-        <v>81</v>
-      </c>
-      <c r="E44"/>
+        <v>78</v>
+      </c>
+      <c r="E44" t="s">
+        <v>180</v>
+      </c>
       <c r="F44" t="s">
         <v>3</v>
       </c>
-      <c r="G44"/>
+      <c r="G44" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H44" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
@@ -1851,15 +2098,19 @@
         <v>20407</v>
       </c>
       <c r="C45" t="s">
-        <v>82</v>
-      </c>
-      <c r="E45"/>
+        <v>79</v>
+      </c>
+      <c r="E45" t="s">
+        <v>181</v>
+      </c>
       <c r="F45" t="s">
         <v>3</v>
       </c>
-      <c r="G45"/>
+      <c r="G45" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H45" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
@@ -1867,15 +2118,19 @@
         <v>20408</v>
       </c>
       <c r="C46" t="s">
-        <v>83</v>
-      </c>
-      <c r="E46"/>
+        <v>80</v>
+      </c>
+      <c r="E46" t="s">
+        <v>182</v>
+      </c>
       <c r="F46" t="s">
         <v>3</v>
       </c>
-      <c r="G46"/>
+      <c r="G46" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H46" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
@@ -1883,15 +2138,19 @@
         <v>20409</v>
       </c>
       <c r="C47" t="s">
-        <v>84</v>
-      </c>
-      <c r="E47"/>
+        <v>81</v>
+      </c>
+      <c r="E47" t="s">
+        <v>183</v>
+      </c>
       <c r="F47" t="s">
         <v>3</v>
       </c>
-      <c r="G47"/>
+      <c r="G47" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="H47" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
@@ -1899,15 +2158,19 @@
         <v>20410</v>
       </c>
       <c r="C48" t="s">
-        <v>85</v>
-      </c>
-      <c r="E48"/>
+        <v>82</v>
+      </c>
+      <c r="E48" t="s">
+        <v>184</v>
+      </c>
       <c r="F48" t="s">
         <v>3</v>
       </c>
-      <c r="G48"/>
+      <c r="G48" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H48" t="s">
-        <v>76</v>
+        <v>73</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
@@ -1915,15 +2178,19 @@
         <v>20501</v>
       </c>
       <c r="C49" t="s">
-        <v>86</v>
-      </c>
-      <c r="E49"/>
+        <v>83</v>
+      </c>
+      <c r="E49" t="s">
+        <v>166</v>
+      </c>
       <c r="F49" t="s">
         <v>3</v>
       </c>
-      <c r="G49"/>
+      <c r="G49" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H49" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
@@ -1931,15 +2198,19 @@
         <v>20502</v>
       </c>
       <c r="C50" t="s">
-        <v>88</v>
-      </c>
-      <c r="E50"/>
+        <v>85</v>
+      </c>
+      <c r="E50" t="s">
+        <v>167</v>
+      </c>
       <c r="F50" t="s">
         <v>3</v>
       </c>
-      <c r="G50"/>
+      <c r="G50" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H50" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
@@ -1947,15 +2218,19 @@
         <v>20503</v>
       </c>
       <c r="C51" t="s">
-        <v>89</v>
-      </c>
-      <c r="E51"/>
+        <v>86</v>
+      </c>
+      <c r="E51" t="s">
+        <v>168</v>
+      </c>
       <c r="F51" t="s">
         <v>3</v>
       </c>
-      <c r="G51"/>
+      <c r="G51" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H51" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
@@ -1963,15 +2238,19 @@
         <v>20504</v>
       </c>
       <c r="C52" t="s">
-        <v>90</v>
-      </c>
-      <c r="E52"/>
+        <v>87</v>
+      </c>
+      <c r="E52" t="s">
+        <v>169</v>
+      </c>
       <c r="F52" t="s">
         <v>3</v>
       </c>
-      <c r="G52"/>
+      <c r="G52" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H52" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
@@ -1979,15 +2258,19 @@
         <v>20505</v>
       </c>
       <c r="C53" t="s">
-        <v>91</v>
-      </c>
-      <c r="E53"/>
+        <v>88</v>
+      </c>
+      <c r="E53" t="s">
+        <v>170</v>
+      </c>
       <c r="F53" t="s">
         <v>3</v>
       </c>
-      <c r="G53"/>
+      <c r="G53" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H53" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
@@ -1995,15 +2278,19 @@
         <v>20506</v>
       </c>
       <c r="C54" t="s">
-        <v>92</v>
-      </c>
-      <c r="E54"/>
+        <v>89</v>
+      </c>
+      <c r="E54" t="s">
+        <v>171</v>
+      </c>
       <c r="F54" t="s">
         <v>3</v>
       </c>
-      <c r="G54"/>
+      <c r="G54" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H54" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
@@ -2011,15 +2298,19 @@
         <v>20507</v>
       </c>
       <c r="C55" t="s">
-        <v>93</v>
-      </c>
-      <c r="E55"/>
+        <v>90</v>
+      </c>
+      <c r="E55" t="s">
+        <v>172</v>
+      </c>
       <c r="F55" t="s">
         <v>3</v>
       </c>
-      <c r="G55"/>
+      <c r="G55" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H55" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
@@ -2027,15 +2318,19 @@
         <v>20508</v>
       </c>
       <c r="C56" t="s">
-        <v>94</v>
-      </c>
-      <c r="E56"/>
+        <v>91</v>
+      </c>
+      <c r="E56" t="s">
+        <v>173</v>
+      </c>
       <c r="F56" t="s">
         <v>3</v>
       </c>
-      <c r="G56"/>
+      <c r="G56" s="18" t="s">
+        <v>32</v>
+      </c>
       <c r="H56" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.3">
@@ -2043,15 +2338,19 @@
         <v>20509</v>
       </c>
       <c r="C57" t="s">
-        <v>95</v>
-      </c>
-      <c r="E57"/>
+        <v>92</v>
+      </c>
+      <c r="E57" t="s">
+        <v>174</v>
+      </c>
       <c r="F57" t="s">
         <v>3</v>
       </c>
-      <c r="G57"/>
+      <c r="G57" s="18" t="s">
+        <v>36</v>
+      </c>
       <c r="H57" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
@@ -2059,15 +2358,19 @@
         <v>20510</v>
       </c>
       <c r="C58" t="s">
-        <v>96</v>
-      </c>
-      <c r="E58"/>
+        <v>93</v>
+      </c>
+      <c r="E58" t="s">
+        <v>175</v>
+      </c>
       <c r="F58" t="s">
         <v>3</v>
       </c>
-      <c r="G58"/>
+      <c r="G58" s="18" t="s">
+        <v>39</v>
+      </c>
       <c r="H58" t="s">
-        <v>87</v>
+        <v>84</v>
       </c>
     </row>
   </sheetData>
@@ -2102,7 +2405,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>97</v>
+        <v>94</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2156,11 +2459,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>98</v>
+        <v>95</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
-        <v>99</v>
+        <v>194</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -2174,11 +2477,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>100</v>
+        <v>96</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18" t="s">
-        <v>101</v>
+        <v>97</v>
       </c>
       <c r="L5" s="10"/>
     </row>
@@ -2187,10 +2490,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>102</v>
+        <v>98</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>103</v>
+        <v>99</v>
       </c>
       <c r="F6" s="2"/>
       <c r="L6" s="10"/>
@@ -2200,10 +2503,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>104</v>
+        <v>100</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>105</v>
+        <v>101</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -2211,10 +2514,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>106</v>
+        <v>102</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>107</v>
+        <v>103</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2241,7 +2544,7 @@
     <col min="2" max="2" width="10.125" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="15.875" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="11.75" bestFit="1" customWidth="1"/>
     <col min="8" max="10" width="18.5" style="2" customWidth="1"/>
@@ -2266,19 +2569,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>108</v>
+        <v>104</v>
       </c>
       <c r="D2" t="s">
-        <v>109</v>
+        <v>105</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>110</v>
+        <v>106</v>
       </c>
       <c r="G2" t="s">
-        <v>111</v>
+        <v>107</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2517,7 +2820,7 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="F15">
         <v>23</v>
@@ -2534,7 +2837,7 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="F16">
         <v>25</v>
@@ -2551,7 +2854,7 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="F17">
         <v>27</v>
@@ -2568,7 +2871,7 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>58</v>
+        <v>55</v>
       </c>
       <c r="F18">
         <v>29</v>
@@ -2585,7 +2888,7 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>59</v>
+        <v>56</v>
       </c>
       <c r="F19">
         <v>31</v>
@@ -2602,7 +2905,7 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>60</v>
+        <v>57</v>
       </c>
       <c r="F20">
         <v>33</v>
@@ -2619,7 +2922,7 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="F21">
         <v>35</v>
@@ -2636,7 +2939,7 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="F22">
         <v>37</v>
@@ -2653,7 +2956,7 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="F23">
         <v>39</v>
@@ -2670,7 +2973,7 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>64</v>
+        <v>61</v>
       </c>
       <c r="F24">
         <v>41</v>
@@ -2687,7 +2990,7 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>66</v>
+        <v>63</v>
       </c>
       <c r="F25">
         <v>43</v>
@@ -2704,7 +3007,7 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="F26">
         <v>45</v>
@@ -2721,7 +3024,7 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="F27">
         <v>47</v>
@@ -2738,7 +3041,7 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>69</v>
+        <v>66</v>
       </c>
       <c r="F28">
         <v>49</v>
@@ -2755,7 +3058,7 @@
         <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>70</v>
+        <v>67</v>
       </c>
       <c r="F29">
         <v>51</v>
@@ -2772,7 +3075,7 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>71</v>
+        <v>68</v>
       </c>
       <c r="F30">
         <v>53</v>
@@ -2789,7 +3092,7 @@
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>72</v>
+        <v>69</v>
       </c>
       <c r="F31">
         <v>55</v>
@@ -2806,7 +3109,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>73</v>
+        <v>70</v>
       </c>
       <c r="F32">
         <v>57</v>
@@ -2823,7 +3126,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>74</v>
+        <v>71</v>
       </c>
       <c r="F33">
         <v>59</v>
@@ -2840,7 +3143,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>75</v>
+        <v>72</v>
       </c>
       <c r="F34">
         <v>61</v>
@@ -2857,7 +3160,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>77</v>
+        <v>74</v>
       </c>
       <c r="F35">
         <v>63</v>
@@ -2874,7 +3177,7 @@
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>78</v>
+        <v>75</v>
       </c>
       <c r="F36">
         <v>65</v>
@@ -2891,7 +3194,7 @@
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>79</v>
+        <v>76</v>
       </c>
       <c r="F37">
         <v>67</v>
@@ -2908,7 +3211,7 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>80</v>
+        <v>77</v>
       </c>
       <c r="F38">
         <v>69</v>
@@ -2925,7 +3228,7 @@
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>81</v>
+        <v>78</v>
       </c>
       <c r="F39">
         <v>71</v>
@@ -2942,7 +3245,7 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>82</v>
+        <v>79</v>
       </c>
       <c r="F40">
         <v>73</v>
@@ -2959,7 +3262,7 @@
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>83</v>
+        <v>80</v>
       </c>
       <c r="F41">
         <v>75</v>
@@ -2976,7 +3279,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>84</v>
+        <v>81</v>
       </c>
       <c r="F42">
         <v>77</v>
@@ -2993,7 +3296,7 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="F43">
         <v>79</v>
@@ -3010,7 +3313,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>86</v>
+        <v>83</v>
       </c>
       <c r="F44">
         <v>81</v>
@@ -3027,7 +3330,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>88</v>
+        <v>85</v>
       </c>
       <c r="F45">
         <v>83</v>
@@ -3044,7 +3347,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>89</v>
+        <v>86</v>
       </c>
       <c r="F46">
         <v>85</v>
@@ -3061,7 +3364,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>90</v>
+        <v>87</v>
       </c>
       <c r="F47">
         <v>87</v>
@@ -3078,7 +3381,7 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>91</v>
+        <v>88</v>
       </c>
       <c r="F48">
         <v>89</v>
@@ -3095,7 +3398,7 @@
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>92</v>
+        <v>89</v>
       </c>
       <c r="F49">
         <v>91</v>
@@ -3112,7 +3415,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>93</v>
+        <v>90</v>
       </c>
       <c r="F50">
         <v>93</v>
@@ -3129,7 +3432,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>94</v>
+        <v>91</v>
       </c>
       <c r="F51">
         <v>95</v>
@@ -3146,7 +3449,7 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>95</v>
+        <v>92</v>
       </c>
       <c r="F52">
         <v>97</v>
@@ -3163,7 +3466,7 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>96</v>
+        <v>93</v>
       </c>
       <c r="F53">
         <v>99</v>
@@ -3198,7 +3501,7 @@
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>112</v>
+        <v>108</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>4</v>
@@ -3225,31 +3528,31 @@
         <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="G2" t="s">
+        <v>109</v>
+      </c>
+      <c r="H2" t="s">
+        <v>110</v>
+      </c>
+      <c r="I2" s="2" t="s">
+        <v>111</v>
+      </c>
+      <c r="J2" s="2" t="s">
+        <v>112</v>
+      </c>
+      <c r="K2" s="2" t="s">
         <v>113</v>
       </c>
-      <c r="H2" t="s">
+      <c r="L2" s="2" t="s">
         <v>114</v>
-      </c>
-      <c r="I2" s="2" t="s">
-        <v>115</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>116</v>
-      </c>
-      <c r="K2" s="2" t="s">
-        <v>117</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>118</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>14</v>
@@ -3270,13 +3573,13 @@
         <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>120</v>
+        <v>116</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>121</v>
+        <v>117</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>13</v>
@@ -3284,19 +3587,19 @@
     </row>
     <row r="4" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>123</v>
+        <v>119</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>124</v>
+        <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>148</v>
+        <v>144</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -3305,7 +3608,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J4" s="2">
         <v>500</v>
@@ -3319,19 +3622,19 @@
     </row>
     <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>126</v>
+        <v>122</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>127</v>
+        <v>123</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>151</v>
+        <v>147</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>128</v>
+        <v>124</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -3340,7 +3643,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J5" s="2">
         <v>500</v>
@@ -3354,19 +3657,19 @@
     </row>
     <row r="6" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>130</v>
+        <v>126</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>131</v>
+        <v>127</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>132</v>
+        <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>152</v>
+        <v>148</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>133</v>
+        <v>129</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -3375,7 +3678,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J6" s="2">
         <v>500</v>
@@ -3389,19 +3692,19 @@
     </row>
     <row r="7" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>134</v>
+        <v>130</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>135</v>
+        <v>131</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>136</v>
+        <v>132</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>153</v>
+        <v>149</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>137</v>
+        <v>133</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -3410,7 +3713,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>129</v>
+        <v>125</v>
       </c>
       <c r="J7" s="2">
         <v>500</v>
@@ -3451,7 +3754,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>138</v>
+        <v>134</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3467,28 +3770,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>135</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>136</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>137</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>138</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>141</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>143</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>144</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>145</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>146</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3497,7 +3800,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>119</v>
+        <v>115</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>13</v>
@@ -3526,7 +3829,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -3535,7 +3838,7 @@
         <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3549,7 +3852,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3558,7 +3861,7 @@
         <v>2001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -3572,7 +3875,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3581,7 +3884,7 @@
         <v>2001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
@@ -3595,7 +3898,7 @@
         <v>10004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -3604,7 +3907,7 @@
         <v>2001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G7" s="2">
         <v>150</v>
@@ -3618,7 +3921,7 @@
         <v>10005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D8" s="2">
         <v>5</v>
@@ -3627,7 +3930,7 @@
         <v>2001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G8" s="2">
         <v>200</v>
@@ -3641,7 +3944,7 @@
         <v>10006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D9" s="2">
         <v>6</v>
@@ -3650,7 +3953,7 @@
         <v>2001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G9" s="2">
         <v>250</v>
@@ -3664,7 +3967,7 @@
         <v>10007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D10" s="2">
         <v>7</v>
@@ -3673,7 +3976,7 @@
         <v>2001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G10" s="2">
         <v>300</v>
@@ -3687,7 +3990,7 @@
         <v>10008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D11" s="2">
         <v>8</v>
@@ -3696,7 +3999,7 @@
         <v>2001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G11" s="2">
         <v>350</v>
@@ -3710,7 +4013,7 @@
         <v>10009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D12" s="2">
         <v>9</v>
@@ -3719,7 +4022,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G12" s="2">
         <v>400</v>
@@ -3733,7 +4036,7 @@
         <v>10010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D13" s="2">
         <v>10</v>
@@ -3742,7 +4045,7 @@
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G13" s="2">
         <v>450</v>
@@ -3756,7 +4059,7 @@
         <v>10011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D14" s="2">
         <v>11</v>
@@ -3765,7 +4068,7 @@
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G14" s="2">
         <v>500</v>
@@ -3779,7 +4082,7 @@
         <v>10012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D15" s="2">
         <v>12</v>
@@ -3788,7 +4091,7 @@
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G15" s="2">
         <v>550</v>
@@ -3802,7 +4105,7 @@
         <v>10013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D16" s="2">
         <v>13</v>
@@ -3811,7 +4114,7 @@
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G16" s="2">
         <v>600</v>
@@ -3825,7 +4128,7 @@
         <v>10014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D17" s="2">
         <v>14</v>
@@ -3834,7 +4137,7 @@
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G17" s="2">
         <v>650</v>
@@ -3848,7 +4151,7 @@
         <v>10015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>122</v>
+        <v>118</v>
       </c>
       <c r="D18" s="2">
         <v>15</v>
@@ -3857,7 +4160,7 @@
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G18" s="2">
         <v>700</v>
@@ -3871,7 +4174,7 @@
         <v>20001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -3880,7 +4183,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -3894,7 +4197,7 @@
         <v>20002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -3903,7 +4206,7 @@
         <v>3001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G20" s="2">
         <v>50</v>
@@ -3917,7 +4220,7 @@
         <v>20003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -3926,7 +4229,7 @@
         <v>3001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G21" s="2">
         <v>75</v>
@@ -3940,7 +4243,7 @@
         <v>20004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -3949,7 +4252,7 @@
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G22" s="2">
         <v>100</v>
@@ -3963,7 +4266,7 @@
         <v>20005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -3972,7 +4275,7 @@
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G23" s="2">
         <v>125</v>
@@ -3986,7 +4289,7 @@
         <v>20006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -3995,7 +4298,7 @@
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G24" s="2">
         <v>150</v>
@@ -4009,7 +4312,7 @@
         <v>20007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D25" s="2">
         <v>7</v>
@@ -4018,7 +4321,7 @@
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G25" s="2">
         <v>175</v>
@@ -4032,7 +4335,7 @@
         <v>20008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D26" s="2">
         <v>8</v>
@@ -4041,7 +4344,7 @@
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G26" s="2">
         <v>200</v>
@@ -4055,7 +4358,7 @@
         <v>20009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D27" s="2">
         <v>9</v>
@@ -4064,7 +4367,7 @@
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G27" s="2">
         <v>225</v>
@@ -4078,7 +4381,7 @@
         <v>20010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
@@ -4087,7 +4390,7 @@
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G28" s="2">
         <v>250</v>
@@ -4101,7 +4404,7 @@
         <v>20011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D29" s="2">
         <v>11</v>
@@ -4110,7 +4413,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G29" s="2">
         <v>275</v>
@@ -4124,7 +4427,7 @@
         <v>20012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -4133,7 +4436,7 @@
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G30" s="2">
         <v>300</v>
@@ -4147,7 +4450,7 @@
         <v>20013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D31" s="2">
         <v>13</v>
@@ -4156,7 +4459,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G31" s="2">
         <v>325</v>
@@ -4170,7 +4473,7 @@
         <v>20014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D32" s="2">
         <v>14</v>
@@ -4179,7 +4482,7 @@
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G32" s="2">
         <v>350</v>
@@ -4193,7 +4496,7 @@
         <v>20015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D33" s="2">
         <v>15</v>
@@ -4202,7 +4505,7 @@
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G33" s="2">
         <v>375</v>
@@ -4216,7 +4519,7 @@
         <v>20016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
@@ -4225,7 +4528,7 @@
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G34" s="2">
         <v>400</v>
@@ -4239,7 +4542,7 @@
         <v>20017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D35" s="2">
         <v>17</v>
@@ -4248,7 +4551,7 @@
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G35" s="2">
         <v>425</v>
@@ -4262,7 +4565,7 @@
         <v>20018</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D36" s="2">
         <v>18</v>
@@ -4271,7 +4574,7 @@
         <v>3001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G36" s="2">
         <v>450</v>
@@ -4285,7 +4588,7 @@
         <v>20019</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D37" s="2">
         <v>19</v>
@@ -4294,7 +4597,7 @@
         <v>3001</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G37" s="2">
         <v>475</v>
@@ -4308,7 +4611,7 @@
         <v>20020</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>125</v>
+        <v>121</v>
       </c>
       <c r="D38" s="2">
         <v>20</v>
@@ -4317,7 +4620,7 @@
         <v>3001</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>147</v>
+        <v>143</v>
       </c>
       <c r="G38" s="2">
         <v>500</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="2"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="195">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="197">
   <si>
     <t>!Enum</t>
   </si>
@@ -433,9 +433,6 @@
     <t>DungeonStage</t>
   </si>
   <si>
-    <t>DungeonType</t>
-  </si>
-  <si>
     <t>Stage</t>
   </si>
   <si>
@@ -620,6 +617,18 @@
   </si>
   <si>
     <t>Image_Act_1</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonType</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>안개 어린 산길</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>산맥의 관문</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1133,7 +1142,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1375,7 +1384,7 @@
         <v>20101</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>30</v>
+        <v>195</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>31</v>
@@ -1440,7 +1449,7 @@
         <v>40</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>3</v>
@@ -1461,7 +1470,7 @@
         <v>41</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="F13" t="s">
         <v>3</v>
@@ -1481,7 +1490,7 @@
         <v>42</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="F14" t="s">
         <v>3</v>
@@ -1501,7 +1510,7 @@
         <v>43</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="F15" t="s">
         <v>3</v>
@@ -1521,7 +1530,7 @@
         <v>44</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>154</v>
+        <v>153</v>
       </c>
       <c r="F16" t="s">
         <v>3</v>
@@ -1541,7 +1550,7 @@
         <v>45</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>155</v>
+        <v>154</v>
       </c>
       <c r="F17" t="s">
         <v>3</v>
@@ -1558,10 +1567,10 @@
         <v>20110</v>
       </c>
       <c r="C18" t="s">
-        <v>46</v>
+        <v>196</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="F18" t="s">
         <v>3</v>
@@ -1641,7 +1650,7 @@
         <v>54</v>
       </c>
       <c r="E22" t="s">
-        <v>157</v>
+        <v>156</v>
       </c>
       <c r="F22" t="s">
         <v>3</v>
@@ -1661,7 +1670,7 @@
         <v>55</v>
       </c>
       <c r="E23" t="s">
-        <v>158</v>
+        <v>157</v>
       </c>
       <c r="F23" t="s">
         <v>3</v>
@@ -1681,7 +1690,7 @@
         <v>56</v>
       </c>
       <c r="E24" t="s">
-        <v>159</v>
+        <v>158</v>
       </c>
       <c r="F24" t="s">
         <v>3</v>
@@ -1701,7 +1710,7 @@
         <v>57</v>
       </c>
       <c r="E25" t="s">
-        <v>160</v>
+        <v>159</v>
       </c>
       <c r="F25" t="s">
         <v>3</v>
@@ -1721,7 +1730,7 @@
         <v>58</v>
       </c>
       <c r="E26" t="s">
-        <v>161</v>
+        <v>160</v>
       </c>
       <c r="F26" t="s">
         <v>3</v>
@@ -1741,7 +1750,7 @@
         <v>59</v>
       </c>
       <c r="E27" t="s">
-        <v>162</v>
+        <v>161</v>
       </c>
       <c r="F27" t="s">
         <v>3</v>
@@ -1761,7 +1770,7 @@
         <v>60</v>
       </c>
       <c r="E28" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
       <c r="F28" t="s">
         <v>3</v>
@@ -1781,7 +1790,7 @@
         <v>61</v>
       </c>
       <c r="E29" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
       <c r="F29" t="s">
         <v>3</v>
@@ -1801,7 +1810,7 @@
         <v>63</v>
       </c>
       <c r="E30" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="F30" t="s">
         <v>3</v>
@@ -1821,7 +1830,7 @@
         <v>64</v>
       </c>
       <c r="E31" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="F31" t="s">
         <v>3</v>
@@ -1841,7 +1850,7 @@
         <v>65</v>
       </c>
       <c r="E32" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
       <c r="F32" t="s">
         <v>3</v>
@@ -1861,7 +1870,7 @@
         <v>66</v>
       </c>
       <c r="E33" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
       <c r="F33" t="s">
         <v>3</v>
@@ -1881,7 +1890,7 @@
         <v>67</v>
       </c>
       <c r="E34" t="s">
-        <v>189</v>
+        <v>188</v>
       </c>
       <c r="F34" t="s">
         <v>3</v>
@@ -1901,7 +1910,7 @@
         <v>68</v>
       </c>
       <c r="E35" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="F35" t="s">
         <v>3</v>
@@ -1921,7 +1930,7 @@
         <v>69</v>
       </c>
       <c r="E36" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F36" t="s">
         <v>3</v>
@@ -1941,7 +1950,7 @@
         <v>70</v>
       </c>
       <c r="E37" t="s">
-        <v>192</v>
+        <v>191</v>
       </c>
       <c r="F37" t="s">
         <v>3</v>
@@ -1961,7 +1970,7 @@
         <v>71</v>
       </c>
       <c r="E38" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
       <c r="F38" t="s">
         <v>3</v>
@@ -1981,7 +1990,7 @@
         <v>72</v>
       </c>
       <c r="E39" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F39" t="s">
         <v>3</v>
@@ -2001,7 +2010,7 @@
         <v>74</v>
       </c>
       <c r="E40" t="s">
-        <v>176</v>
+        <v>175</v>
       </c>
       <c r="F40" t="s">
         <v>3</v>
@@ -2021,7 +2030,7 @@
         <v>75</v>
       </c>
       <c r="E41" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F41" t="s">
         <v>3</v>
@@ -2041,7 +2050,7 @@
         <v>76</v>
       </c>
       <c r="E42" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="F42" t="s">
         <v>3</v>
@@ -2061,7 +2070,7 @@
         <v>77</v>
       </c>
       <c r="E43" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F43" t="s">
         <v>3</v>
@@ -2081,7 +2090,7 @@
         <v>78</v>
       </c>
       <c r="E44" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="F44" t="s">
         <v>3</v>
@@ -2101,7 +2110,7 @@
         <v>79</v>
       </c>
       <c r="E45" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F45" t="s">
         <v>3</v>
@@ -2121,7 +2130,7 @@
         <v>80</v>
       </c>
       <c r="E46" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="F46" t="s">
         <v>3</v>
@@ -2141,7 +2150,7 @@
         <v>81</v>
       </c>
       <c r="E47" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="F47" t="s">
         <v>3</v>
@@ -2161,7 +2170,7 @@
         <v>82</v>
       </c>
       <c r="E48" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="F48" t="s">
         <v>3</v>
@@ -2181,7 +2190,7 @@
         <v>83</v>
       </c>
       <c r="E49" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="F49" t="s">
         <v>3</v>
@@ -2201,7 +2210,7 @@
         <v>85</v>
       </c>
       <c r="E50" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
       <c r="F50" t="s">
         <v>3</v>
@@ -2221,7 +2230,7 @@
         <v>86</v>
       </c>
       <c r="E51" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="F51" t="s">
         <v>3</v>
@@ -2241,7 +2250,7 @@
         <v>87</v>
       </c>
       <c r="E52" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="F52" t="s">
         <v>3</v>
@@ -2261,7 +2270,7 @@
         <v>88</v>
       </c>
       <c r="E53" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="F53" t="s">
         <v>3</v>
@@ -2281,7 +2290,7 @@
         <v>89</v>
       </c>
       <c r="E54" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
       <c r="F54" t="s">
         <v>3</v>
@@ -2301,7 +2310,7 @@
         <v>90</v>
       </c>
       <c r="E55" t="s">
-        <v>172</v>
+        <v>171</v>
       </c>
       <c r="F55" t="s">
         <v>3</v>
@@ -2321,7 +2330,7 @@
         <v>91</v>
       </c>
       <c r="E56" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
       <c r="F56" t="s">
         <v>3</v>
@@ -2341,7 +2350,7 @@
         <v>92</v>
       </c>
       <c r="E57" t="s">
-        <v>174</v>
+        <v>173</v>
       </c>
       <c r="F57" t="s">
         <v>3</v>
@@ -2361,7 +2370,7 @@
         <v>93</v>
       </c>
       <c r="E58" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
       <c r="F58" t="s">
         <v>3</v>
@@ -2463,7 +2472,7 @@
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
-        <v>194</v>
+        <v>193</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -2626,9 +2635,6 @@
       <c r="E4" t="s">
         <v>30</v>
       </c>
-      <c r="F4">
-        <v>1</v>
-      </c>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
@@ -2647,9 +2653,6 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="F5">
-        <v>3</v>
-      </c>
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2665,9 +2668,6 @@
       <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="F6">
-        <v>5</v>
-      </c>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2683,9 +2683,6 @@
       <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="F7">
-        <v>7</v>
-      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -2700,9 +2697,6 @@
       <c r="E8" t="s">
         <v>41</v>
       </c>
-      <c r="F8">
-        <v>9</v>
-      </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -2717,9 +2711,6 @@
       <c r="E9" t="s">
         <v>42</v>
       </c>
-      <c r="F9">
-        <v>11</v>
-      </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B10">
@@ -2734,9 +2725,6 @@
       <c r="E10" t="s">
         <v>43</v>
       </c>
-      <c r="F10">
-        <v>13</v>
-      </c>
       <c r="H10" s="10"/>
     </row>
     <row r="11" spans="1:11" x14ac:dyDescent="0.3">
@@ -2752,9 +2740,6 @@
       <c r="E11" t="s">
         <v>44</v>
       </c>
-      <c r="F11">
-        <v>15</v>
-      </c>
       <c r="H11" s="10"/>
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
@@ -2770,9 +2755,6 @@
       <c r="E12" t="s">
         <v>45</v>
       </c>
-      <c r="F12">
-        <v>17</v>
-      </c>
       <c r="H12" s="10"/>
     </row>
     <row r="13" spans="1:11" x14ac:dyDescent="0.3">
@@ -2789,7 +2771,7 @@
         <v>46</v>
       </c>
       <c r="F13">
-        <v>19</v>
+        <v>10</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2805,9 +2787,6 @@
       <c r="E14" t="s">
         <v>47</v>
       </c>
-      <c r="F14">
-        <v>21</v>
-      </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B15">
@@ -2822,9 +2801,6 @@
       <c r="E15" t="s">
         <v>50</v>
       </c>
-      <c r="F15">
-        <v>23</v>
-      </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B16">
@@ -2839,9 +2815,6 @@
       <c r="E16" t="s">
         <v>52</v>
       </c>
-      <c r="F16">
-        <v>25</v>
-      </c>
     </row>
     <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
@@ -2856,9 +2829,6 @@
       <c r="E17" t="s">
         <v>54</v>
       </c>
-      <c r="F17">
-        <v>27</v>
-      </c>
     </row>
     <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18">
@@ -2873,9 +2843,6 @@
       <c r="E18" t="s">
         <v>55</v>
       </c>
-      <c r="F18">
-        <v>29</v>
-      </c>
     </row>
     <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19">
@@ -2890,9 +2857,6 @@
       <c r="E19" t="s">
         <v>56</v>
       </c>
-      <c r="F19">
-        <v>31</v>
-      </c>
     </row>
     <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20">
@@ -2907,9 +2871,6 @@
       <c r="E20" t="s">
         <v>57</v>
       </c>
-      <c r="F20">
-        <v>33</v>
-      </c>
     </row>
     <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21">
@@ -2924,9 +2885,6 @@
       <c r="E21" t="s">
         <v>58</v>
       </c>
-      <c r="F21">
-        <v>35</v>
-      </c>
     </row>
     <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22">
@@ -2941,9 +2899,6 @@
       <c r="E22" t="s">
         <v>59</v>
       </c>
-      <c r="F22">
-        <v>37</v>
-      </c>
     </row>
     <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23">
@@ -2959,7 +2914,7 @@
         <v>60</v>
       </c>
       <c r="F23">
-        <v>39</v>
+        <v>30</v>
       </c>
     </row>
     <row r="24" spans="2:6" x14ac:dyDescent="0.3">
@@ -2975,9 +2930,6 @@
       <c r="E24" t="s">
         <v>61</v>
       </c>
-      <c r="F24">
-        <v>41</v>
-      </c>
     </row>
     <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25">
@@ -2992,9 +2944,6 @@
       <c r="E25" t="s">
         <v>63</v>
       </c>
-      <c r="F25">
-        <v>43</v>
-      </c>
     </row>
     <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26">
@@ -3009,9 +2958,6 @@
       <c r="E26" t="s">
         <v>64</v>
       </c>
-      <c r="F26">
-        <v>45</v>
-      </c>
     </row>
     <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27">
@@ -3026,9 +2972,6 @@
       <c r="E27" t="s">
         <v>65</v>
       </c>
-      <c r="F27">
-        <v>47</v>
-      </c>
     </row>
     <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28">
@@ -3043,9 +2986,6 @@
       <c r="E28" t="s">
         <v>66</v>
       </c>
-      <c r="F28">
-        <v>49</v>
-      </c>
     </row>
     <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29">
@@ -3060,9 +3000,6 @@
       <c r="E29" t="s">
         <v>67</v>
       </c>
-      <c r="F29">
-        <v>51</v>
-      </c>
     </row>
     <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30">
@@ -3077,9 +3014,6 @@
       <c r="E30" t="s">
         <v>68</v>
       </c>
-      <c r="F30">
-        <v>53</v>
-      </c>
     </row>
     <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31">
@@ -3094,9 +3028,6 @@
       <c r="E31" t="s">
         <v>69</v>
       </c>
-      <c r="F31">
-        <v>55</v>
-      </c>
     </row>
     <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32">
@@ -3111,9 +3042,6 @@
       <c r="E32" t="s">
         <v>70</v>
       </c>
-      <c r="F32">
-        <v>57</v>
-      </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B33">
@@ -3129,7 +3057,7 @@
         <v>71</v>
       </c>
       <c r="F33">
-        <v>59</v>
+        <v>50</v>
       </c>
     </row>
     <row r="34" spans="2:6" x14ac:dyDescent="0.3">
@@ -3145,9 +3073,6 @@
       <c r="E34" t="s">
         <v>72</v>
       </c>
-      <c r="F34">
-        <v>61</v>
-      </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B35">
@@ -3162,9 +3087,6 @@
       <c r="E35" t="s">
         <v>74</v>
       </c>
-      <c r="F35">
-        <v>63</v>
-      </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B36">
@@ -3179,9 +3101,6 @@
       <c r="E36" t="s">
         <v>75</v>
       </c>
-      <c r="F36">
-        <v>65</v>
-      </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B37">
@@ -3196,9 +3115,6 @@
       <c r="E37" t="s">
         <v>76</v>
       </c>
-      <c r="F37">
-        <v>67</v>
-      </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B38">
@@ -3213,9 +3129,6 @@
       <c r="E38" t="s">
         <v>77</v>
       </c>
-      <c r="F38">
-        <v>69</v>
-      </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B39">
@@ -3230,9 +3143,6 @@
       <c r="E39" t="s">
         <v>78</v>
       </c>
-      <c r="F39">
-        <v>71</v>
-      </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B40">
@@ -3247,9 +3157,6 @@
       <c r="E40" t="s">
         <v>79</v>
       </c>
-      <c r="F40">
-        <v>73</v>
-      </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B41">
@@ -3264,9 +3171,6 @@
       <c r="E41" t="s">
         <v>80</v>
       </c>
-      <c r="F41">
-        <v>75</v>
-      </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B42">
@@ -3281,9 +3185,6 @@
       <c r="E42" t="s">
         <v>81</v>
       </c>
-      <c r="F42">
-        <v>77</v>
-      </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B43">
@@ -3299,7 +3200,7 @@
         <v>82</v>
       </c>
       <c r="F43">
-        <v>79</v>
+        <v>70</v>
       </c>
     </row>
     <row r="44" spans="2:6" x14ac:dyDescent="0.3">
@@ -3315,9 +3216,6 @@
       <c r="E44" t="s">
         <v>83</v>
       </c>
-      <c r="F44">
-        <v>81</v>
-      </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B45">
@@ -3332,9 +3230,6 @@
       <c r="E45" t="s">
         <v>85</v>
       </c>
-      <c r="F45">
-        <v>83</v>
-      </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B46">
@@ -3349,9 +3244,6 @@
       <c r="E46" t="s">
         <v>86</v>
       </c>
-      <c r="F46">
-        <v>85</v>
-      </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B47">
@@ -3366,9 +3258,6 @@
       <c r="E47" t="s">
         <v>87</v>
       </c>
-      <c r="F47">
-        <v>87</v>
-      </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B48">
@@ -3383,9 +3272,6 @@
       <c r="E48" t="s">
         <v>88</v>
       </c>
-      <c r="F48">
-        <v>89</v>
-      </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B49">
@@ -3400,9 +3286,6 @@
       <c r="E49" t="s">
         <v>89</v>
       </c>
-      <c r="F49">
-        <v>91</v>
-      </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B50">
@@ -3417,9 +3300,6 @@
       <c r="E50" t="s">
         <v>90</v>
       </c>
-      <c r="F50">
-        <v>93</v>
-      </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B51">
@@ -3434,9 +3314,6 @@
       <c r="E51" t="s">
         <v>91</v>
       </c>
-      <c r="F51">
-        <v>95</v>
-      </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B52">
@@ -3451,9 +3328,6 @@
       <c r="E52" t="s">
         <v>92</v>
       </c>
-      <c r="F52">
-        <v>97</v>
-      </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B53">
@@ -3469,7 +3343,7 @@
         <v>93</v>
       </c>
       <c r="F53">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -3528,7 +3402,7 @@
         <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G2" t="s">
         <v>109</v>
@@ -3596,10 +3470,10 @@
         <v>120</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>144</v>
+        <v>143</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -3631,7 +3505,7 @@
         <v>123</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
       <c r="F5" s="2" t="s">
         <v>124</v>
@@ -3666,7 +3540,7 @@
         <v>128</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>148</v>
+        <v>147</v>
       </c>
       <c r="F6" s="2" t="s">
         <v>129</v>
@@ -3701,7 +3575,7 @@
         <v>132</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>149</v>
+        <v>148</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>133</v>
@@ -3770,28 +3644,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>194</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>135</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>136</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>137</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>138</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>139</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>140</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>141</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3838,7 +3712,7 @@
         <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3861,7 +3735,7 @@
         <v>2001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -3884,7 +3758,7 @@
         <v>2001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
@@ -3907,7 +3781,7 @@
         <v>2001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G7" s="2">
         <v>150</v>
@@ -3930,7 +3804,7 @@
         <v>2001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G8" s="2">
         <v>200</v>
@@ -3953,7 +3827,7 @@
         <v>2001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G9" s="2">
         <v>250</v>
@@ -3976,7 +3850,7 @@
         <v>2001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G10" s="2">
         <v>300</v>
@@ -3999,7 +3873,7 @@
         <v>2001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G11" s="2">
         <v>350</v>
@@ -4022,7 +3896,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G12" s="2">
         <v>400</v>
@@ -4045,7 +3919,7 @@
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G13" s="2">
         <v>450</v>
@@ -4068,7 +3942,7 @@
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G14" s="2">
         <v>500</v>
@@ -4091,7 +3965,7 @@
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G15" s="2">
         <v>550</v>
@@ -4114,7 +3988,7 @@
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G16" s="2">
         <v>600</v>
@@ -4137,7 +4011,7 @@
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G17" s="2">
         <v>650</v>
@@ -4160,7 +4034,7 @@
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G18" s="2">
         <v>700</v>
@@ -4183,7 +4057,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -4206,7 +4080,7 @@
         <v>3001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G20" s="2">
         <v>50</v>
@@ -4229,7 +4103,7 @@
         <v>3001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G21" s="2">
         <v>75</v>
@@ -4252,7 +4126,7 @@
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G22" s="2">
         <v>100</v>
@@ -4275,7 +4149,7 @@
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G23" s="2">
         <v>125</v>
@@ -4298,7 +4172,7 @@
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G24" s="2">
         <v>150</v>
@@ -4321,7 +4195,7 @@
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G25" s="2">
         <v>175</v>
@@ -4344,7 +4218,7 @@
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G26" s="2">
         <v>200</v>
@@ -4367,7 +4241,7 @@
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G27" s="2">
         <v>225</v>
@@ -4390,7 +4264,7 @@
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G28" s="2">
         <v>250</v>
@@ -4413,7 +4287,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G29" s="2">
         <v>275</v>
@@ -4436,7 +4310,7 @@
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G30" s="2">
         <v>300</v>
@@ -4459,7 +4333,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G31" s="2">
         <v>325</v>
@@ -4482,7 +4356,7 @@
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G32" s="2">
         <v>350</v>
@@ -4505,7 +4379,7 @@
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G33" s="2">
         <v>375</v>
@@ -4528,7 +4402,7 @@
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G34" s="2">
         <v>400</v>
@@ -4551,7 +4425,7 @@
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G35" s="2">
         <v>425</v>
@@ -4574,7 +4448,7 @@
         <v>3001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G36" s="2">
         <v>450</v>
@@ -4597,7 +4471,7 @@
         <v>3001</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G37" s="2">
         <v>475</v>
@@ -4620,7 +4494,7 @@
         <v>3001</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>143</v>
+        <v>142</v>
       </c>
       <c r="G38" s="2">
         <v>500</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -19,7 +19,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="197">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="510" uniqueCount="212">
   <si>
     <t>!Enum</t>
   </si>
@@ -144,30 +144,75 @@
     <t>붉은 안개 능선</t>
   </si>
   <si>
+    <t>Icon_Field_1-4</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-4</t>
+  </si>
+  <si>
     <t>버려진 채석장</t>
   </si>
   <si>
+    <t>Icon_Field_1-5</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-5</t>
+  </si>
+  <si>
     <t>산양의 벼랑</t>
   </si>
   <si>
+    <t>Icon_Field_1-6</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-6</t>
+  </si>
+  <si>
     <t>마른 계곡</t>
   </si>
   <si>
+    <t>Icon_Field_1-7</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-7</t>
+  </si>
+  <si>
     <t>안개 폭포</t>
   </si>
   <si>
+    <t>Icon_Field_1-8</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-8</t>
+  </si>
+  <si>
     <t>산정 제단</t>
   </si>
   <si>
+    <t>Icon_Field_1-9</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-9</t>
+  </si>
+  <si>
     <t>산맥의 관문</t>
   </si>
   <si>
+    <t>Icon_Field_1-10</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_1-10</t>
+  </si>
+  <si>
     <t>모래바람 언덕</t>
   </si>
   <si>
     <t>Icon_Field_2-1</t>
   </si>
   <si>
+    <t>MapPrefab_Field_2-1</t>
+  </si>
+  <si>
     <t>Sound_Act2</t>
   </si>
   <si>
@@ -177,138 +222,279 @@
     <t>Icon_Field_2-2</t>
   </si>
   <si>
+    <t>MapPrefab_Field_2-2</t>
+  </si>
+  <si>
     <t>뒤집힌 대상로</t>
   </si>
   <si>
     <t>Icon_Field_2-3</t>
   </si>
   <si>
+    <t>MapPrefab_Field_2-3</t>
+  </si>
+  <si>
     <t>붉은 사구</t>
   </si>
   <si>
+    <t>Icon_Field_2-4</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-4</t>
+  </si>
+  <si>
     <t>도적 야영지</t>
   </si>
   <si>
+    <t>Icon_Field_2-5</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-5</t>
+  </si>
+  <si>
     <t>유리모래 평원</t>
   </si>
   <si>
+    <t>Icon_Field_2-6</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-6</t>
+  </si>
+  <si>
     <t>침몰한 방주</t>
   </si>
   <si>
+    <t>Icon_Field_2-7</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-7</t>
+  </si>
+  <si>
     <t>전갈 둥지</t>
   </si>
   <si>
+    <t>Icon_Field_2-8</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-8</t>
+  </si>
+  <si>
     <t>사막의 무덤</t>
   </si>
   <si>
+    <t>Icon_Field_2-9</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-9</t>
+  </si>
+  <si>
     <t>사막의 관문</t>
   </si>
   <si>
+    <t>Icon_Field_2-10</t>
+  </si>
+  <si>
+    <t>MapPrefab_Field_2-10</t>
+  </si>
+  <si>
     <t>안개 낀 습지</t>
   </si>
   <si>
+    <t>Icon_Field_3-1</t>
+  </si>
+  <si>
     <t>Sound_Act3</t>
   </si>
   <si>
     <t>썩은 뿌리 숲</t>
   </si>
   <si>
+    <t>Icon_Field_3-2</t>
+  </si>
+  <si>
     <t>늪지 오두막</t>
   </si>
   <si>
+    <t>Icon_Field_3-3</t>
+  </si>
+  <si>
     <t>독버섯 군락</t>
   </si>
   <si>
+    <t>Icon_Field_3-4</t>
+  </si>
+  <si>
     <t>물귀신의 웅덩이</t>
   </si>
   <si>
+    <t>Icon_Field_3-5</t>
+  </si>
+  <si>
     <t>잠긴 신전</t>
   </si>
   <si>
+    <t>Icon_Field_3-6</t>
+  </si>
+  <si>
     <t>이끼 다리</t>
   </si>
   <si>
+    <t>Icon_Field_3-7</t>
+  </si>
+  <si>
     <t>검은 수렁</t>
   </si>
   <si>
+    <t>Icon_Field_3-8</t>
+  </si>
+  <si>
     <t>늪의 제단</t>
   </si>
   <si>
+    <t>Icon_Field_3-9</t>
+  </si>
+  <si>
     <t>늪지의 관문</t>
   </si>
   <si>
+    <t>Icon_Field_3-10</t>
+  </si>
+  <si>
     <t>눈보라 평원</t>
   </si>
   <si>
+    <t>Icon_Field_4-1</t>
+  </si>
+  <si>
     <t>Sound_Act4</t>
   </si>
   <si>
     <t>얼어붙은 호수</t>
   </si>
   <si>
+    <t>Icon_Field_4-2</t>
+  </si>
+  <si>
     <t>버려진 산장</t>
   </si>
   <si>
+    <t>Icon_Field_4-3</t>
+  </si>
+  <si>
     <t>서리 동굴</t>
   </si>
   <si>
+    <t>Icon_Field_4-4</t>
+  </si>
+  <si>
     <t>빙하 균열</t>
   </si>
   <si>
+    <t>Icon_Field_4-5</t>
+  </si>
+  <si>
     <t>늑대의 사냥터</t>
   </si>
   <si>
+    <t>Icon_Field_4-6</t>
+  </si>
+  <si>
     <t>얼음 첨탑</t>
   </si>
   <si>
+    <t>Icon_Field_4-7</t>
+  </si>
+  <si>
     <t>눈에 묻힌 마을</t>
   </si>
   <si>
+    <t>Icon_Field_4-8</t>
+  </si>
+  <si>
     <t>설원의 제단</t>
   </si>
   <si>
+    <t>Icon_Field_4-9</t>
+  </si>
+  <si>
     <t>설원의 관문</t>
   </si>
   <si>
+    <t>Icon_Field_4-10</t>
+  </si>
+  <si>
     <t>잿빛 구릉</t>
   </si>
   <si>
+    <t>Icon_Field_5-1</t>
+  </si>
+  <si>
     <t>Sound_Act5</t>
   </si>
   <si>
     <t>용암 협곡</t>
   </si>
   <si>
+    <t>Icon_Field_5-2</t>
+  </si>
+  <si>
     <t>무너진 대장간</t>
   </si>
   <si>
+    <t>Icon_Field_5-3</t>
+  </si>
+  <si>
     <t>화산재 평원</t>
   </si>
   <si>
+    <t>Icon_Field_5-4</t>
+  </si>
+  <si>
     <t>불의 제단</t>
   </si>
   <si>
+    <t>Icon_Field_5-5</t>
+  </si>
+  <si>
     <t>검은 연기 굴</t>
   </si>
   <si>
+    <t>Icon_Field_5-6</t>
+  </si>
+  <si>
     <t>끓는 호수</t>
   </si>
   <si>
+    <t>Icon_Field_5-7</t>
+  </si>
+  <si>
     <t>용의 둥지</t>
   </si>
   <si>
+    <t>Icon_Field_5-8</t>
+  </si>
+  <si>
     <t>화산 분화구</t>
   </si>
   <si>
+    <t>Icon_Field_5-9</t>
+  </si>
+  <si>
     <t>최후의 관문</t>
   </si>
   <si>
+    <t>Icon_Field_5-10</t>
+  </si>
+  <si>
     <t>Act</t>
   </si>
   <si>
     <t>Act I - 붉은 안개 산맥</t>
   </si>
   <si>
+    <t>Image_Act_1</t>
+  </si>
+  <si>
     <t>Act II - 핏빛 사막</t>
   </si>
   <si>
@@ -346,6 +532,9 @@
   </si>
   <si>
     <t>!EnumTable</t>
+  </si>
+  <si>
+    <t>Thumbnail</t>
   </si>
   <si>
     <t>DefaultEnterCount</t>
@@ -383,6 +572,12 @@
   <si>
     <t>고블린 고브의 황금 던전이다.
 골드를 주보상으로 얻을 수 있다.</t>
+  </si>
+  <si>
+    <t>Image_GoldDungeon</t>
+  </si>
+  <si>
+    <t>Ruby</t>
   </si>
   <si>
     <t>Rift</t>
@@ -399,9 +594,6 @@
     <t>Image_RiftDungeon</t>
   </si>
   <si>
-    <t>Ruby</t>
-  </si>
-  <si>
     <t>Labyrinth</t>
   </si>
   <si>
@@ -413,6 +605,9 @@
 (고급상자 전리품 획득)</t>
   </si>
   <si>
+    <t>Icon_LabyrinthDungeon</t>
+  </si>
+  <si>
     <t>Image_LabyrinthDungeon</t>
   </si>
   <si>
@@ -427,12 +622,18 @@
 (유물획득)</t>
   </si>
   <si>
+    <t>Icon_RuinsDungeon</t>
+  </si>
+  <si>
     <t>Image_RuinsDungeon</t>
   </si>
   <si>
     <t>DungeonStage</t>
   </si>
   <si>
+    <t>DungeonType</t>
+  </si>
+  <si>
     <t>Stage</t>
   </si>
   <si>
@@ -455,180 +656,13 @@
   </si>
   <si>
     <t>2001;2002;2003</t>
-  </si>
-  <si>
-    <t>Image_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Thumbnail</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_GoldDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_RiftDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_LabyrinthDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_RuinsDungeon</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_1-4</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-5</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-6</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-7</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-8</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-9</t>
-  </si>
-  <si>
-    <t>Icon_Field_1-10</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-4</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-5</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-6</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-7</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-8</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-9</t>
-  </si>
-  <si>
-    <t>Icon_Field_2-10</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_4-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_5-1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>Icon_Field_5-2</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-3</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-4</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-5</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-6</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-7</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-8</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-9</t>
-  </si>
-  <si>
-    <t>Icon_Field_5-10</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-2</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-3</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-4</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-5</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-6</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-7</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-8</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-9</t>
-  </si>
-  <si>
-    <t>Icon_Field_4-10</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-2</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-3</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-4</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-5</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-6</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-7</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-8</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-9</t>
-  </si>
-  <si>
-    <t>Icon_Field_3-10</t>
-  </si>
-  <si>
-    <t>Image_Act_1</t>
-    <phoneticPr fontId="8" type="noConversion"/>
-  </si>
-  <si>
-    <t>DungeonType</t>
-    <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
     <t>안개 어린 산길</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
   <si>
-    <t>산맥의 관문</t>
+    <t>무너진 초소</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1142,7 +1176,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1158,8 +1192,8 @@
     <col min="3" max="3" width="8.125" style="2" customWidth="1"/>
     <col min="4" max="4" width="71.125" style="2" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="17.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" style="2" customWidth="1"/>
-    <col min="7" max="16384" width="9" style="2"/>
+    <col min="6" max="7" width="9" style="2" customWidth="1"/>
+    <col min="8" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:4" s="4" customFormat="1" x14ac:dyDescent="0.3">
@@ -1189,7 +1223,7 @@
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
 </file>
 
@@ -1211,8 +1245,8 @@
     <col min="14" max="14" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="15" max="15" width="8.875" style="2" bestFit="1" customWidth="1"/>
     <col min="16" max="16" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="17" max="17" width="9" style="2" customWidth="1"/>
-    <col min="18" max="16384" width="9" style="2"/>
+    <col min="17" max="18" width="9" style="2" customWidth="1"/>
+    <col min="19" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:14" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -1384,7 +1418,7 @@
         <v>20101</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>195</v>
+        <v>210</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>31</v>
@@ -1404,7 +1438,7 @@
         <v>20102</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>34</v>
+        <v>211</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>35</v>
@@ -1413,7 +1447,7 @@
         <v>3</v>
       </c>
       <c r="G10" s="18" t="s">
-        <v>32</v>
+        <v>36</v>
       </c>
       <c r="H10" s="2" t="s">
         <v>33</v>
@@ -1434,7 +1468,7 @@
         <v>3</v>
       </c>
       <c r="G11" s="18" t="s">
-        <v>32</v>
+        <v>39</v>
       </c>
       <c r="H11" s="2" t="s">
         <v>33</v>
@@ -1449,13 +1483,13 @@
         <v>40</v>
       </c>
       <c r="E12" s="18" t="s">
-        <v>149</v>
+        <v>41</v>
       </c>
       <c r="F12" s="2" t="s">
         <v>3</v>
       </c>
       <c r="G12" s="18" t="s">
-        <v>32</v>
+        <v>42</v>
       </c>
       <c r="H12" s="2" t="s">
         <v>33</v>
@@ -1467,16 +1501,16 @@
         <v>20105</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>41</v>
+        <v>43</v>
       </c>
       <c r="E13" s="18" t="s">
-        <v>150</v>
+        <v>44</v>
       </c>
       <c r="F13" t="s">
         <v>3</v>
       </c>
       <c r="G13" s="18" t="s">
-        <v>32</v>
+        <v>45</v>
       </c>
       <c r="H13" t="s">
         <v>33</v>
@@ -1487,16 +1521,16 @@
         <v>20106</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>42</v>
+        <v>46</v>
       </c>
       <c r="E14" s="18" t="s">
-        <v>151</v>
+        <v>47</v>
       </c>
       <c r="F14" t="s">
         <v>3</v>
       </c>
       <c r="G14" s="18" t="s">
-        <v>32</v>
+        <v>48</v>
       </c>
       <c r="H14" t="s">
         <v>33</v>
@@ -1507,16 +1541,16 @@
         <v>20107</v>
       </c>
       <c r="C15" t="s">
-        <v>43</v>
+        <v>49</v>
       </c>
       <c r="E15" s="18" t="s">
-        <v>152</v>
+        <v>50</v>
       </c>
       <c r="F15" t="s">
         <v>3</v>
       </c>
       <c r="G15" s="18" t="s">
-        <v>32</v>
+        <v>51</v>
       </c>
       <c r="H15" t="s">
         <v>33</v>
@@ -1527,16 +1561,16 @@
         <v>20108</v>
       </c>
       <c r="C16" t="s">
-        <v>44</v>
+        <v>52</v>
       </c>
       <c r="E16" s="18" t="s">
-        <v>153</v>
+        <v>53</v>
       </c>
       <c r="F16" t="s">
         <v>3</v>
       </c>
       <c r="G16" s="18" t="s">
-        <v>32</v>
+        <v>54</v>
       </c>
       <c r="H16" t="s">
         <v>33</v>
@@ -1547,16 +1581,16 @@
         <v>20109</v>
       </c>
       <c r="C17" t="s">
-        <v>45</v>
+        <v>55</v>
       </c>
       <c r="E17" s="18" t="s">
-        <v>154</v>
+        <v>56</v>
       </c>
       <c r="F17" t="s">
         <v>3</v>
       </c>
       <c r="G17" s="18" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H17" t="s">
         <v>33</v>
@@ -1567,16 +1601,16 @@
         <v>20110</v>
       </c>
       <c r="C18" t="s">
-        <v>196</v>
+        <v>58</v>
       </c>
       <c r="E18" s="18" t="s">
-        <v>155</v>
+        <v>59</v>
       </c>
       <c r="F18" t="s">
         <v>3</v>
       </c>
       <c r="G18" s="18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H18" t="s">
         <v>33</v>
@@ -1587,19 +1621,19 @@
         <v>20201</v>
       </c>
       <c r="C19" t="s">
-        <v>47</v>
+        <v>61</v>
       </c>
       <c r="E19" t="s">
-        <v>48</v>
+        <v>62</v>
       </c>
       <c r="F19" t="s">
         <v>3</v>
       </c>
       <c r="G19" s="18" t="s">
-        <v>32</v>
+        <v>63</v>
       </c>
       <c r="H19" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="20" spans="2:8" x14ac:dyDescent="0.3">
@@ -1607,19 +1641,19 @@
         <v>20202</v>
       </c>
       <c r="C20" t="s">
-        <v>50</v>
+        <v>65</v>
       </c>
       <c r="E20" t="s">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="F20" t="s">
         <v>3</v>
       </c>
       <c r="G20" s="18" t="s">
-        <v>32</v>
+        <v>67</v>
       </c>
       <c r="H20" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="21" spans="2:8" x14ac:dyDescent="0.3">
@@ -1627,19 +1661,19 @@
         <v>20203</v>
       </c>
       <c r="C21" t="s">
-        <v>52</v>
+        <v>68</v>
       </c>
       <c r="E21" t="s">
-        <v>53</v>
+        <v>69</v>
       </c>
       <c r="F21" t="s">
         <v>3</v>
       </c>
       <c r="G21" s="18" t="s">
-        <v>32</v>
+        <v>70</v>
       </c>
       <c r="H21" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="22" spans="2:8" x14ac:dyDescent="0.3">
@@ -1647,19 +1681,19 @@
         <v>20204</v>
       </c>
       <c r="C22" t="s">
-        <v>54</v>
+        <v>71</v>
       </c>
       <c r="E22" t="s">
-        <v>156</v>
+        <v>72</v>
       </c>
       <c r="F22" t="s">
         <v>3</v>
       </c>
       <c r="G22" s="18" t="s">
-        <v>32</v>
+        <v>73</v>
       </c>
       <c r="H22" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="23" spans="2:8" x14ac:dyDescent="0.3">
@@ -1667,19 +1701,19 @@
         <v>20205</v>
       </c>
       <c r="C23" t="s">
-        <v>55</v>
+        <v>74</v>
       </c>
       <c r="E23" t="s">
-        <v>157</v>
+        <v>75</v>
       </c>
       <c r="F23" t="s">
         <v>3</v>
       </c>
       <c r="G23" s="18" t="s">
-        <v>32</v>
+        <v>76</v>
       </c>
       <c r="H23" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="24" spans="2:8" x14ac:dyDescent="0.3">
@@ -1687,19 +1721,19 @@
         <v>20206</v>
       </c>
       <c r="C24" t="s">
-        <v>56</v>
+        <v>77</v>
       </c>
       <c r="E24" t="s">
-        <v>158</v>
+        <v>78</v>
       </c>
       <c r="F24" t="s">
         <v>3</v>
       </c>
       <c r="G24" s="18" t="s">
-        <v>32</v>
+        <v>79</v>
       </c>
       <c r="H24" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="25" spans="2:8" x14ac:dyDescent="0.3">
@@ -1707,19 +1741,19 @@
         <v>20207</v>
       </c>
       <c r="C25" t="s">
-        <v>57</v>
+        <v>80</v>
       </c>
       <c r="E25" t="s">
-        <v>159</v>
+        <v>81</v>
       </c>
       <c r="F25" t="s">
         <v>3</v>
       </c>
       <c r="G25" s="18" t="s">
-        <v>32</v>
+        <v>82</v>
       </c>
       <c r="H25" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="26" spans="2:8" x14ac:dyDescent="0.3">
@@ -1727,19 +1761,19 @@
         <v>20208</v>
       </c>
       <c r="C26" t="s">
-        <v>58</v>
+        <v>83</v>
       </c>
       <c r="E26" t="s">
-        <v>160</v>
+        <v>84</v>
       </c>
       <c r="F26" t="s">
         <v>3</v>
       </c>
       <c r="G26" s="18" t="s">
-        <v>32</v>
+        <v>85</v>
       </c>
       <c r="H26" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="27" spans="2:8" x14ac:dyDescent="0.3">
@@ -1747,19 +1781,19 @@
         <v>20209</v>
       </c>
       <c r="C27" t="s">
-        <v>59</v>
+        <v>86</v>
       </c>
       <c r="E27" t="s">
-        <v>161</v>
+        <v>87</v>
       </c>
       <c r="F27" t="s">
         <v>3</v>
       </c>
       <c r="G27" s="18" t="s">
-        <v>36</v>
+        <v>88</v>
       </c>
       <c r="H27" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="28" spans="2:8" x14ac:dyDescent="0.3">
@@ -1767,19 +1801,19 @@
         <v>20210</v>
       </c>
       <c r="C28" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="E28" t="s">
-        <v>162</v>
+        <v>90</v>
       </c>
       <c r="F28" t="s">
         <v>3</v>
       </c>
       <c r="G28" s="18" t="s">
-        <v>39</v>
+        <v>91</v>
       </c>
       <c r="H28" t="s">
-        <v>49</v>
+        <v>64</v>
       </c>
     </row>
     <row r="29" spans="2:8" x14ac:dyDescent="0.3">
@@ -1787,10 +1821,10 @@
         <v>20301</v>
       </c>
       <c r="C29" t="s">
-        <v>61</v>
+        <v>92</v>
       </c>
       <c r="E29" t="s">
-        <v>163</v>
+        <v>93</v>
       </c>
       <c r="F29" t="s">
         <v>3</v>
@@ -1799,7 +1833,7 @@
         <v>32</v>
       </c>
       <c r="H29" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="30" spans="2:8" x14ac:dyDescent="0.3">
@@ -1807,10 +1841,10 @@
         <v>20302</v>
       </c>
       <c r="C30" t="s">
-        <v>63</v>
+        <v>95</v>
       </c>
       <c r="E30" t="s">
-        <v>184</v>
+        <v>96</v>
       </c>
       <c r="F30" t="s">
         <v>3</v>
@@ -1819,7 +1853,7 @@
         <v>32</v>
       </c>
       <c r="H30" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="31" spans="2:8" x14ac:dyDescent="0.3">
@@ -1827,10 +1861,10 @@
         <v>20303</v>
       </c>
       <c r="C31" t="s">
-        <v>64</v>
+        <v>97</v>
       </c>
       <c r="E31" t="s">
-        <v>185</v>
+        <v>98</v>
       </c>
       <c r="F31" t="s">
         <v>3</v>
@@ -1839,7 +1873,7 @@
         <v>32</v>
       </c>
       <c r="H31" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="32" spans="2:8" x14ac:dyDescent="0.3">
@@ -1847,10 +1881,10 @@
         <v>20304</v>
       </c>
       <c r="C32" t="s">
-        <v>65</v>
+        <v>99</v>
       </c>
       <c r="E32" t="s">
-        <v>186</v>
+        <v>100</v>
       </c>
       <c r="F32" t="s">
         <v>3</v>
@@ -1859,7 +1893,7 @@
         <v>32</v>
       </c>
       <c r="H32" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="33" spans="2:8" x14ac:dyDescent="0.3">
@@ -1867,10 +1901,10 @@
         <v>20305</v>
       </c>
       <c r="C33" t="s">
-        <v>66</v>
+        <v>101</v>
       </c>
       <c r="E33" t="s">
-        <v>187</v>
+        <v>102</v>
       </c>
       <c r="F33" t="s">
         <v>3</v>
@@ -1879,7 +1913,7 @@
         <v>32</v>
       </c>
       <c r="H33" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="34" spans="2:8" x14ac:dyDescent="0.3">
@@ -1887,10 +1921,10 @@
         <v>20306</v>
       </c>
       <c r="C34" t="s">
-        <v>67</v>
+        <v>103</v>
       </c>
       <c r="E34" t="s">
-        <v>188</v>
+        <v>104</v>
       </c>
       <c r="F34" t="s">
         <v>3</v>
@@ -1899,7 +1933,7 @@
         <v>32</v>
       </c>
       <c r="H34" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="35" spans="2:8" x14ac:dyDescent="0.3">
@@ -1907,10 +1941,10 @@
         <v>20307</v>
       </c>
       <c r="C35" t="s">
-        <v>68</v>
+        <v>105</v>
       </c>
       <c r="E35" t="s">
-        <v>189</v>
+        <v>106</v>
       </c>
       <c r="F35" t="s">
         <v>3</v>
@@ -1919,7 +1953,7 @@
         <v>32</v>
       </c>
       <c r="H35" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="36" spans="2:8" x14ac:dyDescent="0.3">
@@ -1927,10 +1961,10 @@
         <v>20308</v>
       </c>
       <c r="C36" t="s">
-        <v>69</v>
+        <v>107</v>
       </c>
       <c r="E36" t="s">
-        <v>190</v>
+        <v>108</v>
       </c>
       <c r="F36" t="s">
         <v>3</v>
@@ -1939,7 +1973,7 @@
         <v>32</v>
       </c>
       <c r="H36" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="37" spans="2:8" x14ac:dyDescent="0.3">
@@ -1947,19 +1981,19 @@
         <v>20309</v>
       </c>
       <c r="C37" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
       <c r="E37" t="s">
-        <v>191</v>
+        <v>110</v>
       </c>
       <c r="F37" t="s">
         <v>3</v>
       </c>
       <c r="G37" s="18" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H37" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="38" spans="2:8" x14ac:dyDescent="0.3">
@@ -1967,19 +2001,19 @@
         <v>20310</v>
       </c>
       <c r="C38" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="E38" t="s">
-        <v>192</v>
+        <v>112</v>
       </c>
       <c r="F38" t="s">
         <v>3</v>
       </c>
       <c r="G38" s="18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H38" t="s">
-        <v>62</v>
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="2:8" x14ac:dyDescent="0.3">
@@ -1987,10 +2021,10 @@
         <v>20401</v>
       </c>
       <c r="C39" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
       <c r="E39" t="s">
-        <v>164</v>
+        <v>114</v>
       </c>
       <c r="F39" t="s">
         <v>3</v>
@@ -1999,7 +2033,7 @@
         <v>32</v>
       </c>
       <c r="H39" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="40" spans="2:8" x14ac:dyDescent="0.3">
@@ -2007,10 +2041,10 @@
         <v>20402</v>
       </c>
       <c r="C40" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
       <c r="E40" t="s">
-        <v>175</v>
+        <v>117</v>
       </c>
       <c r="F40" t="s">
         <v>3</v>
@@ -2019,7 +2053,7 @@
         <v>32</v>
       </c>
       <c r="H40" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="41" spans="2:8" x14ac:dyDescent="0.3">
@@ -2027,10 +2061,10 @@
         <v>20403</v>
       </c>
       <c r="C41" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
       <c r="E41" t="s">
-        <v>176</v>
+        <v>119</v>
       </c>
       <c r="F41" t="s">
         <v>3</v>
@@ -2039,7 +2073,7 @@
         <v>32</v>
       </c>
       <c r="H41" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="42" spans="2:8" x14ac:dyDescent="0.3">
@@ -2047,10 +2081,10 @@
         <v>20404</v>
       </c>
       <c r="C42" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
       <c r="E42" t="s">
-        <v>177</v>
+        <v>121</v>
       </c>
       <c r="F42" t="s">
         <v>3</v>
@@ -2059,7 +2093,7 @@
         <v>32</v>
       </c>
       <c r="H42" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="43" spans="2:8" x14ac:dyDescent="0.3">
@@ -2067,10 +2101,10 @@
         <v>20405</v>
       </c>
       <c r="C43" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
       <c r="E43" t="s">
-        <v>178</v>
+        <v>123</v>
       </c>
       <c r="F43" t="s">
         <v>3</v>
@@ -2079,7 +2113,7 @@
         <v>32</v>
       </c>
       <c r="H43" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="44" spans="2:8" x14ac:dyDescent="0.3">
@@ -2087,10 +2121,10 @@
         <v>20406</v>
       </c>
       <c r="C44" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
       <c r="E44" t="s">
-        <v>179</v>
+        <v>125</v>
       </c>
       <c r="F44" t="s">
         <v>3</v>
@@ -2099,7 +2133,7 @@
         <v>32</v>
       </c>
       <c r="H44" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="45" spans="2:8" x14ac:dyDescent="0.3">
@@ -2107,10 +2141,10 @@
         <v>20407</v>
       </c>
       <c r="C45" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
       <c r="E45" t="s">
-        <v>180</v>
+        <v>127</v>
       </c>
       <c r="F45" t="s">
         <v>3</v>
@@ -2119,7 +2153,7 @@
         <v>32</v>
       </c>
       <c r="H45" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="46" spans="2:8" x14ac:dyDescent="0.3">
@@ -2127,10 +2161,10 @@
         <v>20408</v>
       </c>
       <c r="C46" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
       <c r="E46" t="s">
-        <v>181</v>
+        <v>129</v>
       </c>
       <c r="F46" t="s">
         <v>3</v>
@@ -2139,7 +2173,7 @@
         <v>32</v>
       </c>
       <c r="H46" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="47" spans="2:8" x14ac:dyDescent="0.3">
@@ -2147,19 +2181,19 @@
         <v>20409</v>
       </c>
       <c r="C47" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
       <c r="E47" t="s">
-        <v>182</v>
+        <v>131</v>
       </c>
       <c r="F47" t="s">
         <v>3</v>
       </c>
       <c r="G47" s="18" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H47" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="48" spans="2:8" x14ac:dyDescent="0.3">
@@ -2167,19 +2201,19 @@
         <v>20410</v>
       </c>
       <c r="C48" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="E48" t="s">
-        <v>183</v>
+        <v>133</v>
       </c>
       <c r="F48" t="s">
         <v>3</v>
       </c>
       <c r="G48" s="18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H48" t="s">
-        <v>73</v>
+        <v>115</v>
       </c>
     </row>
     <row r="49" spans="2:8" x14ac:dyDescent="0.3">
@@ -2187,10 +2221,10 @@
         <v>20501</v>
       </c>
       <c r="C49" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
       <c r="E49" t="s">
-        <v>165</v>
+        <v>135</v>
       </c>
       <c r="F49" t="s">
         <v>3</v>
@@ -2199,7 +2233,7 @@
         <v>32</v>
       </c>
       <c r="H49" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="50" spans="2:8" x14ac:dyDescent="0.3">
@@ -2207,10 +2241,10 @@
         <v>20502</v>
       </c>
       <c r="C50" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
       <c r="E50" t="s">
-        <v>166</v>
+        <v>138</v>
       </c>
       <c r="F50" t="s">
         <v>3</v>
@@ -2219,7 +2253,7 @@
         <v>32</v>
       </c>
       <c r="H50" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="51" spans="2:8" x14ac:dyDescent="0.3">
@@ -2227,10 +2261,10 @@
         <v>20503</v>
       </c>
       <c r="C51" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
       <c r="E51" t="s">
-        <v>167</v>
+        <v>140</v>
       </c>
       <c r="F51" t="s">
         <v>3</v>
@@ -2239,7 +2273,7 @@
         <v>32</v>
       </c>
       <c r="H51" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="52" spans="2:8" x14ac:dyDescent="0.3">
@@ -2247,10 +2281,10 @@
         <v>20504</v>
       </c>
       <c r="C52" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
       <c r="E52" t="s">
-        <v>168</v>
+        <v>142</v>
       </c>
       <c r="F52" t="s">
         <v>3</v>
@@ -2259,7 +2293,7 @@
         <v>32</v>
       </c>
       <c r="H52" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="53" spans="2:8" x14ac:dyDescent="0.3">
@@ -2267,10 +2301,10 @@
         <v>20505</v>
       </c>
       <c r="C53" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
       <c r="E53" t="s">
-        <v>169</v>
+        <v>144</v>
       </c>
       <c r="F53" t="s">
         <v>3</v>
@@ -2279,7 +2313,7 @@
         <v>32</v>
       </c>
       <c r="H53" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="54" spans="2:8" x14ac:dyDescent="0.3">
@@ -2287,10 +2321,10 @@
         <v>20506</v>
       </c>
       <c r="C54" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
       <c r="E54" t="s">
-        <v>170</v>
+        <v>146</v>
       </c>
       <c r="F54" t="s">
         <v>3</v>
@@ -2299,7 +2333,7 @@
         <v>32</v>
       </c>
       <c r="H54" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="55" spans="2:8" x14ac:dyDescent="0.3">
@@ -2307,10 +2341,10 @@
         <v>20507</v>
       </c>
       <c r="C55" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
       <c r="E55" t="s">
-        <v>171</v>
+        <v>148</v>
       </c>
       <c r="F55" t="s">
         <v>3</v>
@@ -2319,7 +2353,7 @@
         <v>32</v>
       </c>
       <c r="H55" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="56" spans="2:8" x14ac:dyDescent="0.3">
@@ -2327,10 +2361,10 @@
         <v>20508</v>
       </c>
       <c r="C56" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
       <c r="E56" t="s">
-        <v>172</v>
+        <v>150</v>
       </c>
       <c r="F56" t="s">
         <v>3</v>
@@ -2339,7 +2373,7 @@
         <v>32</v>
       </c>
       <c r="H56" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="57" spans="2:8" x14ac:dyDescent="0.3">
@@ -2347,19 +2381,19 @@
         <v>20509</v>
       </c>
       <c r="C57" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
       <c r="E57" t="s">
-        <v>173</v>
+        <v>152</v>
       </c>
       <c r="F57" t="s">
         <v>3</v>
       </c>
       <c r="G57" s="18" t="s">
-        <v>36</v>
+        <v>57</v>
       </c>
       <c r="H57" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
     <row r="58" spans="2:8" x14ac:dyDescent="0.3">
@@ -2367,25 +2401,25 @@
         <v>20510</v>
       </c>
       <c r="C58" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="E58" t="s">
-        <v>174</v>
+        <v>154</v>
       </c>
       <c r="F58" t="s">
         <v>3</v>
       </c>
       <c r="G58" s="18" t="s">
-        <v>39</v>
+        <v>60</v>
       </c>
       <c r="H58" t="s">
-        <v>84</v>
+        <v>136</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="8" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -2405,8 +2439,8 @@
     <col min="12" max="12" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="8.875" style="2" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="9" style="2" customWidth="1"/>
-    <col min="16" max="16384" width="9" style="2"/>
+    <col min="15" max="16" width="9" style="2" customWidth="1"/>
+    <col min="17" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2414,7 +2448,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="13" t="s">
-        <v>94</v>
+        <v>155</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2468,11 +2502,11 @@
         <v>1</v>
       </c>
       <c r="C4" s="18" t="s">
-        <v>95</v>
+        <v>156</v>
       </c>
       <c r="D4" s="18"/>
       <c r="E4" s="18" t="s">
-        <v>193</v>
+        <v>157</v>
       </c>
       <c r="G4" s="8"/>
       <c r="H4" s="8"/>
@@ -2486,11 +2520,11 @@
         <v>2</v>
       </c>
       <c r="C5" s="18" t="s">
-        <v>96</v>
+        <v>158</v>
       </c>
       <c r="D5" s="18"/>
       <c r="E5" s="18" t="s">
-        <v>97</v>
+        <v>159</v>
       </c>
       <c r="L5" s="10"/>
     </row>
@@ -2499,10 +2533,10 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>98</v>
+        <v>160</v>
       </c>
       <c r="E6" s="18" t="s">
-        <v>99</v>
+        <v>161</v>
       </c>
       <c r="F6" s="2"/>
       <c r="L6" s="10"/>
@@ -2512,10 +2546,10 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>100</v>
+        <v>162</v>
       </c>
       <c r="E7" s="18" t="s">
-        <v>101</v>
+        <v>163</v>
       </c>
     </row>
     <row r="8" spans="1:12" x14ac:dyDescent="0.3">
@@ -2523,10 +2557,10 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>102</v>
+        <v>164</v>
       </c>
       <c r="E8" s="18" t="s">
-        <v>103</v>
+        <v>165</v>
       </c>
     </row>
     <row r="10" spans="1:12" x14ac:dyDescent="0.3">
@@ -2560,8 +2594,8 @@
     <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="8.875" style="2" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="14" width="9" style="2" customWidth="1"/>
-    <col min="15" max="16384" width="9" style="2"/>
+    <col min="14" max="15" width="9" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -2578,19 +2612,19 @@
         <v>7</v>
       </c>
       <c r="C2" t="s">
-        <v>104</v>
+        <v>166</v>
       </c>
       <c r="D2" t="s">
-        <v>105</v>
+        <v>167</v>
       </c>
       <c r="E2" t="s">
         <v>8</v>
       </c>
       <c r="F2" t="s">
-        <v>106</v>
+        <v>168</v>
       </c>
       <c r="G2" t="s">
-        <v>107</v>
+        <v>169</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2653,6 +2687,9 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
+      <c r="G5">
+        <v>1</v>
+      </c>
       <c r="K5" s="10"/>
     </row>
     <row r="6" spans="1:11" x14ac:dyDescent="0.3">
@@ -2668,6 +2705,9 @@
       <c r="E6" t="s">
         <v>37</v>
       </c>
+      <c r="G6">
+        <v>2</v>
+      </c>
       <c r="K6" s="10"/>
     </row>
     <row r="7" spans="1:11" x14ac:dyDescent="0.3">
@@ -2683,6 +2723,9 @@
       <c r="E7" t="s">
         <v>40</v>
       </c>
+      <c r="G7">
+        <v>3</v>
+      </c>
     </row>
     <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -2695,7 +2738,10 @@
         <v>5</v>
       </c>
       <c r="E8" t="s">
-        <v>41</v>
+        <v>43</v>
+      </c>
+      <c r="G8">
+        <v>4</v>
       </c>
     </row>
     <row r="9" spans="1:11" x14ac:dyDescent="0.3">
@@ -2709,7 +2755,10 @@
         <v>6</v>
       </c>
       <c r="E9" t="s">
-        <v>42</v>
+        <v>46</v>
+      </c>
+      <c r="G9">
+        <v>5</v>
       </c>
     </row>
     <row r="10" spans="1:11" x14ac:dyDescent="0.3">
@@ -2723,7 +2772,10 @@
         <v>7</v>
       </c>
       <c r="E10" t="s">
-        <v>43</v>
+        <v>49</v>
+      </c>
+      <c r="G10">
+        <v>6</v>
       </c>
       <c r="H10" s="10"/>
     </row>
@@ -2738,7 +2790,10 @@
         <v>8</v>
       </c>
       <c r="E11" t="s">
-        <v>44</v>
+        <v>52</v>
+      </c>
+      <c r="G11">
+        <v>7</v>
       </c>
       <c r="H11" s="10"/>
     </row>
@@ -2753,7 +2808,10 @@
         <v>9</v>
       </c>
       <c r="E12" t="s">
-        <v>45</v>
+        <v>55</v>
+      </c>
+      <c r="G12">
+        <v>8</v>
       </c>
       <c r="H12" s="10"/>
     </row>
@@ -2768,10 +2826,13 @@
         <v>10</v>
       </c>
       <c r="E13" t="s">
-        <v>46</v>
+        <v>58</v>
       </c>
       <c r="F13">
         <v>10</v>
+      </c>
+      <c r="G13">
+        <v>9</v>
       </c>
     </row>
     <row r="14" spans="1:11" x14ac:dyDescent="0.3">
@@ -2785,7 +2846,10 @@
         <v>1</v>
       </c>
       <c r="E14" t="s">
-        <v>47</v>
+        <v>61</v>
+      </c>
+      <c r="G14">
+        <v>10</v>
       </c>
     </row>
     <row r="15" spans="1:11" x14ac:dyDescent="0.3">
@@ -2799,7 +2863,10 @@
         <v>2</v>
       </c>
       <c r="E15" t="s">
-        <v>50</v>
+        <v>65</v>
+      </c>
+      <c r="G15">
+        <v>11</v>
       </c>
     </row>
     <row r="16" spans="1:11" x14ac:dyDescent="0.3">
@@ -2813,10 +2880,13 @@
         <v>3</v>
       </c>
       <c r="E16" t="s">
-        <v>52</v>
-      </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+        <v>68</v>
+      </c>
+      <c r="G16">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>20204</v>
       </c>
@@ -2827,10 +2897,13 @@
         <v>4</v>
       </c>
       <c r="E17" t="s">
-        <v>54</v>
-      </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+        <v>71</v>
+      </c>
+      <c r="G17">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>20205</v>
       </c>
@@ -2841,10 +2914,13 @@
         <v>5</v>
       </c>
       <c r="E18" t="s">
-        <v>55</v>
-      </c>
-    </row>
-    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
+        <v>74</v>
+      </c>
+      <c r="G18">
+        <v>14</v>
+      </c>
+    </row>
+    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>20206</v>
       </c>
@@ -2855,10 +2931,13 @@
         <v>6</v>
       </c>
       <c r="E19" t="s">
-        <v>56</v>
-      </c>
-    </row>
-    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
+        <v>77</v>
+      </c>
+      <c r="G19">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>20207</v>
       </c>
@@ -2869,10 +2948,13 @@
         <v>7</v>
       </c>
       <c r="E20" t="s">
-        <v>57</v>
-      </c>
-    </row>
-    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
+        <v>80</v>
+      </c>
+      <c r="G20">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>20208</v>
       </c>
@@ -2883,10 +2965,13 @@
         <v>8</v>
       </c>
       <c r="E21" t="s">
-        <v>58</v>
-      </c>
-    </row>
-    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
+        <v>83</v>
+      </c>
+      <c r="G21">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20209</v>
       </c>
@@ -2897,10 +2982,13 @@
         <v>9</v>
       </c>
       <c r="E22" t="s">
-        <v>59</v>
-      </c>
-    </row>
-    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
+        <v>86</v>
+      </c>
+      <c r="G22">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>20210</v>
       </c>
@@ -2911,13 +2999,16 @@
         <v>10</v>
       </c>
       <c r="E23" t="s">
-        <v>60</v>
+        <v>89</v>
       </c>
       <c r="F23">
         <v>30</v>
       </c>
-    </row>
-    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G23">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>20301</v>
       </c>
@@ -2928,10 +3019,10 @@
         <v>1</v>
       </c>
       <c r="E24" t="s">
-        <v>61</v>
-      </c>
-    </row>
-    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>20302</v>
       </c>
@@ -2942,10 +3033,10 @@
         <v>2</v>
       </c>
       <c r="E25" t="s">
-        <v>63</v>
-      </c>
-    </row>
-    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>20303</v>
       </c>
@@ -2956,10 +3047,10 @@
         <v>3</v>
       </c>
       <c r="E26" t="s">
-        <v>64</v>
-      </c>
-    </row>
-    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
+        <v>97</v>
+      </c>
+    </row>
+    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>20304</v>
       </c>
@@ -2970,10 +3061,10 @@
         <v>4</v>
       </c>
       <c r="E27" t="s">
-        <v>65</v>
-      </c>
-    </row>
-    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
+        <v>99</v>
+      </c>
+    </row>
+    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>20305</v>
       </c>
@@ -2984,10 +3075,10 @@
         <v>5</v>
       </c>
       <c r="E28" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
+        <v>101</v>
+      </c>
+    </row>
+    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>20306</v>
       </c>
@@ -2998,10 +3089,10 @@
         <v>6</v>
       </c>
       <c r="E29" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
+        <v>103</v>
+      </c>
+    </row>
+    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>20307</v>
       </c>
@@ -3012,10 +3103,10 @@
         <v>7</v>
       </c>
       <c r="E30" t="s">
-        <v>68</v>
-      </c>
-    </row>
-    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>20308</v>
       </c>
@@ -3026,10 +3117,10 @@
         <v>8</v>
       </c>
       <c r="E31" t="s">
-        <v>69</v>
-      </c>
-    </row>
-    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
+        <v>107</v>
+      </c>
+    </row>
+    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>20309</v>
       </c>
@@ -3040,7 +3131,7 @@
         <v>9</v>
       </c>
       <c r="E32" t="s">
-        <v>70</v>
+        <v>109</v>
       </c>
     </row>
     <row r="33" spans="2:6" x14ac:dyDescent="0.3">
@@ -3054,7 +3145,7 @@
         <v>10</v>
       </c>
       <c r="E33" t="s">
-        <v>71</v>
+        <v>111</v>
       </c>
       <c r="F33">
         <v>50</v>
@@ -3071,7 +3162,7 @@
         <v>1</v>
       </c>
       <c r="E34" t="s">
-        <v>72</v>
+        <v>113</v>
       </c>
     </row>
     <row r="35" spans="2:6" x14ac:dyDescent="0.3">
@@ -3085,7 +3176,7 @@
         <v>2</v>
       </c>
       <c r="E35" t="s">
-        <v>74</v>
+        <v>116</v>
       </c>
     </row>
     <row r="36" spans="2:6" x14ac:dyDescent="0.3">
@@ -3099,7 +3190,7 @@
         <v>3</v>
       </c>
       <c r="E36" t="s">
-        <v>75</v>
+        <v>118</v>
       </c>
     </row>
     <row r="37" spans="2:6" x14ac:dyDescent="0.3">
@@ -3113,7 +3204,7 @@
         <v>4</v>
       </c>
       <c r="E37" t="s">
-        <v>76</v>
+        <v>120</v>
       </c>
     </row>
     <row r="38" spans="2:6" x14ac:dyDescent="0.3">
@@ -3127,7 +3218,7 @@
         <v>5</v>
       </c>
       <c r="E38" t="s">
-        <v>77</v>
+        <v>122</v>
       </c>
     </row>
     <row r="39" spans="2:6" x14ac:dyDescent="0.3">
@@ -3141,7 +3232,7 @@
         <v>6</v>
       </c>
       <c r="E39" t="s">
-        <v>78</v>
+        <v>124</v>
       </c>
     </row>
     <row r="40" spans="2:6" x14ac:dyDescent="0.3">
@@ -3155,7 +3246,7 @@
         <v>7</v>
       </c>
       <c r="E40" t="s">
-        <v>79</v>
+        <v>126</v>
       </c>
     </row>
     <row r="41" spans="2:6" x14ac:dyDescent="0.3">
@@ -3169,7 +3260,7 @@
         <v>8</v>
       </c>
       <c r="E41" t="s">
-        <v>80</v>
+        <v>128</v>
       </c>
     </row>
     <row r="42" spans="2:6" x14ac:dyDescent="0.3">
@@ -3183,7 +3274,7 @@
         <v>9</v>
       </c>
       <c r="E42" t="s">
-        <v>81</v>
+        <v>130</v>
       </c>
     </row>
     <row r="43" spans="2:6" x14ac:dyDescent="0.3">
@@ -3197,7 +3288,7 @@
         <v>10</v>
       </c>
       <c r="E43" t="s">
-        <v>82</v>
+        <v>132</v>
       </c>
       <c r="F43">
         <v>70</v>
@@ -3214,7 +3305,7 @@
         <v>1</v>
       </c>
       <c r="E44" t="s">
-        <v>83</v>
+        <v>134</v>
       </c>
     </row>
     <row r="45" spans="2:6" x14ac:dyDescent="0.3">
@@ -3228,7 +3319,7 @@
         <v>2</v>
       </c>
       <c r="E45" t="s">
-        <v>85</v>
+        <v>137</v>
       </c>
     </row>
     <row r="46" spans="2:6" x14ac:dyDescent="0.3">
@@ -3242,7 +3333,7 @@
         <v>3</v>
       </c>
       <c r="E46" t="s">
-        <v>86</v>
+        <v>139</v>
       </c>
     </row>
     <row r="47" spans="2:6" x14ac:dyDescent="0.3">
@@ -3256,7 +3347,7 @@
         <v>4</v>
       </c>
       <c r="E47" t="s">
-        <v>87</v>
+        <v>141</v>
       </c>
     </row>
     <row r="48" spans="2:6" x14ac:dyDescent="0.3">
@@ -3270,7 +3361,7 @@
         <v>5</v>
       </c>
       <c r="E48" t="s">
-        <v>88</v>
+        <v>143</v>
       </c>
     </row>
     <row r="49" spans="2:6" x14ac:dyDescent="0.3">
@@ -3284,7 +3375,7 @@
         <v>6</v>
       </c>
       <c r="E49" t="s">
-        <v>89</v>
+        <v>145</v>
       </c>
     </row>
     <row r="50" spans="2:6" x14ac:dyDescent="0.3">
@@ -3298,7 +3389,7 @@
         <v>7</v>
       </c>
       <c r="E50" t="s">
-        <v>90</v>
+        <v>147</v>
       </c>
     </row>
     <row r="51" spans="2:6" x14ac:dyDescent="0.3">
@@ -3312,7 +3403,7 @@
         <v>8</v>
       </c>
       <c r="E51" t="s">
-        <v>91</v>
+        <v>149</v>
       </c>
     </row>
     <row r="52" spans="2:6" x14ac:dyDescent="0.3">
@@ -3326,7 +3417,7 @@
         <v>9</v>
       </c>
       <c r="E52" t="s">
-        <v>92</v>
+        <v>151</v>
       </c>
     </row>
     <row r="53" spans="2:6" x14ac:dyDescent="0.3">
@@ -3340,7 +3431,7 @@
         <v>10</v>
       </c>
       <c r="E53" t="s">
-        <v>93</v>
+        <v>153</v>
       </c>
       <c r="F53">
         <v>100</v>
@@ -3369,13 +3460,13 @@
     <col min="10" max="10" width="11.25" style="2" bestFit="1" customWidth="1"/>
     <col min="11" max="11" width="20.25" style="2" bestFit="1" customWidth="1"/>
     <col min="12" max="12" width="16.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="9" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="13" max="14" width="9" style="2" customWidth="1"/>
+    <col min="15" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>108</v>
+        <v>170</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>4</v>
@@ -3402,31 +3493,31 @@
         <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>144</v>
+        <v>171</v>
       </c>
       <c r="G2" t="s">
-        <v>109</v>
+        <v>172</v>
       </c>
       <c r="H2" t="s">
-        <v>110</v>
+        <v>173</v>
       </c>
       <c r="I2" s="2" t="s">
-        <v>111</v>
+        <v>174</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>112</v>
+        <v>175</v>
       </c>
       <c r="K2" s="2" t="s">
-        <v>113</v>
+        <v>176</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>114</v>
+        <v>177</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>14</v>
@@ -3447,13 +3538,13 @@
         <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>116</v>
+        <v>179</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>117</v>
+        <v>180</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>13</v>
@@ -3461,19 +3552,19 @@
     </row>
     <row r="4" spans="1:12" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>119</v>
+        <v>182</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>120</v>
+        <v>183</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>145</v>
+        <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>143</v>
+        <v>184</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -3482,7 +3573,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="J4" s="2">
         <v>500</v>
@@ -3496,19 +3587,19 @@
     </row>
     <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>122</v>
+        <v>187</v>
       </c>
       <c r="D5" s="17" t="s">
-        <v>123</v>
+        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>146</v>
+        <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>124</v>
+        <v>189</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -3517,7 +3608,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="J5" s="2">
         <v>500</v>
@@ -3531,19 +3622,19 @@
     </row>
     <row r="6" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>126</v>
+        <v>190</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>127</v>
+        <v>191</v>
       </c>
       <c r="D6" s="17" t="s">
-        <v>128</v>
+        <v>192</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>147</v>
+        <v>193</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>129</v>
+        <v>194</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -3552,7 +3643,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="J6" s="2">
         <v>500</v>
@@ -3566,19 +3657,19 @@
     </row>
     <row r="7" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>130</v>
+        <v>195</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>131</v>
+        <v>196</v>
       </c>
       <c r="D7" s="17" t="s">
-        <v>132</v>
+        <v>197</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>148</v>
+        <v>198</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>133</v>
+        <v>199</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -3587,7 +3678,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>125</v>
+        <v>185</v>
       </c>
       <c r="J7" s="2">
         <v>500</v>
@@ -3619,8 +3710,8 @@
     <col min="7" max="8" width="14.375" style="2" customWidth="1"/>
     <col min="9" max="9" width="10.875" style="2" bestFit="1" customWidth="1"/>
     <col min="10" max="10" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="9" style="2" customWidth="1"/>
-    <col min="12" max="16384" width="9" style="2"/>
+    <col min="11" max="12" width="9" style="2" customWidth="1"/>
+    <col min="13" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
@@ -3628,7 +3719,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>134</v>
+        <v>200</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3644,28 +3735,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>194</v>
+        <v>201</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>135</v>
+        <v>202</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>136</v>
+        <v>203</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>137</v>
+        <v>204</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>138</v>
+        <v>205</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>139</v>
+        <v>206</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>140</v>
+        <v>207</v>
       </c>
       <c r="J2" s="2" t="s">
-        <v>141</v>
+        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3674,7 +3765,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="8" t="s">
-        <v>115</v>
+        <v>178</v>
       </c>
       <c r="D3" s="8" t="s">
         <v>13</v>
@@ -3703,7 +3794,7 @@
         <v>10001</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D4" s="2">
         <v>1</v>
@@ -3712,7 +3803,7 @@
         <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3726,7 +3817,7 @@
         <v>10002</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D5" s="2">
         <v>2</v>
@@ -3735,7 +3826,7 @@
         <v>2001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -3749,7 +3840,7 @@
         <v>10003</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D6" s="2">
         <v>3</v>
@@ -3758,7 +3849,7 @@
         <v>2001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
@@ -3772,7 +3863,7 @@
         <v>10004</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D7" s="2">
         <v>4</v>
@@ -3781,7 +3872,7 @@
         <v>2001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G7" s="2">
         <v>150</v>
@@ -3795,7 +3886,7 @@
         <v>10005</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D8" s="2">
         <v>5</v>
@@ -3804,7 +3895,7 @@
         <v>2001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G8" s="2">
         <v>200</v>
@@ -3818,7 +3909,7 @@
         <v>10006</v>
       </c>
       <c r="C9" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D9" s="2">
         <v>6</v>
@@ -3827,7 +3918,7 @@
         <v>2001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G9" s="2">
         <v>250</v>
@@ -3841,7 +3932,7 @@
         <v>10007</v>
       </c>
       <c r="C10" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D10" s="2">
         <v>7</v>
@@ -3850,7 +3941,7 @@
         <v>2001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G10" s="2">
         <v>300</v>
@@ -3864,7 +3955,7 @@
         <v>10008</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D11" s="2">
         <v>8</v>
@@ -3873,7 +3964,7 @@
         <v>2001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G11" s="2">
         <v>350</v>
@@ -3887,7 +3978,7 @@
         <v>10009</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D12" s="2">
         <v>9</v>
@@ -3896,7 +3987,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G12" s="2">
         <v>400</v>
@@ -3910,7 +4001,7 @@
         <v>10010</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D13" s="2">
         <v>10</v>
@@ -3919,7 +4010,7 @@
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G13" s="2">
         <v>450</v>
@@ -3933,7 +4024,7 @@
         <v>10011</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D14" s="2">
         <v>11</v>
@@ -3942,7 +4033,7 @@
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G14" s="2">
         <v>500</v>
@@ -3956,7 +4047,7 @@
         <v>10012</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D15" s="2">
         <v>12</v>
@@ -3965,7 +4056,7 @@
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G15" s="2">
         <v>550</v>
@@ -3979,7 +4070,7 @@
         <v>10013</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D16" s="2">
         <v>13</v>
@@ -3988,7 +4079,7 @@
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G16" s="2">
         <v>600</v>
@@ -4002,7 +4093,7 @@
         <v>10014</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D17" s="2">
         <v>14</v>
@@ -4011,7 +4102,7 @@
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G17" s="2">
         <v>650</v>
@@ -4025,7 +4116,7 @@
         <v>10015</v>
       </c>
       <c r="C18" s="2" t="s">
-        <v>118</v>
+        <v>181</v>
       </c>
       <c r="D18" s="2">
         <v>15</v>
@@ -4034,7 +4125,7 @@
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G18" s="2">
         <v>700</v>
@@ -4048,7 +4139,7 @@
         <v>20001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -4057,7 +4148,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -4071,7 +4162,7 @@
         <v>20002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -4080,7 +4171,7 @@
         <v>3001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G20" s="2">
         <v>50</v>
@@ -4094,7 +4185,7 @@
         <v>20003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -4103,7 +4194,7 @@
         <v>3001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G21" s="2">
         <v>75</v>
@@ -4117,7 +4208,7 @@
         <v>20004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -4126,7 +4217,7 @@
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G22" s="2">
         <v>100</v>
@@ -4140,7 +4231,7 @@
         <v>20005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -4149,7 +4240,7 @@
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G23" s="2">
         <v>125</v>
@@ -4163,7 +4254,7 @@
         <v>20006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -4172,7 +4263,7 @@
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G24" s="2">
         <v>150</v>
@@ -4186,7 +4277,7 @@
         <v>20007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D25" s="2">
         <v>7</v>
@@ -4195,7 +4286,7 @@
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G25" s="2">
         <v>175</v>
@@ -4209,7 +4300,7 @@
         <v>20008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D26" s="2">
         <v>8</v>
@@ -4218,7 +4309,7 @@
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G26" s="2">
         <v>200</v>
@@ -4232,7 +4323,7 @@
         <v>20009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D27" s="2">
         <v>9</v>
@@ -4241,7 +4332,7 @@
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G27" s="2">
         <v>225</v>
@@ -4255,7 +4346,7 @@
         <v>20010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
@@ -4264,7 +4355,7 @@
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G28" s="2">
         <v>250</v>
@@ -4278,7 +4369,7 @@
         <v>20011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D29" s="2">
         <v>11</v>
@@ -4287,7 +4378,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G29" s="2">
         <v>275</v>
@@ -4301,7 +4392,7 @@
         <v>20012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -4310,7 +4401,7 @@
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G30" s="2">
         <v>300</v>
@@ -4324,7 +4415,7 @@
         <v>20013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D31" s="2">
         <v>13</v>
@@ -4333,7 +4424,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G31" s="2">
         <v>325</v>
@@ -4347,7 +4438,7 @@
         <v>20014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D32" s="2">
         <v>14</v>
@@ -4356,7 +4447,7 @@
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G32" s="2">
         <v>350</v>
@@ -4370,7 +4461,7 @@
         <v>20015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D33" s="2">
         <v>15</v>
@@ -4379,7 +4470,7 @@
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G33" s="2">
         <v>375</v>
@@ -4393,7 +4484,7 @@
         <v>20016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
@@ -4402,7 +4493,7 @@
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G34" s="2">
         <v>400</v>
@@ -4416,7 +4507,7 @@
         <v>20017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D35" s="2">
         <v>17</v>
@@ -4425,7 +4516,7 @@
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G35" s="2">
         <v>425</v>
@@ -4439,7 +4530,7 @@
         <v>20018</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D36" s="2">
         <v>18</v>
@@ -4448,7 +4539,7 @@
         <v>3001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G36" s="2">
         <v>450</v>
@@ -4462,7 +4553,7 @@
         <v>20019</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D37" s="2">
         <v>19</v>
@@ -4471,7 +4562,7 @@
         <v>3001</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G37" s="2">
         <v>475</v>
@@ -4485,7 +4576,7 @@
         <v>20020</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>121</v>
+        <v>186</v>
       </c>
       <c r="D38" s="2">
         <v>20</v>
@@ -4494,7 +4585,7 @@
         <v>3001</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>142</v>
+        <v>209</v>
       </c>
       <c r="G38" s="2">
         <v>500</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="1"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="4"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -567,9 +567,6 @@
     <t>Gold</t>
   </si>
   <si>
-    <t>고블린의 보물창고</t>
-  </si>
-  <si>
     <t>고블린 고브의 황금 던전이다.
 골드를 주보상으로 얻을 수 있다.</t>
   </si>
@@ -581,9 +578,6 @@
   </si>
   <si>
     <t>Rift</t>
-  </si>
-  <si>
-    <t>심연의 균열</t>
   </si>
   <si>
     <t>끊임없는 연속 스폰
@@ -634,9 +628,6 @@
     <t>DungeonType</t>
   </si>
   <si>
-    <t>Stage</t>
-  </si>
-  <si>
     <t>MapID</t>
   </si>
   <si>
@@ -663,6 +654,18 @@
   </si>
   <si>
     <t>무너진 초소</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>Stage</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>심연의 균열</t>
+    <phoneticPr fontId="8" type="noConversion"/>
+  </si>
+  <si>
+    <t>고블린의 보물창고</t>
     <phoneticPr fontId="8" type="noConversion"/>
   </si>
 </sst>
@@ -1176,7 +1179,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1418,7 +1421,7 @@
         <v>20101</v>
       </c>
       <c r="C9" s="18" t="s">
-        <v>210</v>
+        <v>207</v>
       </c>
       <c r="E9" s="18" t="s">
         <v>31</v>
@@ -1438,7 +1441,7 @@
         <v>20102</v>
       </c>
       <c r="C10" s="18" t="s">
-        <v>211</v>
+        <v>208</v>
       </c>
       <c r="E10" s="18" t="s">
         <v>35</v>
@@ -3555,16 +3558,16 @@
         <v>181</v>
       </c>
       <c r="C4" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="D4" s="17" t="s">
         <v>182</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>183</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>184</v>
+        <v>183</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -3573,7 +3576,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J4" s="2">
         <v>500</v>
@@ -3587,19 +3590,19 @@
     </row>
     <row r="5" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
+        <v>185</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D5" s="17" t="s">
         <v>186</v>
-      </c>
-      <c r="C5" s="2" t="s">
-        <v>187</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>188</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -3608,7 +3611,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J5" s="2">
         <v>500</v>
@@ -3622,19 +3625,19 @@
     </row>
     <row r="6" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>189</v>
+      </c>
+      <c r="D6" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="C6" s="2" t="s">
+      <c r="E6" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="17" t="s">
+      <c r="F6" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="E6" s="2" t="s">
-        <v>193</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -3643,7 +3646,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J6" s="2">
         <v>500</v>
@@ -3657,19 +3660,19 @@
     </row>
     <row r="7" spans="1:12" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="17" t="s">
         <v>195</v>
       </c>
-      <c r="C7" s="2" t="s">
+      <c r="E7" s="2" t="s">
         <v>196</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>197</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>198</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>199</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -3678,7 +3681,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="J7" s="2">
         <v>500</v>
@@ -3719,7 +3722,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="16" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3735,28 +3738,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>209</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>203</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>204</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="J2" s="2" t="s">
         <v>205</v>
-      </c>
-      <c r="H2" s="8" t="s">
-        <v>206</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>207</v>
-      </c>
-      <c r="J2" s="2" t="s">
-        <v>208</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -3803,7 +3806,7 @@
         <v>2001</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G4" s="2">
         <v>1</v>
@@ -3826,7 +3829,7 @@
         <v>2001</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G5" s="2">
         <v>50</v>
@@ -3849,7 +3852,7 @@
         <v>2001</v>
       </c>
       <c r="F6" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G6" s="2">
         <v>100</v>
@@ -3872,7 +3875,7 @@
         <v>2001</v>
       </c>
       <c r="F7" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G7" s="2">
         <v>150</v>
@@ -3895,7 +3898,7 @@
         <v>2001</v>
       </c>
       <c r="F8" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G8" s="2">
         <v>200</v>
@@ -3918,7 +3921,7 @@
         <v>2001</v>
       </c>
       <c r="F9" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G9" s="2">
         <v>250</v>
@@ -3941,7 +3944,7 @@
         <v>2001</v>
       </c>
       <c r="F10" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G10" s="2">
         <v>300</v>
@@ -3964,7 +3967,7 @@
         <v>2001</v>
       </c>
       <c r="F11" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G11" s="2">
         <v>350</v>
@@ -3987,7 +3990,7 @@
         <v>2001</v>
       </c>
       <c r="F12" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G12" s="2">
         <v>400</v>
@@ -4010,7 +4013,7 @@
         <v>2001</v>
       </c>
       <c r="F13" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G13" s="2">
         <v>450</v>
@@ -4033,7 +4036,7 @@
         <v>2001</v>
       </c>
       <c r="F14" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G14" s="2">
         <v>500</v>
@@ -4056,7 +4059,7 @@
         <v>2001</v>
       </c>
       <c r="F15" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G15" s="2">
         <v>550</v>
@@ -4079,7 +4082,7 @@
         <v>2001</v>
       </c>
       <c r="F16" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G16" s="2">
         <v>600</v>
@@ -4102,7 +4105,7 @@
         <v>2001</v>
       </c>
       <c r="F17" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G17" s="2">
         <v>650</v>
@@ -4125,7 +4128,7 @@
         <v>2001</v>
       </c>
       <c r="F18" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G18" s="2">
         <v>700</v>
@@ -4139,7 +4142,7 @@
         <v>20001</v>
       </c>
       <c r="C19" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D19" s="2">
         <v>1</v>
@@ -4148,7 +4151,7 @@
         <v>3001</v>
       </c>
       <c r="F19" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G19" s="2">
         <v>1</v>
@@ -4162,7 +4165,7 @@
         <v>20002</v>
       </c>
       <c r="C20" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D20" s="2">
         <v>2</v>
@@ -4171,7 +4174,7 @@
         <v>3001</v>
       </c>
       <c r="F20" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G20" s="2">
         <v>50</v>
@@ -4185,7 +4188,7 @@
         <v>20003</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D21" s="2">
         <v>3</v>
@@ -4194,7 +4197,7 @@
         <v>3001</v>
       </c>
       <c r="F21" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G21" s="2">
         <v>75</v>
@@ -4208,7 +4211,7 @@
         <v>20004</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D22" s="2">
         <v>4</v>
@@ -4217,7 +4220,7 @@
         <v>3001</v>
       </c>
       <c r="F22" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G22" s="2">
         <v>100</v>
@@ -4231,7 +4234,7 @@
         <v>20005</v>
       </c>
       <c r="C23" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D23" s="2">
         <v>5</v>
@@ -4240,7 +4243,7 @@
         <v>3001</v>
       </c>
       <c r="F23" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G23" s="2">
         <v>125</v>
@@ -4254,7 +4257,7 @@
         <v>20006</v>
       </c>
       <c r="C24" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D24" s="2">
         <v>6</v>
@@ -4263,7 +4266,7 @@
         <v>3001</v>
       </c>
       <c r="F24" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G24" s="2">
         <v>150</v>
@@ -4277,7 +4280,7 @@
         <v>20007</v>
       </c>
       <c r="C25" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D25" s="2">
         <v>7</v>
@@ -4286,7 +4289,7 @@
         <v>3001</v>
       </c>
       <c r="F25" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G25" s="2">
         <v>175</v>
@@ -4300,7 +4303,7 @@
         <v>20008</v>
       </c>
       <c r="C26" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D26" s="2">
         <v>8</v>
@@ -4309,7 +4312,7 @@
         <v>3001</v>
       </c>
       <c r="F26" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G26" s="2">
         <v>200</v>
@@ -4323,7 +4326,7 @@
         <v>20009</v>
       </c>
       <c r="C27" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D27" s="2">
         <v>9</v>
@@ -4332,7 +4335,7 @@
         <v>3001</v>
       </c>
       <c r="F27" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G27" s="2">
         <v>225</v>
@@ -4346,7 +4349,7 @@
         <v>20010</v>
       </c>
       <c r="C28" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D28" s="2">
         <v>10</v>
@@ -4355,7 +4358,7 @@
         <v>3001</v>
       </c>
       <c r="F28" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G28" s="2">
         <v>250</v>
@@ -4369,7 +4372,7 @@
         <v>20011</v>
       </c>
       <c r="C29" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D29" s="2">
         <v>11</v>
@@ -4378,7 +4381,7 @@
         <v>3001</v>
       </c>
       <c r="F29" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G29" s="2">
         <v>275</v>
@@ -4392,7 +4395,7 @@
         <v>20012</v>
       </c>
       <c r="C30" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D30" s="2">
         <v>12</v>
@@ -4401,7 +4404,7 @@
         <v>3001</v>
       </c>
       <c r="F30" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G30" s="2">
         <v>300</v>
@@ -4415,7 +4418,7 @@
         <v>20013</v>
       </c>
       <c r="C31" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D31" s="2">
         <v>13</v>
@@ -4424,7 +4427,7 @@
         <v>3001</v>
       </c>
       <c r="F31" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G31" s="2">
         <v>325</v>
@@ -4438,7 +4441,7 @@
         <v>20014</v>
       </c>
       <c r="C32" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D32" s="2">
         <v>14</v>
@@ -4447,7 +4450,7 @@
         <v>3001</v>
       </c>
       <c r="F32" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G32" s="2">
         <v>350</v>
@@ -4461,7 +4464,7 @@
         <v>20015</v>
       </c>
       <c r="C33" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D33" s="2">
         <v>15</v>
@@ -4470,7 +4473,7 @@
         <v>3001</v>
       </c>
       <c r="F33" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G33" s="2">
         <v>375</v>
@@ -4484,7 +4487,7 @@
         <v>20016</v>
       </c>
       <c r="C34" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D34" s="2">
         <v>16</v>
@@ -4493,7 +4496,7 @@
         <v>3001</v>
       </c>
       <c r="F34" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G34" s="2">
         <v>400</v>
@@ -4507,7 +4510,7 @@
         <v>20017</v>
       </c>
       <c r="C35" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D35" s="2">
         <v>17</v>
@@ -4516,7 +4519,7 @@
         <v>3001</v>
       </c>
       <c r="F35" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G35" s="2">
         <v>425</v>
@@ -4530,7 +4533,7 @@
         <v>20018</v>
       </c>
       <c r="C36" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D36" s="2">
         <v>18</v>
@@ -4539,7 +4542,7 @@
         <v>3001</v>
       </c>
       <c r="F36" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G36" s="2">
         <v>450</v>
@@ -4553,7 +4556,7 @@
         <v>20019</v>
       </c>
       <c r="C37" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D37" s="2">
         <v>19</v>
@@ -4562,7 +4565,7 @@
         <v>3001</v>
       </c>
       <c r="F37" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G37" s="2">
         <v>475</v>
@@ -4576,7 +4579,7 @@
         <v>20020</v>
       </c>
       <c r="C38" s="2" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="D38" s="2">
         <v>20</v>
@@ -4585,7 +4588,7 @@
         <v>3001</v>
       </c>
       <c r="F38" s="2" t="s">
-        <v>209</v>
+        <v>206</v>
       </c>
       <c r="G38" s="2">
         <v>500</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" activeTab="8"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="6" activeTab="11"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -16,13 +16,16 @@
     <sheet name="#RiftDungeon" sheetId="7" r:id="rId7"/>
     <sheet name="#RiftSkill" sheetId="8" r:id="rId8"/>
     <sheet name="#LabyrinthDungeon" sheetId="9" r:id="rId9"/>
+    <sheet name="#RuinsDungeon" sheetId="10" r:id="rId10"/>
+    <sheet name="#RuinsCorePhase" sheetId="11" r:id="rId11"/>
+    <sheet name="#RuinsHazard" sheetId="12" r:id="rId12"/>
   </sheets>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="554" uniqueCount="239">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="293">
   <si>
     <t>!Enum</t>
   </si>
@@ -602,11 +605,6 @@
     <t>망자의 미궁</t>
   </si>
   <si>
-    <t>탈출형 기믹
-왼쪽에서 즉사기가 다가오고 상자획득 및 몬스터 전투 후 탈출
-(고급상자 전리품 획득)</t>
-  </si>
-  <si>
     <t>Icon_LabyrinthDungeon</t>
   </si>
   <si>
@@ -616,11 +614,6 @@
     <t>고대의 유적</t>
   </si>
   <si>
-    <t>샌드백
-유적이 등장하고 내가 부순다 페이스마다 함정 발동
-(유물획득)</t>
-  </si>
-  <si>
     <t>Icon_RuinsDungeon</t>
   </si>
   <si>
@@ -694,55 +687,47 @@
   </si>
   <si>
     <t>Ruins</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Icon_RuinsDungeon</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Labyrinth</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Icon_LabyrinthDungeon</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>MapPrefab_LabyrinthDungeon_1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>MapPrefab_RuinsDungeon_1</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Sound_RuinsDungeon</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>LabyrinthDungeon</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Stage</t>
-    <phoneticPr fontId="12" type="noConversion"/>
-  </si>
-  <si>
-    <t>ChestRewardGroupID</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>RewardGroupID</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>ClearRewardGroupID</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>Sound_LabyrinthDungeon</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>FireDelay</t>
@@ -755,11 +740,204 @@
   </si>
   <si>
     <t>5001;5002;5003;5004;5005;5006;5007;5008;5009;5010;5011;5012</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
     <t>5001;5002;5003;5004;5005;5006;5007;5008;5009;5010;5011;5012</t>
-    <phoneticPr fontId="12" type="noConversion"/>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>탈출형 던전 다가오는 불의 장막을 피해 위쪽 탈출구로 이동</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>유적 방어시스템 무력화 후 보물 획득</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>MonsterSpawnGroupIDs</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>RuinsDungeon</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChestRewardGroupIDs</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>RuinsHazardType</t>
+  </si>
+  <si>
+    <t>HorizontalLine</t>
+  </si>
+  <si>
+    <t>공격 영역 전체 가로줄</t>
+  </si>
+  <si>
+    <t>PointCircle</t>
+  </si>
+  <si>
+    <t>지점 원형</t>
+  </si>
+  <si>
+    <t>PointDonut</t>
+  </si>
+  <si>
+    <t>지점 도넛</t>
+  </si>
+  <si>
+    <t>TargetCircle</t>
+  </si>
+  <si>
+    <t>유저 위치 낙뢰</t>
+  </si>
+  <si>
+    <t>MapPrefab_RuinsDungeon_01</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>CorePhaseGroupID</t>
+  </si>
+  <si>
+    <t>6001;6002;6003</t>
+  </si>
+  <si>
+    <t>RuinsCorePhase</t>
+  </si>
+  <si>
+    <t>GroupID</t>
+  </si>
+  <si>
+    <t>PhaseOrder</t>
+  </si>
+  <si>
+    <t>HpThreshold</t>
+  </si>
+  <si>
+    <t>SpawnGroupIndex</t>
+  </si>
+  <si>
+    <t>HazardIDs</t>
+  </si>
+  <si>
+    <t>1;2</t>
+  </si>
+  <si>
+    <t>3;4;5</t>
+  </si>
+  <si>
+    <t>2;5;4</t>
+  </si>
+  <si>
+    <t>3;5;2;4</t>
+  </si>
+  <si>
+    <t>RuinsHazard</t>
+  </si>
+  <si>
+    <t>HazardType</t>
+  </si>
+  <si>
+    <t>Count</t>
+  </si>
+  <si>
+    <t>Radius</t>
+  </si>
+  <si>
+    <t>InnerRadius</t>
+  </si>
+  <si>
+    <t>WarnTime</t>
+  </si>
+  <si>
+    <t>RepeatInterval</t>
+  </si>
+  <si>
+    <t>PointGroup</t>
+  </si>
+  <si>
+    <t>DamageEffectID</t>
+  </si>
+  <si>
+    <t>AfterDelay</t>
+  </si>
+  <si>
+    <t>!RuinsHazardType</t>
+  </si>
+  <si>
+    <t>!SkillEffect</t>
+  </si>
+  <si>
+    <t>가로줄 3개</t>
+  </si>
+  <si>
+    <t>SE_Ruins_Hazard_Damage</t>
+  </si>
+  <si>
+    <t>낙뢰 3연타</t>
+  </si>
+  <si>
+    <t>가로줄 5개</t>
+  </si>
+  <si>
+    <t>8201;8202;8203</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>8211;8211;8212;8213;8213</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>DungeonChestGrade</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>일반</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Advanced</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>고급</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Premium</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>최고급</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>ChestGrade</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>!DungeonChestGrade</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>Premium</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>NormalChestRewardGroupID</t>
+    <phoneticPr fontId="13" type="noConversion"/>
+  </si>
+  <si>
+    <t>AdvancedChestRewardGroupID</t>
+  </si>
+  <si>
+    <t>PremiumChestRewardGroupID</t>
   </si>
 </sst>
 </file>
@@ -769,12 +947,20 @@
   <numFmts count="1">
     <numFmt numFmtId="176" formatCode="mm&quot;월&quot;\ dd&quot;일&quot;"/>
   </numFmts>
-  <fonts count="15" x14ac:knownFonts="1">
+  <fonts count="16" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="맑은 고딕"/>
       <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="맑은 고딕"/>
+      <family val="2"/>
+      <charset val="129"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -976,12 +1162,12 @@
   </borders>
   <cellStyleXfs count="3">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="0">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="25">
+  <cellXfs count="26">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="2" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -995,60 +1181,63 @@
     <xf numFmtId="0" fontId="0" fillId="2" borderId="3" xfId="0" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
-    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1"/>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="2" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" xfId="2"/>
-    <xf numFmtId="0" fontId="9" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" xfId="2"/>
+    <xf numFmtId="0" fontId="10" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="15" fillId="2" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="6" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="3" borderId="5" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment vertical="center"/>
-    </xf>
     <xf numFmtId="176" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="49" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="3" borderId="1" xfId="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
   </cellXfs>
@@ -1330,7 +1519,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:D4"/>
+  <dimension ref="A1:D15"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="1" bestFit="1" customWidth="1"/>
@@ -1366,10 +1555,1074 @@
         <v>4</v>
       </c>
     </row>
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A6" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B6" s="2" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B7" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>242</v>
+      </c>
+    </row>
+    <row r="8" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B8" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>244</v>
+      </c>
+    </row>
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B9" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C9" s="2" t="s">
+        <v>246</v>
+      </c>
+    </row>
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B10" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="C10" s="2" t="s">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="A12" s="1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>280</v>
+      </c>
+    </row>
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B13" s="2" t="s">
+        <v>281</v>
+      </c>
+      <c r="C13" s="2" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B14" s="2" t="s">
+        <v>283</v>
+      </c>
+      <c r="C14" s="2" t="s">
+        <v>284</v>
+      </c>
+    </row>
+    <row r="15" spans="1:4" x14ac:dyDescent="0.3">
+      <c r="B15" s="2" t="s">
+        <v>285</v>
+      </c>
+      <c r="C15" s="2" t="s">
+        <v>286</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>238</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>226</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>237</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>232</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>239</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>250</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>287</v>
+      </c>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>288</v>
+      </c>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>4001</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E4" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F4" s="2">
+        <v>1</v>
+      </c>
+      <c r="G4" s="2">
+        <v>3</v>
+      </c>
+      <c r="H4" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I4" s="2">
+        <v>1</v>
+      </c>
+      <c r="J4" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>4002</v>
+      </c>
+      <c r="C5" s="2">
+        <v>2</v>
+      </c>
+      <c r="D5" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E5" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F5" s="2">
+        <v>40</v>
+      </c>
+      <c r="G5" s="2">
+        <v>3</v>
+      </c>
+      <c r="H5" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I5" s="2">
+        <v>1</v>
+      </c>
+      <c r="J5" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>4003</v>
+      </c>
+      <c r="C6" s="2">
+        <v>3</v>
+      </c>
+      <c r="D6" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E6" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F6" s="2">
+        <v>80</v>
+      </c>
+      <c r="G6" s="2">
+        <v>3</v>
+      </c>
+      <c r="H6" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I6" s="2">
+        <v>1</v>
+      </c>
+      <c r="J6" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4004</v>
+      </c>
+      <c r="C7" s="2">
+        <v>4</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E7" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F7" s="2">
+        <v>120</v>
+      </c>
+      <c r="G7" s="2">
+        <v>3</v>
+      </c>
+      <c r="H7" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I7" s="2">
+        <v>1</v>
+      </c>
+      <c r="J7" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>4005</v>
+      </c>
+      <c r="C8" s="2">
+        <v>5</v>
+      </c>
+      <c r="D8" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E8" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F8" s="2">
+        <v>160</v>
+      </c>
+      <c r="G8" s="2">
+        <v>3</v>
+      </c>
+      <c r="H8" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I8" s="2">
+        <v>1</v>
+      </c>
+      <c r="J8" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B9" s="2">
+        <v>4006</v>
+      </c>
+      <c r="C9" s="2">
+        <v>6</v>
+      </c>
+      <c r="D9" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E9" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F9" s="2">
+        <v>200</v>
+      </c>
+      <c r="G9" s="2">
+        <v>3</v>
+      </c>
+      <c r="H9" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I9" s="2">
+        <v>1</v>
+      </c>
+      <c r="J9" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B10" s="2">
+        <v>4007</v>
+      </c>
+      <c r="C10" s="2">
+        <v>7</v>
+      </c>
+      <c r="D10" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E10" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F10" s="2">
+        <v>240</v>
+      </c>
+      <c r="G10" s="2">
+        <v>3</v>
+      </c>
+      <c r="H10" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I10" s="2">
+        <v>1</v>
+      </c>
+      <c r="J10" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B11" s="2">
+        <v>4008</v>
+      </c>
+      <c r="C11" s="2">
+        <v>8</v>
+      </c>
+      <c r="D11" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E11" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F11" s="2">
+        <v>280</v>
+      </c>
+      <c r="G11" s="2">
+        <v>3</v>
+      </c>
+      <c r="H11" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I11" s="2">
+        <v>1</v>
+      </c>
+      <c r="J11" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B12" s="2">
+        <v>4009</v>
+      </c>
+      <c r="C12" s="2">
+        <v>9</v>
+      </c>
+      <c r="D12" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E12" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F12" s="2">
+        <v>320</v>
+      </c>
+      <c r="G12" s="2">
+        <v>3</v>
+      </c>
+      <c r="H12" s="2" t="s">
+        <v>278</v>
+      </c>
+      <c r="I12" s="2">
+        <v>1</v>
+      </c>
+      <c r="J12" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B13" s="2">
+        <v>4010</v>
+      </c>
+      <c r="C13" s="2">
+        <v>10</v>
+      </c>
+      <c r="D13" s="2">
+        <v>4001</v>
+      </c>
+      <c r="E13" s="24" t="s">
+        <v>251</v>
+      </c>
+      <c r="F13" s="2">
+        <v>360</v>
+      </c>
+      <c r="G13" s="2">
+        <v>5</v>
+      </c>
+      <c r="H13" s="2" t="s">
+        <v>279</v>
+      </c>
+      <c r="I13" s="2">
+        <v>1</v>
+      </c>
+      <c r="J13" s="2" t="s">
+        <v>289</v>
+      </c>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="24"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E15" s="24"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E16" s="24"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="24"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="24"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="24"/>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="24"/>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="24"/>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E22" s="24"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="24"/>
+      <c r="J23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:J23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>252</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>253</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>254</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>255</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>256</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>257</v>
+      </c>
+      <c r="H2" s="8"/>
+      <c r="I2" s="8"/>
+      <c r="J2" s="8"/>
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="H3" s="8"/>
+      <c r="I3" s="8"/>
+      <c r="J3" s="8"/>
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2">
+        <v>1</v>
+      </c>
+      <c r="D4" s="2">
+        <v>1</v>
+      </c>
+      <c r="E4" s="24">
+        <v>1</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0</v>
+      </c>
+      <c r="G4" s="2" t="s">
+        <v>258</v>
+      </c>
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2">
+        <v>1</v>
+      </c>
+      <c r="D5" s="2">
+        <v>2</v>
+      </c>
+      <c r="E5" s="24">
+        <v>0.75</v>
+      </c>
+      <c r="F5" s="2">
+        <v>3</v>
+      </c>
+      <c r="G5" s="2" t="s">
+        <v>259</v>
+      </c>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2">
+        <v>1</v>
+      </c>
+      <c r="D6" s="2">
+        <v>3</v>
+      </c>
+      <c r="E6" s="24">
+        <v>0.5</v>
+      </c>
+      <c r="F6" s="2">
+        <v>0</v>
+      </c>
+      <c r="G6" s="2" t="s">
+        <v>260</v>
+      </c>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2">
+        <v>1</v>
+      </c>
+      <c r="D7" s="2">
+        <v>4</v>
+      </c>
+      <c r="E7" s="24">
+        <v>0.25</v>
+      </c>
+      <c r="F7" s="2">
+        <v>0</v>
+      </c>
+      <c r="G7" s="2" t="s">
+        <v>261</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E8" s="24"/>
+    </row>
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E9" s="24"/>
+    </row>
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E14" s="24"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E15" s="24"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="E16" s="24"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="24"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="24"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="24"/>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="24"/>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="24"/>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E22" s="24"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="24"/>
+      <c r="J23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+  <dimension ref="A1:L23"/>
+  <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="3" max="4" width="14.375" style="2" customWidth="1"/>
+    <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
+    <col min="6" max="7" width="14.375" style="2" customWidth="1"/>
+    <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="13" width="9" style="2" customWidth="1"/>
+    <col min="14" max="16384" width="9" style="2"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="11" t="s">
+        <v>5</v>
+      </c>
+      <c r="B1" s="25" t="s">
+        <v>262</v>
+      </c>
+      <c r="C1" s="9"/>
+      <c r="D1" s="9"/>
+      <c r="E1" s="9"/>
+      <c r="F1" s="9"/>
+      <c r="G1" s="9"/>
+      <c r="H1" s="9"/>
+      <c r="I1" s="9"/>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="6"/>
+      <c r="B2" s="8" t="s">
+        <v>7</v>
+      </c>
+      <c r="C2" s="8" t="s">
+        <v>8</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>263</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>264</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>265</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>266</v>
+      </c>
+      <c r="H2" s="8" t="s">
+        <v>267</v>
+      </c>
+      <c r="I2" s="8" t="s">
+        <v>268</v>
+      </c>
+      <c r="J2" s="8" t="s">
+        <v>269</v>
+      </c>
+      <c r="K2" s="2" t="s">
+        <v>270</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>271</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="6"/>
+      <c r="B3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="C3" s="8" t="s">
+        <v>14</v>
+      </c>
+      <c r="D3" s="8" t="s">
+        <v>272</v>
+      </c>
+      <c r="E3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="F3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="G3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="H3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="I3" s="8" t="s">
+        <v>181</v>
+      </c>
+      <c r="J3" s="8" t="s">
+        <v>13</v>
+      </c>
+      <c r="K3" s="2" t="s">
+        <v>273</v>
+      </c>
+      <c r="L3" s="2" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" s="2">
+        <v>1</v>
+      </c>
+      <c r="C4" s="2" t="s">
+        <v>274</v>
+      </c>
+      <c r="D4" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E4" s="24">
+        <v>3</v>
+      </c>
+      <c r="F4" s="2">
+        <v>0.5</v>
+      </c>
+      <c r="G4" s="2">
+        <v>0</v>
+      </c>
+      <c r="H4" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I4" s="2">
+        <v>0</v>
+      </c>
+      <c r="J4" s="2">
+        <v>0</v>
+      </c>
+      <c r="K4" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L4" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B5" s="2">
+        <v>2</v>
+      </c>
+      <c r="C5" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="D5" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="E5" s="24">
+        <v>1</v>
+      </c>
+      <c r="F5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="G5" s="2">
+        <v>0</v>
+      </c>
+      <c r="H5" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="I5" s="2">
+        <v>0</v>
+      </c>
+      <c r="J5" s="2">
+        <v>1</v>
+      </c>
+      <c r="K5" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L5" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" s="2">
+        <v>3</v>
+      </c>
+      <c r="C6" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="D6" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="E6" s="24">
+        <v>1</v>
+      </c>
+      <c r="F6" s="2">
+        <v>3</v>
+      </c>
+      <c r="G6" s="2">
+        <v>1.5</v>
+      </c>
+      <c r="H6" s="2">
+        <v>2</v>
+      </c>
+      <c r="I6" s="2">
+        <v>0</v>
+      </c>
+      <c r="J6" s="2">
+        <v>2</v>
+      </c>
+      <c r="K6" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L6" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B7" s="2">
+        <v>4</v>
+      </c>
+      <c r="C7" s="2" t="s">
+        <v>276</v>
+      </c>
+      <c r="D7" s="2" t="s">
+        <v>247</v>
+      </c>
+      <c r="E7" s="24">
+        <v>3</v>
+      </c>
+      <c r="F7" s="2">
+        <v>1</v>
+      </c>
+      <c r="G7" s="2">
+        <v>0</v>
+      </c>
+      <c r="H7" s="2">
+        <v>1</v>
+      </c>
+      <c r="I7" s="2">
+        <v>0.7</v>
+      </c>
+      <c r="J7" s="2">
+        <v>0</v>
+      </c>
+      <c r="K7" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L7" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B8" s="2">
+        <v>5</v>
+      </c>
+      <c r="C8" s="2" t="s">
+        <v>277</v>
+      </c>
+      <c r="D8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="E8" s="24">
+        <v>5</v>
+      </c>
+      <c r="F8" s="2">
+        <v>0.35</v>
+      </c>
+      <c r="G8" s="2">
+        <v>0</v>
+      </c>
+      <c r="H8" s="2">
+        <v>1.2</v>
+      </c>
+      <c r="I8" s="2">
+        <v>0</v>
+      </c>
+      <c r="J8" s="2">
+        <v>0</v>
+      </c>
+      <c r="K8" s="2" t="s">
+        <v>275</v>
+      </c>
+      <c r="L8" s="2">
+        <v>1.5</v>
+      </c>
+    </row>
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E9" s="24"/>
+    </row>
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E10" s="24"/>
+    </row>
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E11" s="24"/>
+    </row>
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E12" s="24"/>
+    </row>
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E13" s="24"/>
+    </row>
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E14" s="24"/>
+      <c r="J14"/>
+    </row>
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E15" s="24"/>
+      <c r="J15"/>
+    </row>
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="E16" s="24"/>
+      <c r="J16"/>
+    </row>
+    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E17" s="24"/>
+      <c r="J17"/>
+    </row>
+    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E18" s="24"/>
+      <c r="J18"/>
+    </row>
+    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E19" s="24"/>
+      <c r="J19"/>
+    </row>
+    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E20" s="24"/>
+      <c r="J20"/>
+    </row>
+    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E21" s="24"/>
+      <c r="J21"/>
+    </row>
+    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E22" s="24"/>
+      <c r="J22"/>
+    </row>
+    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+      <c r="E23" s="24"/>
+      <c r="J23"/>
+    </row>
+  </sheetData>
+  <phoneticPr fontId="13" type="noConversion"/>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
@@ -1547,16 +2800,16 @@
         <v>28</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>233</v>
+        <v>229</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -1567,16 +2820,16 @@
         <v>29</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>226</v>
+        <v>249</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>227</v>
+        <v>224</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -2583,7 +3836,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -2739,7 +3992,7 @@
       <c r="I12" s="10"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3604,7 +4857,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -3799,21 +5052,21 @@
         <v>180</v>
       </c>
     </row>
-    <row r="6" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="C6" s="2" t="s">
         <v>191</v>
       </c>
       <c r="D6" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>192</v>
       </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>193</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>194</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -3837,21 +5090,21 @@
         <v>300</v>
       </c>
     </row>
-    <row r="7" spans="1:13" ht="49.5" customHeight="1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>194</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>236</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>195</v>
       </c>
-      <c r="D7" s="17" t="s">
+      <c r="F7" s="2" t="s">
         <v>196</v>
-      </c>
-      <c r="E7" s="2" t="s">
-        <v>197</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>198</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -3876,7 +5129,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
@@ -3903,7 +5156,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -3917,22 +5170,22 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>202</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>204</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>231</v>
+        <v>227</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -3970,7 +5223,7 @@
         <v>1001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -3987,7 +5240,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F5" s="2">
         <v>50</v>
@@ -4004,7 +5257,7 @@
         <v>1001</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -4021,7 +5274,7 @@
         <v>1001</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F7" s="2">
         <v>150</v>
@@ -4038,7 +5291,7 @@
         <v>1001</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F8" s="2">
         <v>200</v>
@@ -4055,7 +5308,7 @@
         <v>1001</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F9" s="2">
         <v>250</v>
@@ -4072,7 +5325,7 @@
         <v>1001</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F10" s="2">
         <v>300</v>
@@ -4089,7 +5342,7 @@
         <v>1001</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F11" s="2">
         <v>350</v>
@@ -4106,7 +5359,7 @@
         <v>1001</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F12" s="2">
         <v>400</v>
@@ -4123,7 +5376,7 @@
         <v>1001</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F13" s="2">
         <v>450</v>
@@ -4140,7 +5393,7 @@
         <v>1001</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F14" s="2">
         <v>500</v>
@@ -4157,7 +5410,7 @@
         <v>1001</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F15" s="2">
         <v>550</v>
@@ -4174,7 +5427,7 @@
         <v>1001</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F16" s="2">
         <v>600</v>
@@ -4191,7 +5444,7 @@
         <v>1001</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F17" s="2">
         <v>650</v>
@@ -4208,14 +5461,14 @@
         <v>1001</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="F18" s="2">
         <v>700</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
@@ -4241,7 +5494,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -4255,22 +5508,22 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>205</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>201</v>
+      </c>
+      <c r="G2" s="8" t="s">
+        <v>206</v>
+      </c>
+      <c r="H2" s="2" t="s">
         <v>207</v>
-      </c>
-      <c r="D2" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>203</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>208</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>209</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -4314,7 +5567,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -4337,7 +5590,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -4360,7 +5613,7 @@
         <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -4383,7 +5636,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H7">
         <v>10</v>
@@ -4406,7 +5659,7 @@
         <v>125</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H8">
         <v>10</v>
@@ -4429,7 +5682,7 @@
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H9">
         <v>20</v>
@@ -4452,7 +5705,7 @@
         <v>175</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H10">
         <v>20</v>
@@ -4475,7 +5728,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H11">
         <v>20</v>
@@ -4498,7 +5751,7 @@
         <v>225</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H12">
         <v>20</v>
@@ -4521,7 +5774,7 @@
         <v>250</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H13">
         <v>20</v>
@@ -4544,7 +5797,7 @@
         <v>275</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H14">
         <v>30</v>
@@ -4567,7 +5820,7 @@
         <v>300</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H15">
         <v>30</v>
@@ -4590,7 +5843,7 @@
         <v>325</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H16">
         <v>30</v>
@@ -4613,7 +5866,7 @@
         <v>350</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H17">
         <v>30</v>
@@ -4636,7 +5889,7 @@
         <v>375</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H18">
         <v>30</v>
@@ -4659,7 +5912,7 @@
         <v>400</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -4682,7 +5935,7 @@
         <v>425</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -4705,7 +5958,7 @@
         <v>450</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -4728,7 +5981,7 @@
         <v>475</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -4751,14 +6004,14 @@
         <v>500</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="H23">
         <v>40</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -4783,7 +6036,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -4792,13 +6045,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>210</v>
+      </c>
+      <c r="D2" s="2" t="s">
+        <v>211</v>
+      </c>
+      <c r="E2" s="2" t="s">
         <v>212</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>213</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>214</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -4807,7 +6060,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
@@ -4821,7 +6074,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="D4" s="2">
         <v>1500</v>
@@ -4835,7 +6088,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D5" s="2">
         <v>2000</v>
@@ -4849,7 +6102,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="D6" s="2">
         <v>1000</v>
@@ -4863,7 +6116,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D7" s="2">
         <v>500</v>
@@ -4877,7 +6130,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="D8" s="2">
         <v>3000</v>
@@ -4887,7 +6140,7 @@
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" horizontalDpi="0" verticalDpi="0"/>
 </worksheet>
@@ -4895,7 +6148,7 @@
 
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:L23"/>
+  <dimension ref="A1:M23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
@@ -4910,12 +6163,12 @@
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>228</v>
+        <v>225</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -4927,40 +6180,46 @@
       <c r="J1" s="9"/>
       <c r="K1" s="9"/>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>229</v>
+        <v>226</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="F2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="E2" s="8" t="s">
-        <v>202</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>203</v>
-      </c>
       <c r="G2" s="8" t="s">
-        <v>234</v>
+        <v>230</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>235</v>
+        <v>231</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>236</v>
+        <v>232</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>230</v>
+        <v>290</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>232</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+        <v>228</v>
+      </c>
+      <c r="L2" s="2" t="s">
+        <v>291</v>
+      </c>
+      <c r="M2" s="2" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -4992,8 +6251,14 @@
       <c r="K3" s="8" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L3" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="M3" s="2" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="4" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>3001</v>
       </c>
@@ -5004,7 +6269,7 @@
         <v>3001</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>237</v>
+        <v>233</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -5024,9 +6289,14 @@
       <c r="K4" s="2">
         <v>8101</v>
       </c>
-      <c r="L4"/>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L4">
+        <v>8002</v>
+      </c>
+      <c r="M4" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="5" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>3002</v>
       </c>
@@ -5037,7 +6307,7 @@
         <v>3001</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F5" s="2">
         <v>40</v>
@@ -5057,9 +6327,14 @@
       <c r="K5" s="2">
         <v>8101</v>
       </c>
-      <c r="L5"/>
-    </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L5">
+        <v>8002</v>
+      </c>
+      <c r="M5" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>3003</v>
       </c>
@@ -5070,7 +6345,7 @@
         <v>3001</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F6" s="2">
         <v>80</v>
@@ -5090,9 +6365,14 @@
       <c r="K6" s="2">
         <v>8101</v>
       </c>
-      <c r="L6"/>
-    </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L6">
+        <v>8002</v>
+      </c>
+      <c r="M6" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>3004</v>
       </c>
@@ -5103,7 +6383,7 @@
         <v>3001</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F7" s="2">
         <v>120</v>
@@ -5123,9 +6403,14 @@
       <c r="K7" s="2">
         <v>8101</v>
       </c>
-      <c r="L7"/>
-    </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L7">
+        <v>8002</v>
+      </c>
+      <c r="M7" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>3005</v>
       </c>
@@ -5136,7 +6421,7 @@
         <v>3001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F8" s="2">
         <v>160</v>
@@ -5156,9 +6441,14 @@
       <c r="K8" s="2">
         <v>8101</v>
       </c>
-      <c r="L8"/>
-    </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L8">
+        <v>8002</v>
+      </c>
+      <c r="M8" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>3006</v>
       </c>
@@ -5169,7 +6459,7 @@
         <v>3001</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F9" s="2">
         <v>200</v>
@@ -5189,9 +6479,14 @@
       <c r="K9" s="2">
         <v>8102</v>
       </c>
-      <c r="L9"/>
-    </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L9">
+        <v>8002</v>
+      </c>
+      <c r="M9" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>3007</v>
       </c>
@@ -5202,7 +6497,7 @@
         <v>3001</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F10" s="2">
         <v>240</v>
@@ -5222,9 +6517,14 @@
       <c r="K10" s="2">
         <v>8102</v>
       </c>
-      <c r="L10"/>
-    </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L10">
+        <v>8002</v>
+      </c>
+      <c r="M10" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>3008</v>
       </c>
@@ -5235,7 +6535,7 @@
         <v>3001</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F11" s="2">
         <v>280</v>
@@ -5255,9 +6555,14 @@
       <c r="K11" s="2">
         <v>8102</v>
       </c>
-      <c r="L11"/>
-    </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L11">
+        <v>8002</v>
+      </c>
+      <c r="M11" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>3009</v>
       </c>
@@ -5268,7 +6573,7 @@
         <v>3001</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F12" s="2">
         <v>320</v>
@@ -5288,9 +6593,14 @@
       <c r="K12" s="2">
         <v>8102</v>
       </c>
-      <c r="L12"/>
-    </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L12">
+        <v>8002</v>
+      </c>
+      <c r="M12" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>3010</v>
       </c>
@@ -5301,7 +6611,7 @@
         <v>3001</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F13" s="2">
         <v>360</v>
@@ -5321,9 +6631,14 @@
       <c r="K13" s="2">
         <v>8102</v>
       </c>
-      <c r="L13"/>
-    </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L13">
+        <v>8002</v>
+      </c>
+      <c r="M13" s="2">
+        <v>8003</v>
+      </c>
+    </row>
+    <row r="14" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
         <v>3011</v>
       </c>
@@ -5334,7 +6649,7 @@
         <v>3001</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F14" s="2">
         <v>400</v>
@@ -5354,9 +6669,14 @@
       <c r="K14" s="2">
         <v>8103</v>
       </c>
-      <c r="L14"/>
-    </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L14">
+        <v>8003</v>
+      </c>
+      <c r="M14" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="15" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
         <v>3012</v>
       </c>
@@ -5367,7 +6687,7 @@
         <v>3001</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F15" s="2">
         <v>440</v>
@@ -5387,9 +6707,14 @@
       <c r="K15" s="2">
         <v>8103</v>
       </c>
-      <c r="L15"/>
-    </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="L15">
+        <v>8003</v>
+      </c>
+      <c r="M15" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
         <v>3013</v>
       </c>
@@ -5400,7 +6725,7 @@
         <v>3001</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F16" s="2">
         <v>480</v>
@@ -5420,9 +6745,14 @@
       <c r="K16" s="2">
         <v>8103</v>
       </c>
-      <c r="L16"/>
-    </row>
-    <row r="17" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L16">
+        <v>8003</v>
+      </c>
+      <c r="M16" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="17" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>3014</v>
       </c>
@@ -5433,7 +6763,7 @@
         <v>3001</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F17" s="2">
         <v>520</v>
@@ -5453,9 +6783,14 @@
       <c r="K17" s="2">
         <v>8103</v>
       </c>
-      <c r="L17"/>
-    </row>
-    <row r="18" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L17">
+        <v>8003</v>
+      </c>
+      <c r="M17" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="18" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>3015</v>
       </c>
@@ -5466,7 +6801,7 @@
         <v>3001</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F18" s="2">
         <v>560</v>
@@ -5486,9 +6821,14 @@
       <c r="K18" s="2">
         <v>8103</v>
       </c>
-      <c r="L18"/>
-    </row>
-    <row r="19" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L18">
+        <v>8003</v>
+      </c>
+      <c r="M18" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="19" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B19" s="2">
         <v>3016</v>
       </c>
@@ -5499,7 +6839,7 @@
         <v>3001</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F19" s="2">
         <v>600</v>
@@ -5519,9 +6859,14 @@
       <c r="K19" s="2">
         <v>8104</v>
       </c>
-      <c r="L19"/>
-    </row>
-    <row r="20" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L19">
+        <v>8003</v>
+      </c>
+      <c r="M19" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="20" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B20" s="2">
         <v>3017</v>
       </c>
@@ -5532,7 +6877,7 @@
         <v>3001</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F20" s="2">
         <v>640</v>
@@ -5552,9 +6897,14 @@
       <c r="K20" s="2">
         <v>8104</v>
       </c>
-      <c r="L20"/>
-    </row>
-    <row r="21" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L20">
+        <v>8003</v>
+      </c>
+      <c r="M20" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="21" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B21" s="2">
         <v>3018</v>
       </c>
@@ -5565,7 +6915,7 @@
         <v>3001</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F21" s="2">
         <v>680</v>
@@ -5585,9 +6935,14 @@
       <c r="K21" s="2">
         <v>8104</v>
       </c>
-      <c r="L21"/>
-    </row>
-    <row r="22" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L21">
+        <v>8003</v>
+      </c>
+      <c r="M21" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="22" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B22" s="2">
         <v>3019</v>
       </c>
@@ -5598,7 +6953,7 @@
         <v>3001</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F22" s="2">
         <v>720</v>
@@ -5618,9 +6973,14 @@
       <c r="K22" s="2">
         <v>8104</v>
       </c>
-      <c r="L22"/>
-    </row>
-    <row r="23" spans="2:12" x14ac:dyDescent="0.3">
+      <c r="L22">
+        <v>8003</v>
+      </c>
+      <c r="M22" s="2">
+        <v>8004</v>
+      </c>
+    </row>
+    <row r="23" spans="2:13" x14ac:dyDescent="0.3">
       <c r="B23" s="2">
         <v>3020</v>
       </c>
@@ -5631,7 +6991,7 @@
         <v>3001</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>238</v>
+        <v>234</v>
       </c>
       <c r="F23" s="2">
         <v>760</v>
@@ -5651,10 +7011,15 @@
       <c r="K23" s="2">
         <v>8104</v>
       </c>
-      <c r="L23"/>
+      <c r="L23">
+        <v>8003</v>
+      </c>
+      <c r="M23" s="2">
+        <v>8004</v>
+      </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="12" type="noConversion"/>
+  <phoneticPr fontId="13" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="683" uniqueCount="293">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="292">
   <si>
     <t>!Enum</t>
   </si>
@@ -529,9 +529,6 @@
   </si>
   <si>
     <t>Order</t>
-  </si>
-  <si>
-    <t>ReqLevel</t>
   </si>
   <si>
     <t>ReqQuestID</t>
@@ -1511,7 +1508,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1560,39 +1557,39 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>240</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>241</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
+        <v>242</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>243</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>244</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
+        <v>244</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>245</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>246</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
+        <v>246</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>247</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>248</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1600,31 +1597,31 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>280</v>
+        <v>279</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
+        <v>280</v>
+      </c>
+      <c r="C13" s="2" t="s">
         <v>281</v>
-      </c>
-      <c r="C13" s="2" t="s">
-        <v>282</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
+        <v>282</v>
+      </c>
+      <c r="C14" s="2" t="s">
         <v>283</v>
-      </c>
-      <c r="C14" s="2" t="s">
-        <v>284</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
+        <v>284</v>
+      </c>
+      <c r="C15" s="2" t="s">
         <v>285</v>
-      </c>
-      <c r="C15" s="2" t="s">
-        <v>286</v>
       </c>
     </row>
   </sheetData>
@@ -1655,7 +1652,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>238</v>
+        <v>237</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -1671,28 +1668,28 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D2" s="8" t="s">
-        <v>199</v>
+        <v>198</v>
       </c>
       <c r="E2" s="8" t="s">
-        <v>237</v>
+        <v>236</v>
       </c>
       <c r="F2" s="8" t="s">
-        <v>201</v>
+        <v>200</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>232</v>
+        <v>231</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
       <c r="I2" s="8" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>287</v>
+        <v>286</v>
       </c>
     </row>
     <row r="3" spans="1:10" x14ac:dyDescent="0.3">
@@ -1722,7 +1719,7 @@
         <v>13</v>
       </c>
       <c r="J3" s="8" t="s">
-        <v>288</v>
+        <v>287</v>
       </c>
     </row>
     <row r="4" spans="1:10" x14ac:dyDescent="0.3">
@@ -1736,7 +1733,7 @@
         <v>4001</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -1745,13 +1742,13 @@
         <v>3</v>
       </c>
       <c r="H4" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I4" s="2">
         <v>1</v>
       </c>
       <c r="J4" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -1765,7 +1762,7 @@
         <v>4001</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F5" s="2">
         <v>40</v>
@@ -1774,13 +1771,13 @@
         <v>3</v>
       </c>
       <c r="H5" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I5" s="2">
         <v>1</v>
       </c>
       <c r="J5" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -1794,7 +1791,7 @@
         <v>4001</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F6" s="2">
         <v>80</v>
@@ -1803,13 +1800,13 @@
         <v>3</v>
       </c>
       <c r="H6" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I6" s="2">
         <v>1</v>
       </c>
       <c r="J6" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -1823,7 +1820,7 @@
         <v>4001</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F7" s="2">
         <v>120</v>
@@ -1832,13 +1829,13 @@
         <v>3</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I7" s="2">
         <v>1</v>
       </c>
       <c r="J7" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -1852,7 +1849,7 @@
         <v>4001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F8" s="2">
         <v>160</v>
@@ -1861,13 +1858,13 @@
         <v>3</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I8" s="2">
         <v>1</v>
       </c>
       <c r="J8" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="9" spans="1:10" x14ac:dyDescent="0.3">
@@ -1881,7 +1878,7 @@
         <v>4001</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F9" s="2">
         <v>200</v>
@@ -1890,13 +1887,13 @@
         <v>3</v>
       </c>
       <c r="H9" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I9" s="2">
         <v>1</v>
       </c>
       <c r="J9" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="10" spans="1:10" x14ac:dyDescent="0.3">
@@ -1910,7 +1907,7 @@
         <v>4001</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F10" s="2">
         <v>240</v>
@@ -1919,13 +1916,13 @@
         <v>3</v>
       </c>
       <c r="H10" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I10" s="2">
         <v>1</v>
       </c>
       <c r="J10" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="11" spans="1:10" x14ac:dyDescent="0.3">
@@ -1939,7 +1936,7 @@
         <v>4001</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F11" s="2">
         <v>280</v>
@@ -1948,13 +1945,13 @@
         <v>3</v>
       </c>
       <c r="H11" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I11" s="2">
         <v>1</v>
       </c>
       <c r="J11" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="12" spans="1:10" x14ac:dyDescent="0.3">
@@ -1968,7 +1965,7 @@
         <v>4001</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F12" s="2">
         <v>320</v>
@@ -1977,13 +1974,13 @@
         <v>3</v>
       </c>
       <c r="H12" s="2" t="s">
-        <v>278</v>
+        <v>277</v>
       </c>
       <c r="I12" s="2">
         <v>1</v>
       </c>
       <c r="J12" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="13" spans="1:10" x14ac:dyDescent="0.3">
@@ -1997,7 +1994,7 @@
         <v>4001</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="F13" s="2">
         <v>360</v>
@@ -2006,13 +2003,13 @@
         <v>5</v>
       </c>
       <c r="H13" s="2" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="I13" s="2">
         <v>1</v>
       </c>
       <c r="J13" s="2" t="s">
-        <v>289</v>
+        <v>288</v>
       </c>
     </row>
     <row r="14" spans="1:10" x14ac:dyDescent="0.3">
@@ -2083,7 +2080,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>252</v>
+        <v>251</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2099,19 +2096,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>252</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>255</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>256</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>257</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2129,7 +2126,7 @@
         <v>13</v>
       </c>
       <c r="E3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F3" s="8" t="s">
         <v>13</v>
@@ -2158,7 +2155,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2178,7 +2175,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2198,7 +2195,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2218,7 +2215,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2307,7 +2304,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2326,31 +2323,31 @@
         <v>8</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>262</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>268</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="2" t="s">
         <v>269</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>270</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>271</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2362,31 +2359,31 @@
         <v>14</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="F3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="J3" s="8" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="L3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
     </row>
     <row r="4" spans="1:12" x14ac:dyDescent="0.3">
@@ -2394,10 +2391,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E4" s="24">
         <v>3</v>
@@ -2418,7 +2415,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L4" s="2">
         <v>1.5</v>
@@ -2429,10 +2426,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="E5" s="24">
         <v>1</v>
@@ -2453,7 +2450,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L5" s="2">
         <v>1.5</v>
@@ -2464,10 +2461,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="E6" s="24">
         <v>1</v>
@@ -2488,7 +2485,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L6" s="2">
         <v>1.5</v>
@@ -2499,10 +2496,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>247</v>
+        <v>246</v>
       </c>
       <c r="E7" s="24">
         <v>3</v>
@@ -2523,7 +2520,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L7" s="2">
         <v>1.5</v>
@@ -2534,10 +2531,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>277</v>
+        <v>276</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>241</v>
+        <v>240</v>
       </c>
       <c r="E8" s="24">
         <v>5</v>
@@ -2558,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="L8" s="2">
         <v>1.5</v>
@@ -2800,16 +2797,16 @@
         <v>28</v>
       </c>
       <c r="E7" s="21" t="s">
-        <v>222</v>
+        <v>221</v>
       </c>
       <c r="F7" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G7" s="21" t="s">
-        <v>223</v>
+        <v>222</v>
       </c>
       <c r="H7" s="2" t="s">
-        <v>229</v>
+        <v>228</v>
       </c>
     </row>
     <row r="8" spans="1:14" x14ac:dyDescent="0.3">
@@ -2820,16 +2817,16 @@
         <v>29</v>
       </c>
       <c r="E8" s="21" t="s">
-        <v>220</v>
+        <v>219</v>
       </c>
       <c r="F8" s="2" t="s">
         <v>4</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>249</v>
+        <v>248</v>
       </c>
       <c r="H8" s="2" t="s">
-        <v>224</v>
+        <v>223</v>
       </c>
     </row>
     <row r="9" spans="1:14" x14ac:dyDescent="0.3">
@@ -3999,7 +3996,7 @@
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:K53"/>
+  <dimension ref="A1:J53"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
@@ -4007,17 +4004,16 @@
     <col min="3" max="3" width="9.875" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="6.375" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="15.875" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="11.75" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="18.5" style="2" customWidth="1"/>
-    <col min="11" max="11" width="17.25" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="8.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="13" width="13.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="14" max="16" width="9" style="2" customWidth="1"/>
-    <col min="17" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="11.75" bestFit="1" customWidth="1"/>
+    <col min="7" max="9" width="18.5" style="2" customWidth="1"/>
+    <col min="10" max="10" width="17.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="8.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="13.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="15" width="9" style="2" customWidth="1"/>
+    <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
@@ -4025,7 +4021,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
         <v>7</v>
@@ -4042,14 +4038,11 @@
       <c r="F2" t="s">
         <v>168</v>
       </c>
-      <c r="G2" t="s">
-        <v>169</v>
-      </c>
+      <c r="G2" s="8"/>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
-      <c r="J2" s="8"/>
-    </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -4066,15 +4059,12 @@
       <c r="F3" t="s">
         <v>13</v>
       </c>
-      <c r="G3" t="s">
-        <v>13</v>
-      </c>
+      <c r="G3" s="8"/>
       <c r="H3" s="8"/>
       <c r="I3" s="8"/>
       <c r="J3" s="8"/>
-      <c r="K3" s="8"/>
-    </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A4" s="6"/>
       <c r="B4" s="2">
         <v>20101</v>
@@ -4088,12 +4078,12 @@
       <c r="E4" t="s">
         <v>30</v>
       </c>
+      <c r="G4" s="8"/>
       <c r="H4" s="8"/>
       <c r="I4" s="8"/>
       <c r="J4" s="8"/>
-      <c r="K4" s="8"/>
-    </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>20102</v>
       </c>
@@ -4106,12 +4096,12 @@
       <c r="E5" t="s">
         <v>34</v>
       </c>
-      <c r="G5">
+      <c r="F5">
         <v>1</v>
       </c>
-      <c r="K5" s="10"/>
-    </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J5" s="10"/>
+    </row>
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>20103</v>
       </c>
@@ -4124,12 +4114,12 @@
       <c r="E6" t="s">
         <v>37</v>
       </c>
-      <c r="G6">
+      <c r="F6">
         <v>2</v>
       </c>
-      <c r="K6" s="10"/>
-    </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="J6" s="10"/>
+    </row>
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>20104</v>
       </c>
@@ -4142,11 +4132,11 @@
       <c r="E7" t="s">
         <v>40</v>
       </c>
-      <c r="G7">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="F7">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>20105</v>
       </c>
@@ -4159,11 +4149,11 @@
       <c r="E8" t="s">
         <v>43</v>
       </c>
-      <c r="G8">
+      <c r="F8">
         <v>4</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>20106</v>
       </c>
@@ -4176,11 +4166,11 @@
       <c r="E9" t="s">
         <v>46</v>
       </c>
-      <c r="G9">
+      <c r="F9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B10">
         <v>20107</v>
       </c>
@@ -4193,12 +4183,12 @@
       <c r="E10" t="s">
         <v>49</v>
       </c>
-      <c r="G10">
+      <c r="F10">
         <v>6</v>
       </c>
-      <c r="H10" s="10"/>
-    </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G10" s="10"/>
+    </row>
+    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B11">
         <v>20108</v>
       </c>
@@ -4211,12 +4201,12 @@
       <c r="E11" t="s">
         <v>52</v>
       </c>
-      <c r="G11">
+      <c r="F11">
         <v>7</v>
       </c>
-      <c r="H11" s="10"/>
-    </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G11" s="10"/>
+    </row>
+    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B12">
         <v>20109</v>
       </c>
@@ -4229,12 +4219,12 @@
       <c r="E12" t="s">
         <v>55</v>
       </c>
-      <c r="G12">
+      <c r="F12">
         <v>8</v>
       </c>
-      <c r="H12" s="10"/>
-    </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="G12" s="10"/>
+    </row>
+    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B13">
         <v>20110</v>
       </c>
@@ -4248,13 +4238,10 @@
         <v>58</v>
       </c>
       <c r="F13">
-        <v>10</v>
-      </c>
-      <c r="G13">
         <v>9</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B14">
         <v>20201</v>
       </c>
@@ -4267,11 +4254,11 @@
       <c r="E14" t="s">
         <v>61</v>
       </c>
-      <c r="G14">
+      <c r="F14">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B15">
         <v>20202</v>
       </c>
@@ -4284,11 +4271,11 @@
       <c r="E15" t="s">
         <v>65</v>
       </c>
-      <c r="G15">
+      <c r="F15">
         <v>11</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
       <c r="B16">
         <v>20203</v>
       </c>
@@ -4301,11 +4288,11 @@
       <c r="E16" t="s">
         <v>68</v>
       </c>
-      <c r="G16">
+      <c r="F16">
         <v>12</v>
       </c>
     </row>
-    <row r="17" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B17">
         <v>20204</v>
       </c>
@@ -4318,11 +4305,11 @@
       <c r="E17" t="s">
         <v>71</v>
       </c>
-      <c r="G17">
+      <c r="F17">
         <v>13</v>
       </c>
     </row>
-    <row r="18" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B18">
         <v>20205</v>
       </c>
@@ -4335,11 +4322,11 @@
       <c r="E18" t="s">
         <v>74</v>
       </c>
-      <c r="G18">
+      <c r="F18">
         <v>14</v>
       </c>
     </row>
-    <row r="19" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B19">
         <v>20206</v>
       </c>
@@ -4352,11 +4339,11 @@
       <c r="E19" t="s">
         <v>77</v>
       </c>
-      <c r="G19">
+      <c r="F19">
         <v>15</v>
       </c>
     </row>
-    <row r="20" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B20">
         <v>20207</v>
       </c>
@@ -4369,11 +4356,11 @@
       <c r="E20" t="s">
         <v>80</v>
       </c>
-      <c r="G20">
+      <c r="F20">
         <v>16</v>
       </c>
     </row>
-    <row r="21" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B21">
         <v>20208</v>
       </c>
@@ -4386,11 +4373,11 @@
       <c r="E21" t="s">
         <v>83</v>
       </c>
-      <c r="G21">
+      <c r="F21">
         <v>17</v>
       </c>
     </row>
-    <row r="22" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B22">
         <v>20209</v>
       </c>
@@ -4403,11 +4390,11 @@
       <c r="E22" t="s">
         <v>86</v>
       </c>
-      <c r="G22">
+      <c r="F22">
         <v>18</v>
       </c>
     </row>
-    <row r="23" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B23">
         <v>20210</v>
       </c>
@@ -4421,13 +4408,10 @@
         <v>89</v>
       </c>
       <c r="F23">
-        <v>30</v>
-      </c>
-      <c r="G23">
         <v>19</v>
       </c>
     </row>
-    <row r="24" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B24">
         <v>20301</v>
       </c>
@@ -4441,7 +4425,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="25" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B25">
         <v>20302</v>
       </c>
@@ -4455,7 +4439,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="26" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="26" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B26">
         <v>20303</v>
       </c>
@@ -4469,7 +4453,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="27" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="27" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B27">
         <v>20304</v>
       </c>
@@ -4483,7 +4467,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="28" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="28" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B28">
         <v>20305</v>
       </c>
@@ -4497,7 +4481,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="29" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="29" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B29">
         <v>20306</v>
       </c>
@@ -4511,7 +4495,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="30" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="30" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B30">
         <v>20307</v>
       </c>
@@ -4525,7 +4509,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="31" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="31" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B31">
         <v>20308</v>
       </c>
@@ -4539,7 +4523,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="32" spans="2:7" x14ac:dyDescent="0.3">
+    <row r="32" spans="2:6" x14ac:dyDescent="0.3">
       <c r="B32">
         <v>20309</v>
       </c>
@@ -4553,7 +4537,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="33" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="33" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B33">
         <v>20310</v>
       </c>
@@ -4566,11 +4550,8 @@
       <c r="E33" t="s">
         <v>111</v>
       </c>
-      <c r="F33">
-        <v>50</v>
-      </c>
-    </row>
-    <row r="34" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="34" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B34">
         <v>20401</v>
       </c>
@@ -4584,7 +4565,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="35" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="35" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B35">
         <v>20402</v>
       </c>
@@ -4598,7 +4579,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="36" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="36" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B36">
         <v>20403</v>
       </c>
@@ -4612,7 +4593,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="37" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="37" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B37">
         <v>20404</v>
       </c>
@@ -4626,7 +4607,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="38" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="38" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B38">
         <v>20405</v>
       </c>
@@ -4640,7 +4621,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="39" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="39" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B39">
         <v>20406</v>
       </c>
@@ -4654,7 +4635,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="40" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="40" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B40">
         <v>20407</v>
       </c>
@@ -4668,7 +4649,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="41" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="41" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B41">
         <v>20408</v>
       </c>
@@ -4682,7 +4663,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="42" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="42" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B42">
         <v>20409</v>
       </c>
@@ -4696,7 +4677,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="43" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="43" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B43">
         <v>20410</v>
       </c>
@@ -4709,11 +4690,8 @@
       <c r="E43" t="s">
         <v>132</v>
       </c>
-      <c r="F43">
-        <v>70</v>
-      </c>
-    </row>
-    <row r="44" spans="2:6" x14ac:dyDescent="0.3">
+    </row>
+    <row r="44" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B44">
         <v>20501</v>
       </c>
@@ -4727,7 +4705,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="45" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="45" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B45">
         <v>20502</v>
       </c>
@@ -4741,7 +4719,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="46" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="46" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B46">
         <v>20503</v>
       </c>
@@ -4755,7 +4733,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="47" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="47" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B47">
         <v>20504</v>
       </c>
@@ -4769,7 +4747,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="48" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="48" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B48">
         <v>20505</v>
       </c>
@@ -4783,7 +4761,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="49" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="49" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B49">
         <v>20506</v>
       </c>
@@ -4797,7 +4775,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="50" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="50" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B50">
         <v>20507</v>
       </c>
@@ -4811,7 +4789,7 @@
         <v>147</v>
       </c>
     </row>
-    <row r="51" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="51" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B51">
         <v>20508</v>
       </c>
@@ -4825,7 +4803,7 @@
         <v>149</v>
       </c>
     </row>
-    <row r="52" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="52" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B52">
         <v>20509</v>
       </c>
@@ -4839,7 +4817,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="53" spans="2:6" x14ac:dyDescent="0.3">
+    <row r="53" spans="2:5" x14ac:dyDescent="0.3">
       <c r="B53">
         <v>20510</v>
       </c>
@@ -4851,9 +4829,6 @@
       </c>
       <c r="E53" t="s">
         <v>153</v>
-      </c>
-      <c r="F53">
-        <v>100</v>
       </c>
     </row>
   </sheetData>
@@ -4886,7 +4861,7 @@
   <sheetData>
     <row r="1" spans="1:13" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="14" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="B1" s="16" t="s">
         <v>4</v>
@@ -4913,34 +4888,34 @@
         <v>10</v>
       </c>
       <c r="F2" s="8" t="s">
+        <v>170</v>
+      </c>
+      <c r="G2" t="s">
         <v>171</v>
       </c>
-      <c r="G2" t="s">
+      <c r="H2" t="s">
         <v>172</v>
       </c>
-      <c r="H2" t="s">
+      <c r="I2" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="I2" s="2" t="s">
+      <c r="J2" s="2" t="s">
         <v>174</v>
       </c>
-      <c r="J2" s="2" t="s">
+      <c r="K2" s="2" t="s">
         <v>175</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>176</v>
       </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="8" t="s">
         <v>177</v>
-      </c>
-      <c r="M2" s="8" t="s">
-        <v>178</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="C3" s="8" t="s">
         <v>14</v>
@@ -4961,13 +4936,13 @@
         <v>13</v>
       </c>
       <c r="I3" s="2" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="J3" s="2" t="s">
         <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>13</v>
@@ -4978,19 +4953,19 @@
     </row>
     <row r="4" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B4" s="2" t="s">
+        <v>181</v>
+      </c>
+      <c r="C4" s="2" t="s">
         <v>182</v>
       </c>
-      <c r="C4" s="2" t="s">
+      <c r="D4" s="17" t="s">
         <v>183</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>184</v>
       </c>
       <c r="E4" s="2" t="s">
         <v>21</v>
       </c>
       <c r="F4" s="2" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
       <c r="G4" s="2">
         <v>5</v>
@@ -4999,7 +4974,7 @@
         <v>30</v>
       </c>
       <c r="I4" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J4" s="2">
         <v>500</v>
@@ -5016,19 +4991,19 @@
     </row>
     <row r="5" spans="1:13" ht="33" customHeight="1" x14ac:dyDescent="0.3">
       <c r="B5" s="2" t="s">
+        <v>186</v>
+      </c>
+      <c r="C5" s="2" t="s">
         <v>187</v>
       </c>
-      <c r="C5" s="2" t="s">
+      <c r="D5" s="17" t="s">
         <v>188</v>
-      </c>
-      <c r="D5" s="17" t="s">
-        <v>189</v>
       </c>
       <c r="E5" s="2" t="s">
         <v>25</v>
       </c>
       <c r="F5" s="2" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
       <c r="G5" s="2">
         <v>5</v>
@@ -5037,7 +5012,7 @@
         <v>30</v>
       </c>
       <c r="I5" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J5" s="2">
         <v>500</v>
@@ -5054,19 +5029,19 @@
     </row>
     <row r="6" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B6" s="2" t="s">
-        <v>221</v>
+        <v>220</v>
       </c>
       <c r="C6" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="D6" s="17" t="s">
+        <v>234</v>
+      </c>
+      <c r="E6" s="2" t="s">
         <v>191</v>
       </c>
-      <c r="D6" s="17" t="s">
-        <v>235</v>
-      </c>
-      <c r="E6" s="2" t="s">
+      <c r="F6" s="2" t="s">
         <v>192</v>
-      </c>
-      <c r="F6" s="2" t="s">
-        <v>193</v>
       </c>
       <c r="G6" s="2">
         <v>5</v>
@@ -5075,7 +5050,7 @@
         <v>30</v>
       </c>
       <c r="I6" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J6" s="2">
         <v>500</v>
@@ -5092,19 +5067,19 @@
     </row>
     <row r="7" spans="1:13" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
-        <v>219</v>
+        <v>218</v>
       </c>
       <c r="C7" s="2" t="s">
+        <v>193</v>
+      </c>
+      <c r="D7" s="17" t="s">
+        <v>235</v>
+      </c>
+      <c r="E7" s="2" t="s">
         <v>194</v>
       </c>
-      <c r="D7" s="17" t="s">
-        <v>236</v>
-      </c>
-      <c r="E7" s="2" t="s">
+      <c r="F7" s="2" t="s">
         <v>195</v>
-      </c>
-      <c r="F7" s="2" t="s">
-        <v>196</v>
       </c>
       <c r="G7" s="2">
         <v>5</v>
@@ -5113,7 +5088,7 @@
         <v>30</v>
       </c>
       <c r="I7" t="s">
-        <v>186</v>
+        <v>185</v>
       </c>
       <c r="J7" s="2">
         <v>500</v>
@@ -5156,7 +5131,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -5170,22 +5145,22 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>197</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>198</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>201</v>
       </c>
-      <c r="G2" s="8" t="s">
-        <v>202</v>
-      </c>
       <c r="H2" s="2" t="s">
-        <v>227</v>
+        <v>226</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5223,7 +5198,7 @@
         <v>1001</v>
       </c>
       <c r="E4" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -5240,7 +5215,7 @@
         <v>1001</v>
       </c>
       <c r="E5" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F5" s="2">
         <v>50</v>
@@ -5257,7 +5232,7 @@
         <v>1001</v>
       </c>
       <c r="E6" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F6" s="2">
         <v>100</v>
@@ -5274,7 +5249,7 @@
         <v>1001</v>
       </c>
       <c r="E7" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F7" s="2">
         <v>150</v>
@@ -5291,7 +5266,7 @@
         <v>1001</v>
       </c>
       <c r="E8" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F8" s="2">
         <v>200</v>
@@ -5308,7 +5283,7 @@
         <v>1001</v>
       </c>
       <c r="E9" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F9" s="2">
         <v>250</v>
@@ -5325,7 +5300,7 @@
         <v>1001</v>
       </c>
       <c r="E10" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F10" s="2">
         <v>300</v>
@@ -5342,7 +5317,7 @@
         <v>1001</v>
       </c>
       <c r="E11" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F11" s="2">
         <v>350</v>
@@ -5359,7 +5334,7 @@
         <v>1001</v>
       </c>
       <c r="E12" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F12" s="2">
         <v>400</v>
@@ -5376,7 +5351,7 @@
         <v>1001</v>
       </c>
       <c r="E13" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F13" s="2">
         <v>450</v>
@@ -5393,7 +5368,7 @@
         <v>1001</v>
       </c>
       <c r="E14" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F14" s="2">
         <v>500</v>
@@ -5410,7 +5385,7 @@
         <v>1001</v>
       </c>
       <c r="E15" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F15" s="2">
         <v>550</v>
@@ -5427,7 +5402,7 @@
         <v>1001</v>
       </c>
       <c r="E16" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F16" s="2">
         <v>600</v>
@@ -5444,7 +5419,7 @@
         <v>1001</v>
       </c>
       <c r="E17" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F17" s="2">
         <v>650</v>
@@ -5461,7 +5436,7 @@
         <v>1001</v>
       </c>
       <c r="E18" s="2" t="s">
-        <v>203</v>
+        <v>202</v>
       </c>
       <c r="F18" s="2">
         <v>700</v>
@@ -5494,7 +5469,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="20" t="s">
-        <v>204</v>
+        <v>203</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -5508,22 +5483,22 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>204</v>
+      </c>
+      <c r="D2" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="8" t="s">
+        <v>199</v>
+      </c>
+      <c r="F2" s="8" t="s">
+        <v>200</v>
+      </c>
+      <c r="G2" s="8" t="s">
         <v>205</v>
       </c>
-      <c r="D2" s="8" t="s">
-        <v>199</v>
-      </c>
-      <c r="E2" s="8" t="s">
-        <v>200</v>
-      </c>
-      <c r="F2" s="8" t="s">
-        <v>201</v>
-      </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="2" t="s">
         <v>206</v>
-      </c>
-      <c r="H2" s="2" t="s">
-        <v>207</v>
       </c>
     </row>
     <row r="3" spans="1:8" x14ac:dyDescent="0.3">
@@ -5544,7 +5519,7 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="H3" s="2" t="s">
         <v>13</v>
@@ -5567,7 +5542,7 @@
         <v>1</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H4">
         <v>10</v>
@@ -5590,7 +5565,7 @@
         <v>50</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H5">
         <v>10</v>
@@ -5613,7 +5588,7 @@
         <v>75</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H6">
         <v>10</v>
@@ -5636,7 +5611,7 @@
         <v>100</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H7">
         <v>10</v>
@@ -5659,7 +5634,7 @@
         <v>125</v>
       </c>
       <c r="G8" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H8">
         <v>10</v>
@@ -5682,7 +5657,7 @@
         <v>150</v>
       </c>
       <c r="G9" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H9">
         <v>20</v>
@@ -5705,7 +5680,7 @@
         <v>175</v>
       </c>
       <c r="G10" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H10">
         <v>20</v>
@@ -5728,7 +5703,7 @@
         <v>200</v>
       </c>
       <c r="G11" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H11">
         <v>20</v>
@@ -5751,7 +5726,7 @@
         <v>225</v>
       </c>
       <c r="G12" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H12">
         <v>20</v>
@@ -5774,7 +5749,7 @@
         <v>250</v>
       </c>
       <c r="G13" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H13">
         <v>20</v>
@@ -5797,7 +5772,7 @@
         <v>275</v>
       </c>
       <c r="G14" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H14">
         <v>30</v>
@@ -5820,7 +5795,7 @@
         <v>300</v>
       </c>
       <c r="G15" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H15">
         <v>30</v>
@@ -5843,7 +5818,7 @@
         <v>325</v>
       </c>
       <c r="G16" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H16">
         <v>30</v>
@@ -5866,7 +5841,7 @@
         <v>350</v>
       </c>
       <c r="G17" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H17">
         <v>30</v>
@@ -5889,7 +5864,7 @@
         <v>375</v>
       </c>
       <c r="G18" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H18">
         <v>30</v>
@@ -5912,7 +5887,7 @@
         <v>400</v>
       </c>
       <c r="G19" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H19">
         <v>40</v>
@@ -5935,7 +5910,7 @@
         <v>425</v>
       </c>
       <c r="G20" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H20">
         <v>40</v>
@@ -5958,7 +5933,7 @@
         <v>450</v>
       </c>
       <c r="G21" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H21">
         <v>40</v>
@@ -5981,7 +5956,7 @@
         <v>475</v>
       </c>
       <c r="G22" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H22">
         <v>40</v>
@@ -6004,7 +5979,7 @@
         <v>500</v>
       </c>
       <c r="G23" s="2" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
       <c r="H23">
         <v>40</v>
@@ -6036,7 +6011,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="19" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
     </row>
     <row r="2" spans="1:5" x14ac:dyDescent="0.3">
@@ -6045,13 +6020,13 @@
         <v>7</v>
       </c>
       <c r="C2" s="2" t="s">
+        <v>209</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>210</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="E2" s="2" t="s">
         <v>211</v>
-      </c>
-      <c r="E2" s="2" t="s">
-        <v>212</v>
       </c>
     </row>
     <row r="3" spans="1:5" x14ac:dyDescent="0.3">
@@ -6060,7 +6035,7 @@
         <v>13</v>
       </c>
       <c r="C3" s="2" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
       <c r="D3" s="2" t="s">
         <v>13</v>
@@ -6074,7 +6049,7 @@
         <v>1</v>
       </c>
       <c r="C4" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="D4" s="2">
         <v>1500</v>
@@ -6088,7 +6063,7 @@
         <v>2</v>
       </c>
       <c r="C5" t="s">
-        <v>215</v>
+        <v>214</v>
       </c>
       <c r="D5" s="2">
         <v>2000</v>
@@ -6102,7 +6077,7 @@
         <v>3</v>
       </c>
       <c r="C6" t="s">
-        <v>216</v>
+        <v>215</v>
       </c>
       <c r="D6" s="2">
         <v>1000</v>
@@ -6116,7 +6091,7 @@
         <v>4</v>
       </c>
       <c r="C7" t="s">
-        <v>217</v>
+        <v>216</v>
       </c>
       <c r="D7" s="2">
         <v>500</v>
@@ -6130,7 +6105,7 @@
         <v>5</v>
       </c>
       <c r="C8" t="s">
-        <v>218</v>
+        <v>217</v>
       </c>
       <c r="D8" s="2">
         <v>3000</v>
@@ -6168,7 +6143,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="22" t="s">
-        <v>225</v>
+        <v>224</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -6186,37 +6161,37 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
-        <v>226</v>
+        <v>225</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>198</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>199</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>200</v>
       </c>
-      <c r="F2" s="8" t="s">
-        <v>201</v>
-      </c>
       <c r="G2" s="8" t="s">
+        <v>229</v>
+      </c>
+      <c r="H2" s="8" t="s">
         <v>230</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>231</v>
       </c>
-      <c r="I2" s="8" t="s">
-        <v>232</v>
-      </c>
       <c r="J2" s="8" t="s">
+        <v>289</v>
+      </c>
+      <c r="K2" s="8" t="s">
+        <v>227</v>
+      </c>
+      <c r="L2" s="2" t="s">
         <v>290</v>
       </c>
-      <c r="K2" s="8" t="s">
-        <v>228</v>
-      </c>
-      <c r="L2" s="2" t="s">
+      <c r="M2" s="2" t="s">
         <v>291</v>
-      </c>
-      <c r="M2" s="2" t="s">
-        <v>292</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -6237,10 +6212,10 @@
         <v>13</v>
       </c>
       <c r="G3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="H3" s="8" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="I3" s="8" t="s">
         <v>13</v>
@@ -6269,7 +6244,7 @@
         <v>3001</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>233</v>
+        <v>232</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
@@ -6307,7 +6282,7 @@
         <v>3001</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F5" s="2">
         <v>40</v>
@@ -6345,7 +6320,7 @@
         <v>3001</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F6" s="2">
         <v>80</v>
@@ -6383,7 +6358,7 @@
         <v>3001</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F7" s="2">
         <v>120</v>
@@ -6421,7 +6396,7 @@
         <v>3001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F8" s="2">
         <v>160</v>
@@ -6459,7 +6434,7 @@
         <v>3001</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F9" s="2">
         <v>200</v>
@@ -6497,7 +6472,7 @@
         <v>3001</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F10" s="2">
         <v>240</v>
@@ -6535,7 +6510,7 @@
         <v>3001</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F11" s="2">
         <v>280</v>
@@ -6573,7 +6548,7 @@
         <v>3001</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F12" s="2">
         <v>320</v>
@@ -6611,7 +6586,7 @@
         <v>3001</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F13" s="2">
         <v>360</v>
@@ -6649,7 +6624,7 @@
         <v>3001</v>
       </c>
       <c r="E14" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F14" s="2">
         <v>400</v>
@@ -6687,7 +6662,7 @@
         <v>3001</v>
       </c>
       <c r="E15" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F15" s="2">
         <v>440</v>
@@ -6725,7 +6700,7 @@
         <v>3001</v>
       </c>
       <c r="E16" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F16" s="2">
         <v>480</v>
@@ -6763,7 +6738,7 @@
         <v>3001</v>
       </c>
       <c r="E17" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F17" s="2">
         <v>520</v>
@@ -6801,7 +6776,7 @@
         <v>3001</v>
       </c>
       <c r="E18" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F18" s="2">
         <v>560</v>
@@ -6839,7 +6814,7 @@
         <v>3001</v>
       </c>
       <c r="E19" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F19" s="2">
         <v>600</v>
@@ -6877,7 +6852,7 @@
         <v>3001</v>
       </c>
       <c r="E20" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F20" s="2">
         <v>640</v>
@@ -6915,7 +6890,7 @@
         <v>3001</v>
       </c>
       <c r="E21" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F21" s="2">
         <v>680</v>
@@ -6953,7 +6928,7 @@
         <v>3001</v>
       </c>
       <c r="E22" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F22" s="2">
         <v>720</v>
@@ -6991,7 +6966,7 @@
         <v>3001</v>
       </c>
       <c r="E23" s="24" t="s">
-        <v>234</v>
+        <v>233</v>
       </c>
       <c r="F23" s="2">
         <v>760</v>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -1508,7 +1508,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -5203,6 +5203,12 @@
       <c r="F4" s="2">
         <v>1</v>
       </c>
+      <c r="G4" s="2">
+        <v>500</v>
+      </c>
+      <c r="H4" s="2">
+        <v>8301</v>
+      </c>
     </row>
     <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
@@ -5220,6 +5226,12 @@
       <c r="F5" s="2">
         <v>50</v>
       </c>
+      <c r="G5" s="2">
+        <v>1000</v>
+      </c>
+      <c r="H5" s="2">
+        <v>8302</v>
+      </c>
     </row>
     <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
@@ -5237,6 +5249,12 @@
       <c r="F6" s="2">
         <v>100</v>
       </c>
+      <c r="G6" s="2">
+        <v>1500</v>
+      </c>
+      <c r="H6" s="2">
+        <v>8303</v>
+      </c>
     </row>
     <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
@@ -5254,6 +5272,12 @@
       <c r="F7" s="2">
         <v>150</v>
       </c>
+      <c r="G7" s="2">
+        <v>2000</v>
+      </c>
+      <c r="H7" s="2">
+        <v>8304</v>
+      </c>
     </row>
     <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
@@ -5271,6 +5295,12 @@
       <c r="F8" s="2">
         <v>200</v>
       </c>
+      <c r="G8" s="2">
+        <v>2500</v>
+      </c>
+      <c r="H8" s="2">
+        <v>8305</v>
+      </c>
     </row>
     <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
@@ -5288,6 +5318,12 @@
       <c r="F9" s="2">
         <v>250</v>
       </c>
+      <c r="G9" s="2">
+        <v>3000</v>
+      </c>
+      <c r="H9" s="2">
+        <v>8306</v>
+      </c>
     </row>
     <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
@@ -5305,6 +5341,12 @@
       <c r="F10" s="2">
         <v>300</v>
       </c>
+      <c r="G10" s="2">
+        <v>3500</v>
+      </c>
+      <c r="H10" s="2">
+        <v>8307</v>
+      </c>
     </row>
     <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
@@ -5322,6 +5364,12 @@
       <c r="F11" s="2">
         <v>350</v>
       </c>
+      <c r="G11" s="2">
+        <v>4000</v>
+      </c>
+      <c r="H11" s="2">
+        <v>8308</v>
+      </c>
     </row>
     <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
@@ -5339,6 +5387,12 @@
       <c r="F12" s="2">
         <v>400</v>
       </c>
+      <c r="G12" s="2">
+        <v>4500</v>
+      </c>
+      <c r="H12" s="2">
+        <v>8309</v>
+      </c>
     </row>
     <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
@@ -5356,6 +5410,12 @@
       <c r="F13" s="2">
         <v>450</v>
       </c>
+      <c r="G13" s="2">
+        <v>5000</v>
+      </c>
+      <c r="H13" s="2">
+        <v>8310</v>
+      </c>
     </row>
     <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B14" s="2">
@@ -5373,6 +5433,12 @@
       <c r="F14" s="2">
         <v>500</v>
       </c>
+      <c r="G14" s="2">
+        <v>5500</v>
+      </c>
+      <c r="H14" s="2">
+        <v>8311</v>
+      </c>
     </row>
     <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B15" s="2">
@@ -5390,6 +5456,12 @@
       <c r="F15" s="2">
         <v>550</v>
       </c>
+      <c r="G15" s="2">
+        <v>6000</v>
+      </c>
+      <c r="H15" s="2">
+        <v>8312</v>
+      </c>
     </row>
     <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B16" s="2">
@@ -5407,8 +5479,14 @@
       <c r="F16" s="2">
         <v>600</v>
       </c>
-    </row>
-    <row r="17" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G16" s="2">
+        <v>6500</v>
+      </c>
+      <c r="H16" s="2">
+        <v>8313</v>
+      </c>
+    </row>
+    <row r="17" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B17" s="2">
         <v>1014</v>
       </c>
@@ -5424,8 +5502,14 @@
       <c r="F17" s="2">
         <v>650</v>
       </c>
-    </row>
-    <row r="18" spans="2:6" x14ac:dyDescent="0.3">
+      <c r="G17" s="2">
+        <v>7000</v>
+      </c>
+      <c r="H17" s="2">
+        <v>8314</v>
+      </c>
+    </row>
+    <row r="18" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B18" s="2">
         <v>1015</v>
       </c>
@@ -5440,6 +5524,12 @@
       </c>
       <c r="F18" s="2">
         <v>700</v>
+      </c>
+      <c r="G18" s="2">
+        <v>7500</v>
+      </c>
+      <c r="H18" s="2">
+        <v>8315</v>
       </c>
     </row>
   </sheetData>

--- a/Shared/XLS/Map.xlsx
+++ b/Shared/XLS/Map.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="5" lowestEdited="5" rupBuild="9303"/>
   <workbookPr/>
   <bookViews>
-    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="6" activeTab="11"/>
+    <workbookView xWindow="-38520" yWindow="-120" windowWidth="38640" windowHeight="21240" firstSheet="6" activeTab="9"/>
   </bookViews>
   <sheets>
     <sheet name="#Enum" sheetId="1" r:id="rId1"/>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="681" uniqueCount="292">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="657" uniqueCount="287">
   <si>
     <t>!Enum</t>
   </si>
@@ -760,10 +760,6 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>ChestRewardGroupIDs</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>RuinsHazardType</t>
   </si>
   <si>
@@ -879,14 +875,6 @@
     <t>가로줄 5개</t>
   </si>
   <si>
-    <t>8201;8202;8203</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>8211;8211;8212;8213;8213</t>
-    <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
     <t>DungeonChestGrade</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
@@ -915,26 +903,20 @@
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>ChestGrade</t>
+    <t>ChestRewardGroupID_Normal</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>!DungeonChestGrade</t>
+    <t>ChestRewardGroupID_Advanced</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>Premium</t>
+    <t>ChestRewardGroupID_Premium</t>
     <phoneticPr fontId="13" type="noConversion"/>
   </si>
   <si>
-    <t>NormalChestRewardGroupID</t>
+    <t>ClearRewardGroupID</t>
     <phoneticPr fontId="13" type="noConversion"/>
-  </si>
-  <si>
-    <t>AdvancedChestRewardGroupID</t>
-  </si>
-  <si>
-    <t>PremiumChestRewardGroupID</t>
   </si>
 </sst>
 </file>
@@ -1508,7 +1490,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns="" xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" xmlns="" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -1557,39 +1539,39 @@
         <v>0</v>
       </c>
       <c r="B6" s="2" t="s">
-        <v>239</v>
+        <v>238</v>
       </c>
     </row>
     <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B7" s="2" t="s">
+        <v>239</v>
+      </c>
+      <c r="C7" s="2" t="s">
         <v>240</v>
-      </c>
-      <c r="C7" s="2" t="s">
-        <v>241</v>
       </c>
     </row>
     <row r="8" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B8" s="2" t="s">
+        <v>241</v>
+      </c>
+      <c r="C8" s="2" t="s">
         <v>242</v>
-      </c>
-      <c r="C8" s="2" t="s">
-        <v>243</v>
       </c>
     </row>
     <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B9" s="2" t="s">
+        <v>243</v>
+      </c>
+      <c r="C9" s="2" t="s">
         <v>244</v>
-      </c>
-      <c r="C9" s="2" t="s">
-        <v>245</v>
       </c>
     </row>
     <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B10" s="2" t="s">
+        <v>245</v>
+      </c>
+      <c r="C10" s="2" t="s">
         <v>246</v>
-      </c>
-      <c r="C10" s="2" t="s">
-        <v>247</v>
       </c>
     </row>
     <row r="12" spans="1:4" x14ac:dyDescent="0.3">
@@ -1597,31 +1579,31 @@
         <v>0</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>279</v>
+        <v>276</v>
       </c>
     </row>
     <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B13" s="2" t="s">
-        <v>280</v>
+        <v>277</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>281</v>
+        <v>278</v>
       </c>
     </row>
     <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B14" s="2" t="s">
-        <v>282</v>
+        <v>279</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>283</v>
+        <v>280</v>
       </c>
     </row>
     <row r="15" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B15" s="2" t="s">
-        <v>284</v>
+        <v>281</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>285</v>
+        <v>282</v>
       </c>
     </row>
   </sheetData>
@@ -1633,21 +1615,21 @@
 
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <dimension ref="A1:J23"/>
+  <dimension ref="A1:H23"/>
   <sheetFormatPr defaultRowHeight="16.5" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11.625" style="7" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="12.625" style="2" bestFit="1" customWidth="1"/>
     <col min="3" max="4" width="14.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="6" max="7" width="14.375" style="2" customWidth="1"/>
-    <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="23.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="9" style="2" customWidth="1"/>
-    <col min="14" max="16384" width="9" style="2"/>
+    <col min="6" max="6" width="14.375" style="2" customWidth="1"/>
+    <col min="7" max="7" width="21.625" style="2" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="23.875" style="2" bestFit="1" customWidth="1"/>
+    <col min="9" max="11" width="9" style="2" customWidth="1"/>
+    <col min="12" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="5" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:8" s="5" customFormat="1" x14ac:dyDescent="0.3">
       <c r="A1" s="11" t="s">
         <v>5</v>
       </c>
@@ -1660,9 +1642,8 @@
       <c r="F1" s="9"/>
       <c r="G1" s="9"/>
       <c r="H1" s="9"/>
-      <c r="I1" s="9"/>
-    </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="2" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A2" s="6"/>
       <c r="B2" s="8" t="s">
         <v>7</v>
@@ -1680,19 +1661,13 @@
         <v>200</v>
       </c>
       <c r="G2" s="8" t="s">
-        <v>231</v>
+        <v>286</v>
       </c>
       <c r="H2" s="8" t="s">
-        <v>238</v>
-      </c>
-      <c r="I2" s="8" t="s">
-        <v>249</v>
-      </c>
-      <c r="J2" s="8" t="s">
-        <v>286</v>
-      </c>
-    </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+        <v>248</v>
+      </c>
+    </row>
+    <row r="3" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A3" s="6"/>
       <c r="B3" s="2" t="s">
         <v>13</v>
@@ -1715,14 +1690,8 @@
       <c r="H3" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="I3" s="8" t="s">
-        <v>13</v>
-      </c>
-      <c r="J3" s="8" t="s">
-        <v>287</v>
-      </c>
-    </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="4" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B4" s="2">
         <v>4001</v>
       </c>
@@ -1733,25 +1702,16 @@
         <v>4001</v>
       </c>
       <c r="E4" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F4" s="2">
         <v>1</v>
       </c>
-      <c r="G4" s="2">
-        <v>3</v>
-      </c>
-      <c r="H4" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I4" s="2">
+      <c r="H4" s="2">
         <v>1</v>
       </c>
-      <c r="J4" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="5" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B5" s="2">
         <v>4002</v>
       </c>
@@ -1762,25 +1722,16 @@
         <v>4001</v>
       </c>
       <c r="E5" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F5" s="2">
         <v>40</v>
       </c>
-      <c r="G5" s="2">
-        <v>3</v>
-      </c>
-      <c r="H5" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I5" s="2">
+      <c r="H5" s="2">
         <v>1</v>
       </c>
-      <c r="J5" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B6" s="2">
         <v>4003</v>
       </c>
@@ -1791,25 +1742,16 @@
         <v>4001</v>
       </c>
       <c r="E6" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F6" s="2">
         <v>80</v>
       </c>
-      <c r="G6" s="2">
-        <v>3</v>
-      </c>
-      <c r="H6" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I6" s="2">
+      <c r="H6" s="2">
         <v>1</v>
       </c>
-      <c r="J6" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B7" s="2">
         <v>4004</v>
       </c>
@@ -1820,25 +1762,16 @@
         <v>4001</v>
       </c>
       <c r="E7" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F7" s="2">
         <v>120</v>
       </c>
-      <c r="G7" s="2">
-        <v>3</v>
-      </c>
-      <c r="H7" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I7" s="2">
+      <c r="H7" s="2">
         <v>1</v>
       </c>
-      <c r="J7" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B8" s="2">
         <v>4005</v>
       </c>
@@ -1849,25 +1782,16 @@
         <v>4001</v>
       </c>
       <c r="E8" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F8" s="2">
         <v>160</v>
       </c>
-      <c r="G8" s="2">
-        <v>3</v>
-      </c>
-      <c r="H8" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I8" s="2">
+      <c r="H8" s="2">
         <v>1</v>
       </c>
-      <c r="J8" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B9" s="2">
         <v>4006</v>
       </c>
@@ -1878,25 +1802,16 @@
         <v>4001</v>
       </c>
       <c r="E9" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F9" s="2">
         <v>200</v>
       </c>
-      <c r="G9" s="2">
-        <v>3</v>
-      </c>
-      <c r="H9" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I9" s="2">
+      <c r="H9" s="2">
         <v>1</v>
       </c>
-      <c r="J9" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="10" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B10" s="2">
         <v>4007</v>
       </c>
@@ -1907,25 +1822,16 @@
         <v>4001</v>
       </c>
       <c r="E10" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F10" s="2">
         <v>240</v>
       </c>
-      <c r="G10" s="2">
-        <v>3</v>
-      </c>
-      <c r="H10" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I10" s="2">
+      <c r="H10" s="2">
         <v>1</v>
       </c>
-      <c r="J10" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="11" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B11" s="2">
         <v>4008</v>
       </c>
@@ -1936,25 +1842,16 @@
         <v>4001</v>
       </c>
       <c r="E11" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F11" s="2">
         <v>280</v>
       </c>
-      <c r="G11" s="2">
-        <v>3</v>
-      </c>
-      <c r="H11" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I11" s="2">
+      <c r="H11" s="2">
         <v>1</v>
       </c>
-      <c r="J11" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="12" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B12" s="2">
         <v>4009</v>
       </c>
@@ -1965,25 +1862,16 @@
         <v>4001</v>
       </c>
       <c r="E12" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F12" s="2">
         <v>320</v>
       </c>
-      <c r="G12" s="2">
-        <v>3</v>
-      </c>
-      <c r="H12" s="2" t="s">
-        <v>277</v>
-      </c>
-      <c r="I12" s="2">
+      <c r="H12" s="2">
         <v>1</v>
       </c>
-      <c r="J12" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="13" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B13" s="2">
         <v>4010</v>
       </c>
@@ -1994,63 +1882,44 @@
         <v>4001</v>
       </c>
       <c r="E13" s="24" t="s">
-        <v>250</v>
+        <v>249</v>
       </c>
       <c r="F13" s="2">
         <v>360</v>
       </c>
-      <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="H13" s="2" t="s">
-        <v>278</v>
-      </c>
-      <c r="I13" s="2">
+      <c r="H13" s="2">
         <v>1</v>
       </c>
-      <c r="J13" s="2" t="s">
-        <v>288</v>
-      </c>
-    </row>
-    <row r="14" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E14" s="24"/>
-      <c r="J14"/>
-    </row>
-    <row r="15" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E15" s="24"/>
-      <c r="J15"/>
-    </row>
-    <row r="16" spans="1:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.3">
       <c r="E16" s="24"/>
-      <c r="J16"/>
-    </row>
-    <row r="17" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="17" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E17" s="24"/>
-      <c r="J17"/>
-    </row>
-    <row r="18" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="18" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E18" s="24"/>
-      <c r="J18"/>
-    </row>
-    <row r="19" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="19" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E19" s="24"/>
-      <c r="J19"/>
-    </row>
-    <row r="20" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="20" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E20" s="24"/>
-      <c r="J20"/>
-    </row>
-    <row r="21" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="21" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E21" s="24"/>
-      <c r="J21"/>
-    </row>
-    <row r="22" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="22" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E22" s="24"/>
-      <c r="J22"/>
-    </row>
-    <row r="23" spans="5:10" x14ac:dyDescent="0.3">
+    </row>
+    <row r="23" spans="5:5" x14ac:dyDescent="0.3">
       <c r="E23" s="24"/>
-      <c r="J23"/>
     </row>
   </sheetData>
   <phoneticPr fontId="13" type="noConversion"/>
@@ -2080,7 +1949,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>251</v>
+        <v>250</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2096,19 +1965,19 @@
         <v>7</v>
       </c>
       <c r="C2" s="8" t="s">
+        <v>251</v>
+      </c>
+      <c r="D2" s="8" t="s">
         <v>252</v>
       </c>
-      <c r="D2" s="8" t="s">
+      <c r="E2" s="8" t="s">
         <v>253</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>254</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>255</v>
-      </c>
-      <c r="G2" s="8" t="s">
-        <v>256</v>
       </c>
       <c r="H2" s="8"/>
       <c r="I2" s="8"/>
@@ -2155,7 +2024,7 @@
         <v>0</v>
       </c>
       <c r="G4" s="2" t="s">
-        <v>257</v>
+        <v>256</v>
       </c>
     </row>
     <row r="5" spans="1:10" x14ac:dyDescent="0.3">
@@ -2175,7 +2044,7 @@
         <v>3</v>
       </c>
       <c r="G5" s="2" t="s">
-        <v>258</v>
+        <v>257</v>
       </c>
     </row>
     <row r="6" spans="1:10" x14ac:dyDescent="0.3">
@@ -2195,7 +2064,7 @@
         <v>0</v>
       </c>
       <c r="G6" s="2" t="s">
-        <v>259</v>
+        <v>258</v>
       </c>
     </row>
     <row r="7" spans="1:10" x14ac:dyDescent="0.3">
@@ -2215,7 +2084,7 @@
         <v>0</v>
       </c>
       <c r="G7" s="2" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="8" spans="1:10" x14ac:dyDescent="0.3">
@@ -2295,7 +2164,8 @@
     <col min="6" max="7" width="14.375" style="2" customWidth="1"/>
     <col min="8" max="8" width="21.625" style="2" bestFit="1" customWidth="1"/>
     <col min="9" max="10" width="23.875" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="13" width="9" style="2" customWidth="1"/>
+    <col min="11" max="11" width="25" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="13" width="9" style="2" customWidth="1"/>
     <col min="14" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -2304,7 +2174,7 @@
         <v>5</v>
       </c>
       <c r="B1" s="25" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
       <c r="C1" s="9"/>
       <c r="D1" s="9"/>
@@ -2323,31 +2193,31 @@
         <v>8</v>
       </c>
       <c r="D2" s="8" t="s">
+        <v>261</v>
+      </c>
+      <c r="E2" s="8" t="s">
         <v>262</v>
       </c>
-      <c r="E2" s="8" t="s">
+      <c r="F2" s="8" t="s">
         <v>263</v>
       </c>
-      <c r="F2" s="8" t="s">
+      <c r="G2" s="8" t="s">
         <v>264</v>
       </c>
-      <c r="G2" s="8" t="s">
+      <c r="H2" s="8" t="s">
         <v>265</v>
       </c>
-      <c r="H2" s="8" t="s">
+      <c r="I2" s="8" t="s">
         <v>266</v>
       </c>
-      <c r="I2" s="8" t="s">
+      <c r="J2" s="8" t="s">
         <v>267</v>
       </c>
-      <c r="J2" s="8" t="s">
+      <c r="K2" s="2" t="s">
         <v>268</v>
       </c>
-      <c r="K2" s="2" t="s">
+      <c r="L2" s="2" t="s">
         <v>269</v>
-      </c>
-      <c r="L2" s="2" t="s">
-        <v>270</v>
       </c>
     </row>
     <row r="3" spans="1:12" x14ac:dyDescent="0.3">
@@ -2359,7 +2229,7 @@
         <v>14</v>
       </c>
       <c r="D3" s="8" t="s">
-        <v>271</v>
+        <v>270</v>
       </c>
       <c r="E3" s="8" t="s">
         <v>13</v>
@@ -2380,7 +2250,7 @@
         <v>13</v>
       </c>
       <c r="K3" s="2" t="s">
-        <v>272</v>
+        <v>271</v>
       </c>
       <c r="L3" s="2" t="s">
         <v>180</v>
@@ -2391,10 +2261,10 @@
         <v>1</v>
       </c>
       <c r="C4" s="2" t="s">
-        <v>273</v>
+        <v>272</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E4" s="24">
         <v>3</v>
@@ -2415,7 +2285,7 @@
         <v>0</v>
       </c>
       <c r="K4" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L4" s="2">
         <v>1.5</v>
@@ -2426,10 +2296,10 @@
         <v>2</v>
       </c>
       <c r="C5" s="2" t="s">
-        <v>243</v>
+        <v>242</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>242</v>
+        <v>241</v>
       </c>
       <c r="E5" s="24">
         <v>1</v>
@@ -2450,7 +2320,7 @@
         <v>1</v>
       </c>
       <c r="K5" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L5" s="2">
         <v>1.5</v>
@@ -2461,10 +2331,10 @@
         <v>3</v>
       </c>
       <c r="C6" s="2" t="s">
-        <v>245</v>
+        <v>244</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>244</v>
+        <v>243</v>
       </c>
       <c r="E6" s="24">
         <v>1</v>
@@ -2485,7 +2355,7 @@
         <v>2</v>
       </c>
       <c r="K6" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L6" s="2">
         <v>1.5</v>
@@ -2496,10 +2366,10 @@
         <v>4</v>
       </c>
       <c r="C7" s="2" t="s">
-        <v>275</v>
+        <v>274</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>246</v>
+        <v>245</v>
       </c>
       <c r="E7" s="24">
         <v>3</v>
@@ -2520,7 +2390,7 @@
         <v>0</v>
       </c>
       <c r="K7" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L7" s="2">
         <v>1.5</v>
@@ -2531,10 +2401,10 @@
         <v>5</v>
       </c>
       <c r="C8" s="2" t="s">
-        <v>276</v>
+        <v>275</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>240</v>
+        <v>239</v>
       </c>
       <c r="E8" s="24">
         <v>5</v>
@@ -2555,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="K8" s="2" t="s">
-        <v>274</v>
+        <v>273</v>
       </c>
       <c r="L8" s="2">
         <v>1.5</v>
@@ -2823,7 +2693,7 @@
         <v>4</v>
       </c>
       <c r="G8" s="21" t="s">
-        <v>248</v>
+        <v>247</v>
       </c>
       <c r="H8" s="2" t="s">
         <v>223</v>
@@ -6221,10 +6091,11 @@
     <col min="3" max="4" width="14.375" style="2" customWidth="1"/>
     <col min="5" max="5" width="23.5" style="2" bestFit="1" customWidth="1"/>
     <col min="6" max="9" width="14.375" style="2" customWidth="1"/>
-    <col min="10" max="10" width="20.75" style="2" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="20.375" style="2" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="15.5" style="2" bestFit="1" customWidth="1"/>
-    <col min="13" max="15" width="9" style="2" customWidth="1"/>
+    <col min="10" max="10" width="20.375" style="2" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="27.75" style="2" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="30.125" style="2" bestFit="1" customWidth="1"/>
+    <col min="13" max="13" width="29.25" style="2" bestFit="1" customWidth="1"/>
+    <col min="14" max="15" width="9" style="2" customWidth="1"/>
     <col min="16" max="16384" width="9" style="2"/>
   </cols>
   <sheetData>
@@ -6272,16 +6143,16 @@
         <v>231</v>
       </c>
       <c r="J2" s="8" t="s">
-        <v>289</v>
+        <v>227</v>
       </c>
       <c r="K2" s="8" t="s">
-        <v>227</v>
+        <v>283</v>
       </c>
       <c r="L2" s="2" t="s">
-        <v>290</v>
+        <v>284</v>
       </c>
       <c r="M2" s="2" t="s">
-        <v>291</v>
+        <v>285</v>
       </c>
     </row>
     <row r="3" spans="1:13" x14ac:dyDescent="0.3">
@@ -6349,10 +6220,10 @@
         <v>15</v>
       </c>
       <c r="J4" s="2">
+        <v>8101</v>
+      </c>
+      <c r="K4" s="2">
         <v>8001</v>
-      </c>
-      <c r="K4" s="2">
-        <v>8101</v>
       </c>
       <c r="L4">
         <v>8002</v>
@@ -6387,10 +6258,10 @@
         <v>15</v>
       </c>
       <c r="J5" s="2">
+        <v>8101</v>
+      </c>
+      <c r="K5" s="2">
         <v>8001</v>
-      </c>
-      <c r="K5" s="2">
-        <v>8101</v>
       </c>
       <c r="L5">
         <v>8002</v>
@@ -6425,10 +6296,10 @@
         <v>15</v>
       </c>
       <c r="J6" s="2">
+        <v>8101</v>
+      </c>
+      <c r="K6" s="2">
         <v>8001</v>
-      </c>
-      <c r="K6" s="2">
-        <v>8101</v>
       </c>
       <c r="L6">
         <v>8002</v>
@@ -6463,10 +6334,10 @@
         <v>15</v>
       </c>
       <c r="J7" s="2">
+        <v>8101</v>
+      </c>
+      <c r="K7" s="2">
         <v>8001</v>
-      </c>
-      <c r="K7" s="2">
-        <v>8101</v>
       </c>
       <c r="L7">
         <v>8002</v>
@@ -6501,10 +6372,10 @@
         <v>15</v>
       </c>
       <c r="J8" s="2">
+        <v>8101</v>
+      </c>
+      <c r="K8" s="2">
         <v>8001</v>
-      </c>
-      <c r="K8" s="2">
-        <v>8101</v>
       </c>
       <c r="L8">
         <v>8002</v>
@@ -6539,10 +6410,10 @@
         <v>15</v>
       </c>
       <c r="J9" s="2">
+        <v>8102</v>
+      </c>
+      <c r="K9" s="2">
         <v>8001</v>
-      </c>
-      <c r="K9" s="2">
-        <v>8102</v>
       </c>
       <c r="L9">
         <v>8002</v>
@@ -6577,10 +6448,10 @@
         <v>15</v>
       </c>
       <c r="J10" s="2">
+        <v>8102</v>
+      </c>
+      <c r="K10" s="2">
         <v>8001</v>
-      </c>
-      <c r="K10" s="2">
-        <v>8102</v>
       </c>
       <c r="L10">
         <v>8002</v>
@@ -6615,10 +6486,10 @@
         <v>15</v>
       </c>
       <c r="J11" s="2">
+        <v>8102</v>
+      </c>
+      <c r="K11" s="2">
         <v>8001</v>
-      </c>
-      <c r="K11" s="2">
-        <v>8102</v>
       </c>
       <c r="L11">
         <v>8002</v>
@@ -6653,10 +6524,10 @@
         <v>15</v>
       </c>
       <c r="J12" s="2">
+        <v>8102</v>
+      </c>
+      <c r="K12" s="2">
         <v>8001</v>
-      </c>
-      <c r="K12" s="2">
-        <v>8102</v>
       </c>
       <c r="L12">
         <v>8002</v>
@@ -6691,10 +6562,10 @@
         <v>15</v>
       </c>
       <c r="J13" s="2">
+        <v>8102</v>
+      </c>
+      <c r="K13" s="2">
         <v>8001</v>
-      </c>
-      <c r="K13" s="2">
-        <v>8102</v>
       </c>
       <c r="L13">
         <v>8002</v>
@@ -6729,10 +6600,10 @@
         <v>15</v>
       </c>
       <c r="J14" s="2">
+        <v>8103</v>
+      </c>
+      <c r="K14" s="2">
         <v>8002</v>
-      </c>
-      <c r="K14" s="2">
-        <v>8103</v>
       </c>
       <c r="L14">
         <v>8003</v>
@@ -6767,10 +6638,10 @@
         <v>15</v>
       </c>
       <c r="J15" s="2">
+        <v>8103</v>
+      </c>
+      <c r="K15" s="2">
         <v>8002</v>
-      </c>
-      <c r="K15" s="2">
-        <v>8103</v>
       </c>
       <c r="L15">
         <v>8003</v>
@@ -6805,10 +6676,10 @@
         <v>15</v>
       </c>
       <c r="J16" s="2">
+        <v>8103</v>
+      </c>
+      <c r="K16" s="2">
         <v>8002</v>
-      </c>
-      <c r="K16" s="2">
-        <v>8103</v>
       </c>
       <c r="L16">
         <v>8003</v>
@@ -6843,10 +6714,10 @@
         <v>15</v>
       </c>
       <c r="J17" s="2">
+        <v>8103</v>
+      </c>
+      <c r="K17" s="2">
         <v>8002</v>
-      </c>
-      <c r="K17" s="2">
-        <v>8103</v>
       </c>
       <c r="L17">
         <v>8003</v>
@@ -6881,10 +6752,10 @@
         <v>15</v>
       </c>
       <c r="J18" s="2">
+        <v>8103</v>
+      </c>
+      <c r="K18" s="2">
         <v>8002</v>
-      </c>
-      <c r="K18" s="2">
-        <v>8103</v>
       </c>
       <c r="L18">
         <v>8003</v>
@@ -6919,10 +6790,10 @@
         <v>15</v>
       </c>
       <c r="J19" s="2">
+        <v>8104</v>
+      </c>
+      <c r="K19" s="2">
         <v>8002</v>
-      </c>
-      <c r="K19" s="2">
-        <v>8104</v>
       </c>
       <c r="L19">
         <v>8003</v>
@@ -6957,10 +6828,10 @@
         <v>15</v>
       </c>
       <c r="J20" s="2">
+        <v>8104</v>
+      </c>
+      <c r="K20" s="2">
         <v>8002</v>
-      </c>
-      <c r="K20" s="2">
-        <v>8104</v>
       </c>
       <c r="L20">
         <v>8003</v>
@@ -6995,10 +6866,10 @@
         <v>15</v>
       </c>
       <c r="J21" s="2">
+        <v>8104</v>
+      </c>
+      <c r="K21" s="2">
         <v>8002</v>
-      </c>
-      <c r="K21" s="2">
-        <v>8104</v>
       </c>
       <c r="L21">
         <v>8003</v>
@@ -7033,10 +6904,10 @@
         <v>15</v>
       </c>
       <c r="J22" s="2">
+        <v>8104</v>
+      </c>
+      <c r="K22" s="2">
         <v>8002</v>
-      </c>
-      <c r="K22" s="2">
-        <v>8104</v>
       </c>
       <c r="L22">
         <v>8003</v>
@@ -7071,10 +6942,10 @@
         <v>15</v>
       </c>
       <c r="J23" s="2">
+        <v>8104</v>
+      </c>
+      <c r="K23" s="2">
         <v>8002</v>
-      </c>
-      <c r="K23" s="2">
-        <v>8104</v>
       </c>
       <c r="L23">
         <v>8003</v>
